--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O282"/>
+  <dimension ref="A1:O303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21910,6 +21910,1623 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>USA Health</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Project Manager - USA Health Shared Services Project Management</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://careers.usahealthsystem.com/jobs/21353?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Mobile, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Bachelor's in business or healthcare administration with 1 year project management experience; substitution with related education/experience allowed.</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>https://usahealthsystem.com</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Academic health system providing hospital care and medical research.</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Project management software</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:12:48 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://careers.publicisgroupe.com/jobs/151351?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>$60k-$80k/yr, $29-$38/hr</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>3-5+ years of agency project management, retail merchandising focus, detail-oriented, cross-functional teams, strong communication; retail planogram experience a plus.</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>https://publicisgroupe.com</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Global communications, advertising, and digital transformation holding company.</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Spreadsheet, Project management tools, Rendering software, Planogram software</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:23:24 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Associate Project Manager</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://careers.publicisgroupe.com/jobs/151350?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>$50k-$63k/yr, $24-$30/hr</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>2+ years of project management experience in an agency environment; strong attention to detail; ability to multi-task; strong communication; experience with distributed teams; exposure to retail merchandising projects a plus.</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>https://publicisgroupe.com</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Global communications, advertising, and digital transformation holding company.</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:20:24 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://careers.velosio.com/jobs/3075</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Project management for ERP/technical implementation; Bachelor's in related field; strong MS Office; PMP helpful; driver's license; 3+ years PM experience.</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Microsoft Word, Excel, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:17:43 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Ascension</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Healthcare Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://jobs.ascension.org/jobs/450093?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Pensacola, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Driver's license; CHC and CAPM/PMP preferred; HS diploma with 3 years' experience or an associate's/bachelor's degree with 2 years' experience; 3 years leadership/management experience preferred.</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>https://ascension.org</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Nonprofit Catholic health system providing hospital and medical care.</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Project management software, Microsoft Project, Excel</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:40:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>MxD</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mxd/jobs/5227847008</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Chicago, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>$58k-$67k/yr, $28-$32/hr</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Associate’s or Bachelor's degree; 2 years in operations, project coordination, or process experience preferred; proficient with MS Office and project tools.</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>https://mxdusa.org</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Drives manufacturing competitiveness through digital technology and cybersecurity solutions.</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Monday.com, Microsoft Teams, HubSpot, CRM</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:18:21 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>GuidePoint Security</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Project Manager (Southeast)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/guidepointsecurity/jobs/6001847004?gh_jid=6001847004</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Tampa or Atlanta or St. Petersburg</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>3+ years project management; 2+ years in consulting/IT PM; Agile experience; Bachelor’s or equivalent; strong communication and leadership; knowledge of information security; MS Office, MS Project; Jira/OpenAir/Salesforce experience.</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>https://guidepointsecurity.com</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Provides cybersecurity consulting, managed services, and integrated technology solutions.</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Jira, OpenAir, Salesforce, Microsoft Project, Microsoft Excel</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:55:34 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>AVI-SPL</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://careers.avispl.com/jobs/11662?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Tampa, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>3-5 years PM experience in AV/Construction/Technology; strong leadership, communication, budgeting; proficient in MS Office and MS Project; valid driver’s license.</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>https://avispl.com</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Provides global audio-visual integration and unified communication solutions.</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>MS Project, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:25:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Great Northern Corporation</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Project Coordinator </t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/gnc/candidateportal/jobs/10010</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>$49k-$49k/yr, $24-$24/hr</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Assists with orders, data entry, and coordination among teams; strong computer skills; high school diploma; detail oriented.</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>https://greatnortherncorp.com</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Manufactures sustainable paper-based packaging and retail display solutions.</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>USA Health</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Project Manager - USA Health Shared Services Project Management</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://internal-usahealth.icims.com/jobs/21353/project-manager---usa-health-shared-services-project-management/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Mobile, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in business or healthcare administration; 1 year of PM experience; ability to manage multiple projects; strong communication and PMO skills.</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>https://usahealthsystem.com</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Academic health system providing patient care and medical education.</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>PMO methodologies, Project management tools, templates, status reporting, budgets</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>General Dynamics Electric Boat</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Facilities Project Manager</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://careers-gdeb.icims.com/jobs/19185/facilities-project-manager/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Groton, Connecticut, United States</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>2+ years facilities engineering or construction; Associate degree in Engineering, Construction Management, or Architecture; strong cross-discipline knowledge; able to manage multiple projects; excellent communication.</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>https://gdeb.com</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Designs, builds, and maintains submarines for the U.S. Navy.</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Corrigo, Oracle, Procore, Microsoft Excel, Microsoft Project, Microsoft Word, Microsoft PowerPoint, Microsoft OneNote, Outlook</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Midwest Interventional Systems</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Project Manager  (MN, Maple Grove)</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://recruiting.myapps.paychex.com/appone/MainInfoReq.asp?R_ID=7155809&amp;B_ID=91&amp;fid=1&amp;SearchScreenID=21825&amp;ssbgcolor=#FFFFFF</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Maple Grove, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Project management experience in product development; budgeting, risk analysis, cross-functional leadership; client relations.</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>https://midwestint.com</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Contract design and manufacturing of minimally invasive medical devices.</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Project management tools, Timelines, RAID, MS Project</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>First Onsite</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Project Manager - Restoration/Construction</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://firstonsiteus.applicantpro.com/jobs/4095190</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Maryland Heights, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>$75k-$85k/yr, $36-$40/hr</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>2+ years as Assistant Project Manager; skilled in construction drawings, specs, take-offs; 7+ industry certifications; valid driver's license; HS diploma; DR/GC experience.</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>https://firstonsite.com</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Provides disaster restoration and property reconstruction services.</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>MS Word, MS Excel, Microsoft Outlook, Xactimate</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>First Onsite</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Project Manager - Restoration/Construction</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://firstonsiteus.applicantpro.com/jobs/4095198</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Lihue, Hawaii, United States</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>$85k-$95k/yr, $40-$45/hr</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>2+ years as Assistant Project Manager; skilled in construction drawings, specs, and take-offs; DR or GC experience; 7+ industry certifications; high school diploma; valid driver's license.</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>https://firstonsite.com</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Provides disaster restoration and property reconstruction services.</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>First Onsite</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Traveling Project Manager - Mitigation</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://firstonsiteus.applicantpro.com/jobs/4095704</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>$75k-$95k/yr, $36-$45/hr</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>2+ years as Assistant Project Manager in restoration/construction; skilled with drawings, specs, take-offs; 7+ certifications; valid driver’s license; high school diploma.</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>https://firstonsite.com</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Provides disaster restoration and property reconstruction services.</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>MS Word, Excel, Microsoft Outlook, Xactimate</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>I.B. Abel</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Project Manager (Electrical Construction)</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://ibabel.bamboohr.com/careers/501</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>York, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>3 years electrical construction project management; Bachelor’s degree in CM/Engineering/Business/Finance/Accounting or related field; proficient with MS Office, MS Project, Copilot.</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>https://ib-abel.com</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Provides electrical construction and utility infrastructure services.</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, MS Project, Copilot</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Digital Infuzion</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>http://digitalinfuzion.applytojob.com/apply/TdcnYVPe9s/Project-Manager</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Rockville, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Experience managing federal IT projects; complex technical projects; PMP certification; 2+ years; bachelor's degree or 6 years of related experience; strong organizational and communication skills.</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>https://digitalinfuzion.com</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Provides biomedical informatics and software for federal health research.</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>KE&amp;G Construction</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Project Manager/Estimator (Heavy Civil)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>http://kegconstruction.applytojob.com/apply/4OSXjoM5NB/Project-ManagerEstimator-Heavy-Civil</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Sierra Vista, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Project Manager/Estimator in heavy civil with experience managing projects, estimating, and team mentorship.</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>https://kegtus.com</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Provides heavy civil construction and infrastructure services in Arizona.</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Haddad Plumbing &amp; Heating</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>http://haddadplumbingheating.applytojob.com/apply/2yKZKQXtBC/Assistant-Project-Manager</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Newark, New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>$65k-$75k/yr, $31-$36/hr</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Mechanical engineering degree; AutoCAD proficiency; OSHA 30; strong communication and organizational skills; ability to work under pressure.</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>https://haddadplumbing.com</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Specialized plumbing and HVAC services for large-scale buildings</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>AutoCAD</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Batchelor &amp; Kimball</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Prefabrication Project Manager</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://bkimechanical.bamboohr.com/careers/406</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Conyers, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>BS in Mechanical engineering; experience in pipe fabrication; strong communication; MS Office; organized; team-oriented.</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>https://bkimechanical.com</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Mechanical and plumbing construction for complex commercial facilities.</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Autobid software, Revit, Microsoft Office, Excel</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SixAxis</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=230815&amp;clientkey=84A3B1A44134E9D4710727973651E0FB</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>West Chester, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree or equivalent experience; previous project management experience; construction industry knowledge; strong leadership; excellent written and verbal communication; proficiency in Microsoft Office and ERP systems.</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>https://sixaxisllc.com</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Manufactures industrial safety equipment and modular access solutions.</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Microsoft Office, ERP systems</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O303"/>
+  <dimension ref="A1:O346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22130,11 +22130,7 @@
           <t>Global communications, advertising, and digital transformation holding company.</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr">
         <is>
           <t>2026-05-21 01:20:24 PM CDT</t>
@@ -22142,11 +22138,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -22197,16 +22189,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr">
         <is>
           <t>Microsoft Project, Microsoft Word, Excel, PowerPoint</t>
@@ -22592,11 +22576,7 @@
           <t>Manufactures sustainable paper-based packaging and retail display solutions.</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr">
         <is>
           <t>2026-05-21 01:00:00 AM CDT</t>
@@ -22977,11 +22957,7 @@
           <t>Provides disaster restoration and property reconstruction services.</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
@@ -23208,11 +23184,7 @@
           <t>Provides biomedical informatics and software for federal health research.</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
@@ -23285,11 +23257,7 @@
           <t>Provides heavy civil construction and infrastructure services in Arizona.</t>
         </is>
       </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
@@ -23522,6 +23490,3305 @@
         </is>
       </c>
       <c r="O303" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Infrastructure Networks (iNet)</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>PROJECT COORDINATOR</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4192170</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Midland, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>3-5 years in project coordination/operations; multi-workflow management; strong organizational skills; cross-functional collaboration.</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>https://inetlte.com</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Provides private LTE and satellite connectivity for remote industrial operations.</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Salesforce, Smartsheet, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>2026-05-21 06:52:58 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Northwell Health</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Project Manager - VIVOHealth (Hybrid)</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://eppr.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/189449</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>New Hyde Park, New York, United States</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>$70k-$116k/yr, $33-$56/hr</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent; 1-3 years experience; PMP preferred.</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Provides clinical healthcare services through a hospital network.</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>2026-05-21 06:24:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>The Driver Provider</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Project Manager - Transportation</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://the-driver-provider.prismhr-hire.com/job/994012/project-manager-transportation</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Claude, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>$145600k-$156000k/yr, $70000-$75000/hr</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Experience managing transportation projects with DOT knowledge; leadership, scheduling, staffing, and compliance; able to work weekends and evenings.</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>https://driverprovider.com</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Premium ground transportation and executive chauffeur services.</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Word processing, Spreadsheets, Email, Database software</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>2026-05-21 06:19:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Project Manager - Hybrid</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://evac.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/435233</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Renton or Irvine or Portland</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or 2-3 years of related project management experience; 2 years in research/grant/healthcare administration.</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>https://providence.org</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Provides comprehensive healthcare services through hospitals, clinics, and health plans.</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>2026-05-21 06:05:31 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Washoe County</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>BUILDING OPERATIONS PROJECT MANAGER</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://www.governmentjobs.com/careers/washoecounty/jobs/5351736</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Reno, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>$78k-$102k/yr, $37-$49/hr</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Four years of project management experience in design/construction; associate degree in construction technology, project management, architecture, or related field; valid driver's license; background check required.</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>https://washoecounty.us</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Provides public services and governance for Washoe County, Nevada.</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Facility management software</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>2026-05-21 06:05:05 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Universal Destinations &amp; Experiences</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Digital Project Manager</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://careers.pageuppeople.com/851/cw/en/job/661859</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Orlando, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree; 1+ years in digital marketing or project management; Agile familiarity; stakeholder management; experience with Workfront/Jira/Asana/Trello; ability to manage multiple digital projects.</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>https://universalorlando.com</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Operates theme parks and immersive entertainment resorts globally.</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Workfront, Asana, Trello, Jira</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:45:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Bosch Building Technologies</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=5fd65cec-5d8b-42e2-b102-5a14f2d591d1&amp;jobId=590389</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>$52k-$69k/yr, $25-$33/hr</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>2 years in admin/project management or security integration; travel to client sites; proficient in Microsoft Office; high school diploma or GED; valid US driver’s license; able to pass pre-employment screening.</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>https://boschbuildingtechnologies.com</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Provides integrated building automation, security, and energy management solutions.</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:30:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>City of Frederick</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Project Coordinator Returnship</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://www.governmentjobs.com/careers/frederick/jobs/5351768</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Frederick, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>$52k-$52k/yr, $25-$25/hr</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>On-site returnship requiring six-month resume gap; on-site commute; experience in business development, marketing, workforce development, or public/private administration; strong organizational, communication, and time management skills; proficiency with Microsoft Word/Excel/PowerPoint; able to work independently and in a team.</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Part Time, Temporary</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>https://cityoffrederickmd.gov</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Provides municipal services and local governance for Frederick, Maryland.</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Database experience</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:26:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Chino</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://www.governmentjobs.com/careers/chinoca/jobs/5350747</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Chino, California, United States</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>$97k-$118k/yr, $46-$57/hr</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Four years of increasingly responsible project management experience; associate degree or equivalent coursework in related fields; valid California Driver’s License.</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>https://cityofchino.org</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Providing municipal services and public safety for Chino residents</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:03:56 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://egup.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/20273504</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Pelzer, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Administrative coordination, document control, reporting support; MS Office/SharePoint proficiency; travel up to 30-50%.</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>https://vertiv.com</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Provides critical power and cooling for data centers.</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Microsoft Outlook, SharePoint</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:53:32 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://eoje.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/6338</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Bowling Green or New Albany</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Bachelor's in computer science, information systems, business, or related field; 2+ years project coordination; knowledge of project mgmt methodologies; strong communication; proficient with MS Office, ERP, ServiceNow, Salesforce.</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>https://blackbox.com</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Global provider of digital infrastructure and managed IT solutions.</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>MS Office, Outlook, SharePoint, MS Project, PPM tools, ERP, ServiceNow, Salesforce, Workforce management, Cloud-based systems</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:53:23 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Ellis Fire</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Service Sales and Project Manager</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://jobs.ourcareerpages.com/job/990767</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Woburn, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>$85k-$110k/yr, $40-$52/hr</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Manage service sales and project activities, coordinate with customers and subcontractors, and ensure successful delivery of fire protection projects.</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>https://ellisfire.com</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Provides fire protection and life safety system installation and services.</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>AutoCAD, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:23:12 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Trileaf</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Environmental Project Manager</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=e526c099-9ef9-40c8-9b4c-30f78cca988d&amp;jobId=579448</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Austin, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>$75k-$90k/yr, $36-$43/hr</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>2+ years managing employees and client relationships; valid driver’s license; telecom experience preferred; EP designation preferred; strong leadership and communication; bachelor's in geology/environmental sciences/engineering.</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>https://trileaf.com</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Provides environmental, architecture, and engineering consulting services nationwide.</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:23:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Illinois Education Association</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Temp Grant Project Coordinator:  NEA Grant</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=276fbcea-bc8c-47d9-9583-7e4fb92c5a05&amp;jobId=542480</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Springfield, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>$43k-$66k/yr, $21-$31/hr</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>High school diploma; strong typing, spelling, math; basic office skills; independent work; MS Office; valid driver’s license; experience with grant coordination is a plus.</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Temporary</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>https://ieanea.org</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Provides labor representation and advocacy for Illinois education staff.</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Microsoft Office, NEA360, Power BI</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:48:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/telus-digital/5a68e201-1597-4888-8146-9fd1ad4e49f1</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>St. Louis, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>$95k-$110k/yr, $45-$52/hr</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Experience leading complex programs, stakeholder management, and roadmaps; ability to manage delivery and governance.</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>https://telusdigital.com</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Provides global digital customer experience and business transformation solutions.</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:43:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>FedEx</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Civil/Mechanical Engineering Project Manager Co-op</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://fedex.paradox.ai/co/FederalExpressCorporation41/Job?job_id=P25-339767-1</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Moon Township, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>$41k-$83k/yr, $20-$40/hr</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Co-op role for engineering student; GPA 3.0+; majors in engineering or related fields preferred; on-site project management exposure; pay $20-$40/hour; relocation stipends possible.</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>https://fedex.com</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Global provider of courier, logistics, and transportation services.</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:41:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Barnhart</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://barnhart-crane-rigging.breezy.hr/p/8a1270a140a5-project-manager</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Jackson, Mississippi, United States</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree or substantial experience; PMP preferred; strong planning, leadership, and communication skills; willing to travel; environmental and safety compliance knowledge.</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>https://barnhartcrane.com</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Provides heavy lifting and specialized transport for industrial projects.</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:26:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Veridiam</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Project Manager - Business Development</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=ac90b88c-560b-4f32-8d8b-c52c535d936c&amp;jobId=569269</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>El Cajon, California, United States</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>$72k-$93k/yr, $34-$44/hr</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in business administration or related field; 3+ years project management or related experience; strong planning, communication, and organizational skills.</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:19:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Zonda</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Project Manager I</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=87b761b2-fd2c-46a5-8297-bc335bcb502f&amp;jobId=596660</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>1-3 years in homebuilding/ArchViz or digital media; Bachelor's degree; PMP/CAPM/Agile a plus; proficient with Jira, Asana, Monday.com, Trello; strong communication and stakeholder management.</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>https://zondahome.com</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Provides data intelligence and advisory for the homebuilding industry.</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Jira, Asana, Monday, Trello</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:56:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>American Ecotech</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Technical Project Manager R&amp;D</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=63609de7-9e2a-4126-88b3-04eab24bbf71&amp;jobId=949823</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Warren, Rhode Island, United States</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a scientific or engineering field; proven experience managing technical or R&amp;D projects; ability to guide products from development to commercialization; knowledge of particulate measurement or aerosol science; strong organizational and leadership skills.</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>https://americanecotech.com</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Designs and distributes air quality and environmental monitoring instrumentation.</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Project Management Software, Documentation tools</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:44:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>HydraPak</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Run Marketing Project Manager</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://hydrapak.rippling-ats.com/job/1026152/run-marketing-project-manager</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Longmont, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>$80k-$100k/yr, $38-$48/hr</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Marketing project management, event marketing, and brand activation experience; strong organization and communication; running/endurance sports knowledge; bachelor’s degree; 3–7 years in related roles.</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>https://hydrapak.com</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Designs and manufactures performance hydration systems and accessories.</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:23:23 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Integra Beauty</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Site Experience Project Coordinator (On-Site)</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/integrabeauty/b8ae59e5-14c6-4b84-8d07-0b53313d704e/apply</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Dania Beach, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>2+ years in project management; experience across creative, marketing, operations; hands-on Shopify; CRO focus.</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>https://integrabeauty.com</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Developing and scaling innovative hair care and beauty brands.</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>Shopify, Figma, GA4, Google Analytics</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:43:24 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Construction Theory</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Construction Design Project Manager</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://constructiontheory.betterteam.com/construction-design-project-manager-1</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Charlotte, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>$41k-$72k/yr, $20-$35/hr</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Part-time role with entry to mid-level experience; strong design software skills; client coordination; measurements and takeoffs; project coordination.</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>https://constructiontheory.com</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Charlotte-based design-build firm providing custom construction and renovation services.</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>AutoCAD, Chief Architect, SketchUp, Adobe Creative Suite, Microsoft Office, Excel, Word, 2D CAD, 3D CAD, Onscreen takeoff, Estimating tools</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:00:10 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>MasTec</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Sr Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://careers.mastec.com/jobs/64064/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Spokane, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>$47k-$58k/yr, $23-$28/hr</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Coordinate with Project Managers and Finance; proficiency in Microsoft Office; strong communication, time management, and budgeting/reporting skills; leadership and project management abilities.</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>https://mastec.com</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Builds and maintains energy, communications, and utility infrastructure.</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:42:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>AVI-SPL</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Associate Project Manager</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://careers.avispl.com/jobs/11670/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Wixom, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Assistant project manager or project coordinator experience; proficient with Microsoft Office; strong communication; able to travel; valid driver’s license.</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>https://avispl.com</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Design and installation of workplace collaboration and audio-visual technology.</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Microsoft Office, PDF software</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:24:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>UES</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Geotechnical Project Manager</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://careers.teamues.com/jobs/4027/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Simpsonville, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Bachelor in Civil or Geological Engineering; 3+ years geotechnical experience; PE preferred; PMP a plus; proven track record in managing mid-to-large engineering projects.</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>https://teamues.com</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Provides geotechnical engineering, environmental consulting, and construction materials testing.</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:29:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>UES</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Construction Materials Testing (CMT) Project Manager</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://careers.teamues.com/jobs/4026/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Charleston, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Civil Engineering or Construction Management; 4–7 years CMT/inspection; certifications preferred; valid driver’s license; willingness to travel up to 40%.</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>https://teamues.com</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Provides geotechnical engineering, environmental consulting, and construction materials testing.</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Project management software</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:25:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Kentucky Community and Technical College System</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Project Manager/Technical Instructor – Workforce Solutions/Workforce Liaison III</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://careers.pageuppeople.com/1124/cw/en/job/496475</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Florence, Kentucky, United States</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>$51k-$54k/yr, $24-$26/hr</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; four years of experience; project management; training/instruction; strong communication; relationship building; detail-oriented; proficient in Microsoft Office.</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>https://kctcs.edu</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Public system providing associate degrees and technical career training.</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel, Forms, Outlook, Teams, SharePoint, Word</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>2026-05-21 08:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Mississippi State University</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Project Manager, STEP</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://careers.pageuppeople.com/773/cw/en/job/510667</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Starkville, Mississippi, United States</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Master's degree in education, public administration, organizational leadership, or business; two years of program coordination or project management experience.</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>https://msstate.edu</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Public university providing higher education and academic research programs</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Canvas LMS, Modern Campus, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>2026-05-21 08:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>The Steel Network</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Project Manager- Commercial Doors &amp;amp; Hardware</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://steelnetwork.applicantstack.com/x/detail/a2f22hf43c8l</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Durham, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>3+ years in door and hardware detailing, estimating, and project management; Pro-Tech and ComSense experience; PM in construction/building materials; strong communication and organizational skills.</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>https://steelnetwork.com</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Manufactures light gauge cold-formed steel studs and connectors.</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>ComSense, Pro-Tech, Microsoft Office (Excel, Teams, Outlook, OneDrive)</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>The Steel Network</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager- Commercial Doors &amp;amp; Hardware</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://steelnetwork.applicantstack.com/x/detail/a2f22hf1qg0a</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Durham, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>2+ years in doors and hardware or related construction; proficient with Microsoft Office; familiarity with bid tracking; knowledge of door hardware and construction materials; local to Raleigh-Durham, NC.</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>https://steelnetwork.com</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Manufactures light gauge cold-formed steel studs and connectors.</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>ComSense, Pro-Tech, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>The PENTA Building Group</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>MEP Project Manager</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://jobs.jobvite.com/pentabuildinggroup/job/oDJaAfwQ?nl=1&amp;fr=true</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Mettler, California, United States</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>$100k-$130k/yr, $48-$62/hr</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Minimum 2 years as a Project Manager on commercial construction; minimum 3 years in MEP scopes; degree in Construction Management or related field or equivalent experience; OSHA 10 or 30; ability to read drawings; scheduling knowledge; on-site availability in Mettler, CA or willingness to relocate; salary DOE.</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>https://pentabldggroup.com</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Commercial general contractor providing construction and preconstruction services.</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Scheduling software</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Naval Project Manager</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://careers.boozallen.com/careers/JobDetail/Washington-Naval-Project-Manager-R0240710/124885</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Washington, District of Columbia, United States</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>$77k-$176k/yr, $37-$84/hr</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>3+ years in project/program management with experience in ship production, scheduling, budgeting, and risk management.</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>https://boozallen.com</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Consulting and technology services for government and commercial clients</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Project, SharePoint, Teams, Power BI, Word, Excel, Visio, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Project Manager, Construction</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://apply-arco.icims.com/jobs/11404/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Albany, New York, United States</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>3-5 years construction project management; estimating; design/build; bachelor’s in Engineering, Construction Management, or related field.</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Provides design-build construction for industrial and commercial facilities.</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>2026-05-21 06:41:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Great Northern Corporation</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Project Coordinator </t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/gnc/candidateportal/jobs/10015</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Chippewa Falls, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>$41k-$52k/yr, $20-$25/hr</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>High school diploma or GED; 2-4 years in customer relations; excellent interpersonal, verbal and written communication.</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>https://greatnortherncorp.com</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Manufactures sustainable paper-based packaging and retail display solutions.</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>2026-05-21 01:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Performance Contracting Group</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/pcg/candidateportal/jobs/7649</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>$115k-$140k/yr, $55-$67/hr</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>3-5 years construction management; experience with drywall, scaffolding, insulation, demolition; proficient in Excel/Word; strong communication and scheduling abilities.</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>https://performancecontracting.com</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Provides national specialty construction, insulation, and environmental abatement services.</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, On-Screen Takeoff, Quickbid</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Wharton-Smith</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/whartonsmith/candidateportal/jobs/8592</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Tampa, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Bachelor's in Civil/Mechanical/Construction Management; 3+ years in engineering/construction; strong communication; CPM scheduling; Primavera P6 experience</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>https://whartonsmith.com</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>General contractor specializing in water and commercial infrastructure.</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Primavera P6, Microsoft Office, Construction Management Software, CPM Scheduling Programs</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Stratus</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Project Manager, Exterior Signage</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://careers-stratus.icims.com/jobs/3903/project-manager%2c-exterior-signage/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Mentor or Rolling Meadows or Clearwater or San Antonio or Mentor</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>$55k-$70k/yr, $26-$33/hr</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Experience managing projects in signage, construction, manufacturing, or multi-site programs; strong communication; cross-functional coordination; solid budgeting; PMP/CAPM preferred but not required; ability to manage multiple projects.</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>https://stratusunlimited.com</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Provides national brand implementation and facility maintenance solutions.</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Morgan Properties</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Make Ready Project Manager</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/morganprop/candidateportal/jobs/16767</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Fort Wayne, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>$50k-$55k/yr, $24-$26/hr</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Experience coordinating make-ready/turns, vendor coordination, and property management or multifamily operations preferred.</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>https://morgan-properties.com</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Operates and manages multifamily residential apartment communities.</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Morgan Properties</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Make Ready Project Manager</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/morganprop/candidateportal/jobs/16760</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Akron, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>$70k-$80k/yr, $33-$38/hr</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Experience coordinating vendors and on-site teams; make-ready/turn processes; property management experience preferred; strong organizational and communication skills.</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>https://morgan-properties.com</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Operates and manages multifamily residential apartment communities.</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>CyberData Technologies</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Portfolio Specialist/Project Coordinator (NEI-4)</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://recruit.hirebridge.com/v3/careercenter/v2/details.aspx?jid=729526&amp;cid=7990&amp;locvalue=1020</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Bethesda, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>2-5 years as a Business Analyst or in a similar role; strong portfolio management and reporting skills.</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>https://cyberdatainc.com</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Delivers IT and cybersecurity services for US federal agencies.</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>ServiceNow, Visio, MS-Project</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>EAD</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager/Construction Manager - Lancaster, PA</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://eadcorporate.isolvedhire.com/jobs/1778771</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Lancaster, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Bachelor's in engineering or construction management; 0-3 years PM/CM; OSHA 30; PMP preferred; MS Office proficiency; manage projects &gt;$1M; valid driver's license.</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>https://eadcorporate.com</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Engineering, automation, and project management services for industrial facilities.</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel, Word</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Verogy</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://verogy.bamboohr.com/careers/73</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>West Hartford, Connecticut, United States</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>2-4 years in project management or coordination; degree in business, project/construction management, renewable energy, or related field; strong organizational and communication skills; experience managing schedules and documentation.</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>https://verogy.com</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Developing and managing commercial and municipal solar energy projects.</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Smartsheet</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
         </is>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O346"/>
+  <dimension ref="A1:O369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23634,11 +23634,7 @@
           <t>Provides clinical healthcare services through a hospital network.</t>
         </is>
       </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr">
         <is>
           <t>2026-05-21 06:24:37 PM CDT</t>
@@ -23788,11 +23784,7 @@
           <t>Provides comprehensive healthcare services through hospitals, clinics, and health plans.</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr">
         <is>
           <t>2026-05-21 06:05:31 PM CDT</t>
@@ -24173,11 +24165,7 @@
           <t>Providing municipal services and public safety for Chino residents</t>
         </is>
       </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr">
         <is>
           <t>2026-05-21 05:03:56 PM CDT</t>
@@ -24481,11 +24469,7 @@
           <t>Provides environmental, architecture, and engineering consulting services nationwide.</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr">
         <is>
           <t>2026-05-21 04:23:00 PM CDT</t>
@@ -24635,11 +24619,7 @@
           <t>Provides global digital customer experience and business transformation solutions.</t>
         </is>
       </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr">
         <is>
           <t>2026-05-21 03:43:55 PM CDT</t>
@@ -24789,11 +24769,7 @@
           <t>Provides heavy lifting and specialized transport for industrial projects.</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr">
         <is>
           <t>2026-05-21 03:26:51 PM CDT</t>
@@ -24858,11 +24834,7 @@
       </c>
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr">
         <is>
           <t>2026-05-21 03:19:00 PM CDT</t>
@@ -25474,11 +25446,7 @@
           <t>Provides geotechnical engineering, environmental consulting, and construction materials testing.</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr">
         <is>
           <t>2026-05-21 10:29:00 AM CDT</t>
@@ -26090,11 +26058,7 @@
           <t>Provides design-build construction for industrial and commercial facilities.</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr">
         <is>
           <t>2026-05-21 06:41:00 AM CDT</t>
@@ -26167,11 +26131,7 @@
           <t>Manufactures sustainable paper-based packaging and retail display solutions.</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr">
         <is>
           <t>2026-05-21 01:00:00 AM CDT</t>
@@ -26398,11 +26358,7 @@
           <t>Provides national brand implementation and facility maintenance solutions.</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr">
         <is>
           <t>2026-05-20 11:00:00 PM CDT</t>
@@ -26475,11 +26431,7 @@
           <t>Operates and manages multifamily residential apartment communities.</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr">
         <is>
           <t>2026-05-20 11:00:00 PM CDT</t>
@@ -26552,11 +26504,7 @@
           <t>Operates and manages multifamily residential apartment communities.</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr">
         <is>
           <t>2026-05-20 11:00:00 PM CDT</t>
@@ -26789,6 +26737,1777 @@
         </is>
       </c>
       <c r="O346" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ATI Restoration</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/atiexternal/cx/job-details?reqId=5001200718706</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah, United States</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>1+ year experience in a coordinator or administrative role; high school diploma; strong customer service and communication; proficient with Salesforce and MS Office; construction industry experience preferred</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>https://atirestoration.com</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Providing disaster recovery, property restoration, and environmental remediation services.</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>MS Word, Excel, PowerPoint, G Suite, Xactimate, Salesforce</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:01:35 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Centex Construction</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=b0df0465-6f34-4d0f-8cad-0914240ca80b&amp;jobId=564362</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Lewisville or United States</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>$65k-$85k/yr, $31-$40/hr</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Oversee day-to-day operations of multifamily renovation projects; manage schedules, budgets, safety, and on-site leadership; coordinate with subcontractors and stakeholders.</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>https://centexconstruction.com</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Renovates and restores multi-family and commercial real estate properties.</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Microsoft Office Suite</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:25:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Fortive</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Construction Project Manager - Close Out</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://ejta.fa.us6.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/9843</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Bachelor's in Engineering/Architecture/Construction Management; 3-5+ years in construction procurement/management; knowledge of NYC regs; Procore/MS Project; travel to NYC boroughs.</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>https://fortive.com</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Manufactures professional instrumentation, industrial tools, and specialized software.</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Procore, MS Project, Smartsheet</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:57:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Deep Blue Sports + Entertainment</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Project Manager, Partnerships</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/deepblue/jobs/4698724005</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>$75k-$90k/yr, $36-$43/hr</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>2+ years project management in fast-paced environments; strong client relations; cross-functional coordination; travel flexibility.</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>https://deepbluesportsent.com</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Drives commercial investment and marketing strategy for women's sports.</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Google Suite, Slack, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:56:34 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Stuller</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Sales Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://secure4.saashr.com/ta/6052029.careers?ShowJob=973395715</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Lafayette, Louisiana, United States</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree or equivalent; 3+ years project or program management in a fast-paced environment; strong organizational and communication skills; cross-functional collaboration.</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>https://stuller.com</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Manufacturer and supplier of jewelry components, gemstones, and tools.</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Salesforce, CRM, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:30:03 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Nox Group</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>MARKETING PROJECT MANAGER</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>https://noxgroup.us/careers/?gh_jid=5228064008</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Phoenix, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Strong project management across departments; proficient with ClickUp and Adobe; 3+ years PM; Bachelor's in Marketing/Communications; PMP preferred.</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>https://noxgroup.us</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Provides industrial construction and virtual design services for large-scale projects.</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>ClickUp, Adobe Creative Suite</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:40:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Plant Project Manager</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://careers.se.com/jobs/117074?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Mount Juliet, Tennessee, United States</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in engineering, Supply Chain, or Business Management; SQL knowledge; problem-solving; MS Office; SAP experience preferred; willingness to contribute to process improvements.</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>https://se.com</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Provider of energy management and industrial automation solutions.</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>SQL, SAP, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:24:08 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Ambient Enterprises</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Johnson Barrow</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/ambiententerprises/jobs/5228538008</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Boise, Idaho, United States</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>$58k-$62k/yr, $28-$30/hr</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Administrative and customer service duties; order processing; QuickBooks experience; HVAC industry familiarity.</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>https://ambient-enterprises.com</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Collective of specialized HVAC design and implementation firms.</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>QuickBooks, Manufacturer software</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:59:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Capitalize Analytics</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/capitalize-data-analytics-llc/jobs/a0b622e9-a945-4655-8b37-1aa2e56eb72b</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Lead delivery of data/tech projects; 4–8 years in technical/delivery roles; strong PM skills with Azure DevOps/Jira; excellent communication.</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>https://capitalizeconsulting.com</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>Provides data analytics, AI, and automation consulting services.</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Azure DevOps, Jira, Azure Data Services, Databricks, Microsoft Fabric, Alteryx, UiPath</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:37:46 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Omnicom Media Group</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://omnicommedia.com/careers/us/omnicom-media-network/?gh_jid=5127837007</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>$50k-$95k/yr, $24-$45/hr</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>2–4 years in project management or media coordination; Bachelor’s degree in Advertising/Marketing/Communications/Business or related field preferred; pharma knowledge is a plus; strong organizational and communication skills; proficient in MS Office and planning tools.</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>https://omnicommedia.com</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Provides global media strategy, planning, and data-driven marketing services.</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Microsoft Office, CRM, planning tools, reporting platforms</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:54:52 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Advanced Technology Services</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Maintenance Planning/Scheduling Project Manager</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/advancedtechnologyservices/jobs/4679960006</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Greenville, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>$104k-$134k/yr, $50-$64/hr</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Associates degree and four years of related experience; 3 years in Manufacturing or IT; 1 year of operational leadership; 1 year with quality-based operating systems.</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>https://advancedtech.com</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Provides managed industrial maintenance and reliability services for manufacturers.</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:51:20 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Clean Harbors</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Field Service Project Manager</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://epyc.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/161338</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Sparks, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>High school diploma required; associates or bachelor’s degree preferred; 3+ years environmental field service operations; leadership experience preferred; Emergency Response and Marine Spill Response training preferred; knowledge of regulations.</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>https://cleanharbors.com</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Provides hazardous waste management and industrial cleaning services.</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Cost estimating, Computer skills</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:50:06 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>QXO</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://jobs.becn.com/jobs/12337?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Aurora, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>$100k-$130k/yr, $48-$62/hr</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Strong leadership and project management skills; excellent communication and organizational abilities; ability to manage multiple projects; attention to detail; independent decision making; supervisory experience; proficient with project management and business software tools.</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>https://qxo.com</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Tech-enabled distributor of building materials and products.</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Project management software</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>2026-05-21 02:16:11 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>ServiceMaster Restore by Service Now</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3419451</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Tustin, California, United States</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>$70k-$95k/yr, $33-$45/hr</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>High school diploma required; valid driver’s license; experience managing teams; knowledge of insurance restoration/construction; proficient in Xactimate; strong customer service skills.</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>https://servicemasterrestore.com</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Provides professional disaster restoration and property cleaning services.</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Xactimate, Estimator software, Tablet/Mobile tools</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:16:52 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>C&amp;S Electrical Contractor South</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Electrical Project Manager</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3419330</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Jacksonville, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Oversee multiple construction projects; manage budgets, schedules, and subcontractors; ensure code compliance.</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>https://careerplug.com</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>Provides commercial and residential electrical contracting services.</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Construction management software</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:36:51 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>DRYmedic Restoration Services</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Mitigation Project Manager</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3419250</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Charlotte, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>$52k-$64k/yr, $25-$31/hr</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Emergency restoration experience, sales ability, strong communication, and leadership skills.</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>https://drymedic.com</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Provides disaster restoration services for residential and commercial properties.</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Xactimate, DASH software</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:15:54 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>E2 Optics</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Project Manager, Hyperscale</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://careers-e2optics.icims.com/jobs/3394/project-manager%2c-hyperscale/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Columbus, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree preferred; 3+ years PM experience in construction, telecommunications, or data centers; PMP preferred.</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>https://e2optics.com</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Provides low-voltage technology integration and infrastructure solutions.</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>MS Project, Primavera P6, BIM</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>ICONIX Waterworks</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://us-iconixww.icims.com/jobs/5208/project-coordinator/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Sacramento, California, United States</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>$60k-$60k/yr, $28-$28/hr</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>High school diploma; 2+ years in construction coordination; estimating and take-off; basic invoicing math.</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>https://iconixww.com</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Distributor of water, wastewater, and civil construction products.</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Estimating, Take-off, Invoicing, Project management</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>American Heart Association</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://careers-heart.icims.com/jobs/17508/project-manager/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>$80k-$90k/yr, $38-$43/hr</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in public health, healthcare administration, nonprofit management, or related field; three years of program coordination or project management experience; PMP certification a plus; strong coordination, planning, and stakeholder management.</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>https://heart.org</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Nonprofit organization dedicated to fighting heart disease and stroke.</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Project management tools, Database management</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Aptive Resources</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://artemisarc-aptiveresources.icims.com/jobs/4357/project-manager/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Lead modernization projects for VHA VFMP; oversee lifecycle; coordinate stakeholders; support Agile and traditional PM; ensure on-time delivery within scope, schedule, budget.</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>https://aptiveresources.com</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Provides management and technology consulting services to government agencies.</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>PMP, Agile, Scrum</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Paul Davis Restoration</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Operations &amp; Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3418636</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Brownstown, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>$45k-$52k/yr, $22-$25/hr</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>High school diploma or GED; valid driver’s license with insurable driving record; strong communication, organization, and detail orientation; ability to work independently in a deadline-driven environment.</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>https://pauldavis.com</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Emergency property restoration and reconstruction services for disaster damage.</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>RMS, DASH, Xactimate, Claims Force, Valudate, Docusketch, SharePoint</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>2026-05-20 10:01:05 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Egan Company</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Project Manager - Panel Shop </t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>http://eganco.hrmdirect.com/employment/view.php?req=3721019</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Champlin, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>$55k-$69k/yr, $26-$33/hr</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Two-year degree or related electrical experience; bachelor’s degree preferred; strong organizational, communication, and MS Office/Google Suite skills.</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>https://eganco.com</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Multi-trade specialty contractor providing construction and building systems integration.</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>CAD, PLC, HMI, MS Office, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>2026-05-20 10:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Challenge Unlimited</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Project Manager - Custodial</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>http://challengeunlimitedinc.applytojob.com/apply/dWTLgsUHPy/Project-Manager-Custodial</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Kansas City, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>$58k-$65k/yr, $28-$31/hr</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in business or related field or 8+ years supervisory/janitorial contract management experience. Must have strong communication and leadership skills.</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>https://cuinc.org</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Provides vocational training and employment for individuals with disabilities.</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, PowerPoint, Outlook</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
         </is>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O369"/>
+  <dimension ref="A1:O372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27578,11 +27578,7 @@
           <t>Provides managed industrial maintenance and reliability services for manufacturers.</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr">
         <is>
           <t>2026-05-21 03:51:20 PM CDT</t>
@@ -28510,6 +28506,237 @@
       <c r="O369" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>SHAZAM</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>EFTI Professional Services Project Manager</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=7ec4dd6d-8d16-4303-8c2b-a76d9376f7aa&amp;jobId=545042</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Des Moines, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>$63k-$80k/yr, $30-$38/hr</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Experience in project management; banking experience preferred; strong communication; research, administration, analysis and project management skills; deadline-driven.</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>https://shazam.net</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Provides debit network and payment processing for community banks.</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:15:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>VML</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Coordinator </t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>https://www.vml.com/careers/job/8561790002?gh_jid=8561790002</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Austin, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Business Admin, Marketing, Communications, Project Management, or related field; 1–3 years client-facing or project coordination experience.</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Global agency providing creative, customer experience, and commerce services.</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:47:21 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>https://careers.umich.edu/job_detail/apply/278023</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Ann Arbor, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>$65k-$75k/yr, $31-$36/hr</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Graduate-level degree in social science, policy, or related field; experience leading research projects; familiarity with PK-12 education and policy; strong writing and data analysis skills.</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Part Time, Temporary</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>https://umich.edu</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Public research university offering undergraduate and graduate education.</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O372"/>
+  <dimension ref="A1:O383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28575,11 +28575,7 @@
           <t>Provides debit network and payment processing for community banks.</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N370" t="inlineStr"/>
       <c r="O370" t="inlineStr">
         <is>
           <t>2026-05-22 08:15:00 AM CDT</t>
@@ -28652,11 +28648,7 @@
           <t>Global agency providing creative, customer experience, and commerce services.</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N371" t="inlineStr"/>
       <c r="O371" t="inlineStr">
         <is>
           <t>2026-05-22 06:47:21 AM CDT</t>
@@ -28729,14 +28721,849 @@
           <t>Public research university offering undergraduate and graduate education.</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Tire Discounters</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/tirediscounters/cx/job-details?reqId=5001200748000</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Cincinnati, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Experience managing multiple cross-functional projects with strong communication, problem solving, and budget/timeline management; proficient with MS Office and PM software; willing for on-call weekends/evenings.</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>https://tirediscounters.com</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Retailer of tires and provider of automotive maintenance services</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Project management software</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:18:46 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Lemio</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d) for digital wellness app (iOS)</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/lemio/16195029-project-manager-m-f-d-for-digital-wellness-app-ios?pid=0a9968ed210507e82356</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Palo Alto, California, United States</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>$50k-$70k/yr, $24-$33/hr</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>2+ years experience; passion for AI tools, mental health, processes, KPIs, and A/B testing; open to various engagement types.</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Full Time, Part Time, Contract</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>https://lemioapp.com</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Mobile app that helps users manage screen time and digital habits.</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>AI tools, Claude, Code, Design, Cowork</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:24:50 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Brown Haven Homes</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Project Manager/Superintendent</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/brownhavenhomes/jobs/5144864007</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Seneca, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>2+ years in new home construction; strong leadership; site leadership across multiple sites; manage schedule, budget, and quality; physically capable (lift 80+ lbs).</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>https://brownhavenhomes.com</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Builds custom homes on land owned by customers.</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Construction software</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:27:34 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>VML MAP</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Coordinator </t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/map/jobs/8561789002</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Austin, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Business Administration, Marketing, Communications, Project Management, or related field; 1–3 years client-facing or project coordination experience; strong organizational and communication skills.</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>https://vml-map.com</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Provides marketing automation and personalized digital customer experience solutions.</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O372" t="inlineStr">
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:47:20 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>STEM Healthcare</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Strategic Engagement Manager (Project Manager)</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/stemhealthcare/jobs/7953590</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>York, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree; 1+ year STEM analysis or project coordination; end-to-end project management experience; strong communication; proficient in Excel and PowerPoint; remote work in North America.</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Full Time, Part Time, Contract, Internship, Temporary, Seasonal, Volunteer</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>https://stemhealthcare.com</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Benchmarking and audit services for global pharmaceutical companies.</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Excel, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>2026-05-22 05:00:17 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Diversified Maintenance</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Project Manager - Janitorial</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>https://diversifiedm-aus.icims.com/jobs/1598821/project-manager---janitorial/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Fountain Inn, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Three years operational janitorial experience; two years management; HS diploma; English proficiency; multitask capable; strong customer service and leadership.</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>https://diversifiedm.com</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Provides commercial janitorial and facilities maintenance services.</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>MSS Solutions</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Alarm Project Manager </t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>http://msssolutions.hrmdirect.com/employment/view.php?req=3721971</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Hanahan, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Fire Life Safety project management, NICET certification preferred; NFPA 72 knowledge; Microsoft Office; 3+ years PM or 5+ years installation experience.</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>https://msssolutions.com</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Provides mechanical construction, HVAC service, and building automation solutions.</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>UNC Health</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Project Manager Operations</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://css-unchealthunc-prd.inforcloudsuite.com/hcm/Jobs/navigation/JobPosting%5BJobPostingSet%5D(9999,226157,1).JobPostingDisplayNav?csk.HROrganization=9999&amp;csk.JobBoard=EXTERNAL</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Lenoir, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>$74k-$107k/yr, $35-$51/hr</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Direct and manage multiple projects from initiation to completion; develop plans, budgets, and schedules; coordinate with stakeholders; onsite 40 hrs/wk in NC.</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>https://unchealth.org</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Provides public healthcare and medical education in North Carolina.</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>mpathic</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Project Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://mpathic2.bamboohr.com/careers/81</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Experience in project management, operations, or delivery; strong cross-functional coordination; 3 years of experience preferred.</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>AI platform analyzing and enhancing clinical and corporate communication.</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Asana, Airtable, Notion, Trello, Slack, Google Workspace, Microsoft 365</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>University of Idaho</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>TH Water Conservation Project Coordinator - PBAC</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>https://uidaho.peopleadmin.com/postings/51609</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Moscow, Idaho, United States</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>$39k-$39k/yr, $19-$19/hr</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>HS diploma or equivalent; 18+; strong communication; reliable; willing to learn; travel to sites; MS Office; driver’s license.</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>https://uidaho.edu</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Microsoft Office Suite, Word, Excel</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>McKenney's</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>http://mckenneys.applytojob.com/apply/KFDI2pQvYh/Construction-Project-Manager</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Lead large-scale construction projects, coordinate multidisciplinary teams, manage budgets, safety, and quality.</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>https://mckenneys.com</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Mechanical contractor providing HVAC, plumbing, and building automation services.</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Cost accounting software, Project scheduling tools</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O383"/>
+  <dimension ref="A1:O386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29025,11 +29025,7 @@
           <t>Provides marketing automation and personalized digital customer experience solutions.</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr">
         <is>
           <t>2026-05-22 06:47:20 AM CDT</t>
@@ -29179,11 +29175,7 @@
           <t>Provides commercial janitorial and facilities maintenance services.</t>
         </is>
       </c>
-      <c r="N378" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr">
         <is>
           <t>2026-05-21 11:00:00 PM CDT</t>
@@ -29333,11 +29325,7 @@
           <t>Provides public healthcare and medical education in North Carolina.</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
@@ -29564,6 +29552,237 @@
       <c r="O383" t="inlineStr">
         <is>
           <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>McGraw Hill</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - K12 International Projects</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>https://careers.mheducation.com/jobs/6662?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>$80k-$100k/yr, $38-$48/hr</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>3–5+ years in project management; edtech/k-12 experience preferred; PMP preferred; ability to lead end-to-end projects; strong communication; BS degree.</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>https://mheducation.com</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Provides digital learning solutions and educational content.</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Smartsheet, MS Project</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:45:04 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>GovCIO</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Project Coordinator 1</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>https://careers.govcio.com/careers-home/jobs/8211?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Martinsburg, West Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>$46k-$74k/yr, $22-$35/hr</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Bachelor's degree with 0-2 years of experience; ability to pass Tier 4 background investigation; onsite work required; knowledge of Power BI is a plus.</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>https://govcio.com</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Provides technology and mission support services to federal agencies.</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Microsoft Power BI</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:04:50 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>AIR Control Concepts</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>HVAC Service Project Manager</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>http://aircontrolconcepts.applytojob.com/apply/3JDUiT8J7s/HVAC-Service-Project-Manager</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Elkridge, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>$60k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Experience in project management or service coordination; strong communication and organizational skills; familiar with PM software.</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>https://aircontrolconcepts.com</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Commercial HVAC equipment distribution and engineering services provider.</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Trello, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O386"/>
+  <dimension ref="A1:O392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29786,6 +29786,468 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Project Manager, Construction</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>https://careers.thearcoway.com/jobs/11413?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Canton, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>BS in Construction, Engineering, Architecture or related field; 3.0+ GPA; 3-5 years design/build construction with GC; cold storage experience preferred; proficient in Word, Excel, Outlook, MS Project.</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Nationwide design-build construction firm specializing in industrial facilities.</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft Outlook, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:51:16 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Project Manager, Construction</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>https://careers.thearcoway.com/jobs/11409?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Riverside, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>BS in Construction, Engineering, Architecture or related field; 3-5 years' design/build construction experience; cold storage experience preferred; proficiency with Word, Excel, Outlook, and Microsoft Project.</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Nationwide design-build construction firm specializing in industrial facilities.</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Word, Excel, Outlook</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:04:16 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Project Manager, Government Services</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>https://careers.thearcoway.com/jobs/11410?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Riverside, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>BS in Construction, Engineering, Architecture with 3.0 GPA; 3-5 years design/build construction with GC; cold storage experience preferred; proficiency in Word, Excel, Outlook, and MS Project.</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Nationwide design-build construction firm specializing in industrial facilities.</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Word, Excel, Outlook, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:04:16 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>ECS Limited</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Environmental Project Manager</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>https://careers.ecslimited.com/jobs/38058?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Tampa, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Bachelor's or Master's in Civil/Environmental Engineering or related field; minimum 2 years of experience; PE or PG license preferred.</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>https://ecslimited.com</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Provides geotechnical, environmental, and facilities engineering consulting services.</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:03:41 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ECS Limited</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Construction Materials Project Manager</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>https://careers.ecslimited.com/jobs/38056?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Carrollton, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Bachelor's in Civil/Construction Eng, Materials Science, Architectural Eng, or Geology; 2+ years experience; valid driver’s license; PE or PG license in work state; strong client relations, communication, safety knowledge, and CMT/ASTM knowledge.</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>https://ecslimited.com</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Provides geotechnical, environmental, and facilities engineering consulting services.</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:03:44 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Zantech</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Secret Cleared Project Manager</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>https://zantech-it.breezy.hr/p/b120651725d1-secret-cleared-project-manager</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Mobile, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>4+ years in project management; 5+ years in related program/support roles; knowledge of ship construction and government contracting; proficient in MS Word/Excel/PowerPoint/SharePoint/Outlook; English fluency; 0900-1700 CST availability.</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>https://zantechit.com</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Provides technology and cybersecurity solutions to federal government agencies.</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, SharePoint, Microsoft Outlook</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:12:13 AM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O599"/>
+  <dimension ref="A1:O638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30241,11 +30241,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
           <t>Project Manager II or III</t>
@@ -30296,21 +30292,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N393" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
       <c r="O393" t="inlineStr">
         <is>
           <t>2026-05-22 02:48:01 PM CDT</t>
@@ -30318,11 +30302,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
           <t>Project Manager - Structural</t>
@@ -30373,16 +30353,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M394" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr">
         <is>
           <t>Construction Management Software, Microsoft Office</t>
@@ -30395,11 +30367,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -30450,21 +30418,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr">
         <is>
           <t>2026-05-22 02:47:49 PM CDT</t>
@@ -30472,11 +30428,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
           <t>Assistant Project Manager | Municipal &amp; Water Resources</t>
@@ -30527,16 +30479,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr">
         <is>
           <t>AutoCAD Civil 3D, HydroCAD, Hydraflow Storm Sewers, Microsoft Office, Project Management Software</t>
@@ -30549,11 +30493,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
           <t>Assistant Project Manager | Municipal &amp; Water Resources</t>
@@ -30604,16 +30544,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr">
         <is>
           <t>AutoCAD Civil 3D, HydroCAD, Hydraflow Storm Sewers, Microsoft Office</t>
@@ -30626,11 +30558,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -30681,16 +30609,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr">
         <is>
           <t>Microsoft Office, BIM, PMIS, Construction software</t>
@@ -30703,11 +30623,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
           <t>Project Coordinator, Clinical &amp; Grant-Funded Programs</t>
@@ -30758,21 +30674,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N399" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
       <c r="O399" t="inlineStr">
         <is>
           <t>2026-05-22 02:44:50 PM CDT</t>
@@ -30780,11 +30684,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -30835,16 +30735,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr">
         <is>
           <t>Comsense, DFH Software, Microsoft Office, CAD, Adobe, Blueprints Reading</t>
@@ -30857,11 +30749,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
           <t>Project Coordinator - Sterling Heights</t>
@@ -30912,21 +30800,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N401" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr">
         <is>
           <t>2026-05-22 02:44:49 PM CDT</t>
@@ -30934,11 +30810,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
           <t>Assistant Project Manager - Commercial Construction</t>
@@ -30989,16 +30861,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr">
         <is>
           <t>Procore, Microsoft Project, Primavera P6</t>
@@ -31011,11 +30875,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
           <t>Project Manager - Commercial Construction</t>
@@ -31066,16 +30926,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr">
         <is>
           <t>Procore, Microsoft Project, Building Connected</t>
@@ -31088,11 +30940,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
           <t>Assistant Project Manager - Commercial Construction</t>
@@ -31143,16 +30991,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr">
         <is>
           <t>Procore, Microsoft Project, Primavera P6</t>
@@ -31165,11 +31005,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
@@ -31220,21 +31056,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N405" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr">
         <is>
           <t>2026-05-22 02:43:44 PM CDT</t>
@@ -31242,11 +31066,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -31297,16 +31117,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr">
         <is>
           <t>CRM system</t>
@@ -31319,11 +31131,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
           <t>Contract Construction Project Manager</t>
@@ -31374,21 +31182,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
       <c r="O407" t="inlineStr">
         <is>
           <t>2026-05-22 02:43:38 PM CDT</t>
@@ -31396,11 +31192,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
           <t>Project Manager - CSST and CDPH at minimum</t>
@@ -31451,21 +31243,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N408" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
       <c r="O408" t="inlineStr">
         <is>
           <t>2026-05-22 02:43:38 PM CDT</t>
@@ -31473,11 +31253,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
           <t>Project Manager - CSST and CDPH at minimum</t>
@@ -31528,21 +31304,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M409" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N409" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
       <c r="O409" t="inlineStr">
         <is>
           <t>2026-05-22 02:43:38 PM CDT</t>
@@ -31550,11 +31314,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
           <t>Project Manager - CSST and CDPH at minimum</t>
@@ -31605,21 +31365,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
       <c r="O410" t="inlineStr">
         <is>
           <t>2026-05-22 02:43:38 PM CDT</t>
@@ -31627,11 +31375,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -31682,16 +31426,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr">
         <is>
           <t>Kudu, Office 365, Adobe</t>
@@ -31704,11 +31440,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
           <t>Project Manager- Government Projects</t>
@@ -31759,16 +31491,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr">
         <is>
           <t>Microsoft Office, AutoCAD</t>
@@ -31781,11 +31505,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -31836,16 +31556,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr">
         <is>
           <t>Microsoft Office, AutoCAD, Microsoft Project</t>
@@ -31858,11 +31570,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
           <t>Project Manager - Lotis - Lake Orion</t>
@@ -31913,16 +31621,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr">
         <is>
           <t>ERP, Project management software, Budgeting tools</t>
@@ -31935,11 +31635,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
           <t>Project Manager - Lotis - Bay City</t>
@@ -31990,16 +31686,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr">
         <is>
           <t>ERP, Project Management Software</t>
@@ -32012,11 +31700,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
           <t>Facility Assistant Project Manager – Janitorial Services</t>
@@ -32067,16 +31751,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft Outlook</t>
@@ -32089,11 +31765,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
           <t>Project Manager (Manufacturing)</t>
@@ -32144,16 +31816,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
       <c r="N417" t="inlineStr">
         <is>
           <t>Microsoft Office, Project Management Software, Gantt Charts</t>
@@ -32166,11 +31830,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -32221,16 +31881,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
       <c r="N418" t="inlineStr">
         <is>
           <t>Microsoft Office, ERP, ATS, CRM, Project management software</t>
@@ -32243,11 +31895,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
           <t>New Product Project Manager</t>
@@ -32298,16 +31946,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr">
         <is>
           <t>Microsoft Office, Project scheduling tools</t>
@@ -32320,11 +31960,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -32375,16 +32011,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr">
         <is>
           <t>AutoCAD, Revit, Orca</t>
@@ -32397,11 +32025,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -32452,16 +32076,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr">
         <is>
           <t>Procore</t>
@@ -32474,11 +32090,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
           <t>Website Project Coordinator</t>
@@ -32529,16 +32141,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M422" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr">
         <is>
           <t>WordPress, Google Analytics, Google Search Console, HTML, CSS, JavaScript, Zendesk, Facebook Business Manager, Google Business Profile</t>
@@ -32551,11 +32155,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -32606,16 +32206,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M423" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr">
         <is>
           <t>Crestron, Lutron, Savant</t>
@@ -32628,11 +32220,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -32683,16 +32271,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M424" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
       <c r="N424" t="inlineStr">
         <is>
           <t>Envisio, Project Management Software</t>
@@ -32705,11 +32285,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -32760,16 +32336,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M425" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
       <c r="N425" t="inlineStr">
         <is>
           <t>Project Management Software</t>
@@ -32782,11 +32350,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -32837,16 +32401,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M426" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr">
         <is>
           <t>MS Project, Microsoft Planner, LMS, SCORM</t>
@@ -32859,11 +32415,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -32914,16 +32466,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M427" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr">
         <is>
           <t>Earned Value Management, Budgeting, Cost management</t>
@@ -32936,11 +32480,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -32991,21 +32531,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N428" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
       <c r="O428" t="inlineStr">
         <is>
           <t>2026-05-22 02:39:14 PM CDT</t>
@@ -33013,11 +32541,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -33068,16 +32592,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
       <c r="N429" t="inlineStr">
         <is>
           <t>Identity and Access Management, Information Security, Project Management</t>
@@ -33090,11 +32606,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -33145,16 +32657,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M430" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
       <c r="N430" t="inlineStr">
         <is>
           <t>Microsoft Office, Project management tools</t>
@@ -33167,11 +32671,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -33222,16 +32722,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
       <c r="N431" t="inlineStr">
         <is>
           <t>Microsoft Office, Excel, Word, Outlook</t>
@@ -33244,11 +32736,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
           <t>Project Manager - Cyber</t>
@@ -33299,21 +32787,9 @@
           <t>Full Time, Contract</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N432" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr"/>
       <c r="O432" t="inlineStr">
         <is>
           <t>2026-05-22 02:38:40 PM CDT</t>
@@ -33321,11 +32797,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
           <t>New Centers Project Manager (DFW)</t>
@@ -33376,16 +32848,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
       <c r="N433" t="inlineStr">
         <is>
           <t>Asana</t>
@@ -33398,11 +32862,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
           <t>Project Manager of IC Development</t>
@@ -33453,16 +32913,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr">
         <is>
           <t>EDA tools, silicon development workflows, project management tools</t>
@@ -33475,11 +32927,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
           <t>Assistant Project Manager - HVAC</t>
@@ -33530,16 +32978,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr">
         <is>
           <t>Procore, Autodesk BIM 360, Bluebeam, Microsoft Excel, Microsoft Project, Microsoft Word</t>
@@ -33552,11 +32992,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
           <t>Assistant Project Manager - HVAC</t>
@@ -33607,16 +33043,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr">
         <is>
           <t>Procore, Autodesk BIM 360, Bluebeam, Microsoft Office, Project</t>
@@ -33629,11 +33057,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
           <t>Service Retrofit Project Coordinator I - HVAC</t>
@@ -33684,16 +33108,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M437" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
       <c r="N437" t="inlineStr">
         <is>
           <t>Microsoft Office Suite</t>
@@ -33706,11 +33122,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
           <t>Assistant Project Manager - HVAC</t>
@@ -33761,16 +33173,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
       <c r="N438" t="inlineStr">
         <is>
           <t>Microsoft Office, Procore, Autodesk BIM 360, Bluebeam</t>
@@ -33783,11 +33187,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
           <t>Commissioning Engineer Project Manager</t>
@@ -33838,16 +33238,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
       <c r="N439" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Word, Microsoft Excel, Outlook</t>
@@ -33860,11 +33252,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
           <t>Commissioning Engineer Project Manager</t>
@@ -33915,16 +33303,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M440" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
       <c r="N440" t="inlineStr">
         <is>
           <t>Microsoft Office</t>
@@ -33937,11 +33317,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
           <t>Fire Alarm Project Manager</t>
@@ -33992,16 +33368,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M441" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
       <c r="N441" t="inlineStr">
         <is>
           <t>Project Management Software</t>
@@ -34014,11 +33382,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
           <t>Fire Alarm Project Manager</t>
@@ -34069,16 +33433,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
       <c r="N442" t="inlineStr">
         <is>
           <t>Project management software, Microsoft Excel</t>
@@ -34091,11 +33447,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
           <t>Fire Alarm Project Manager</t>
@@ -34146,16 +33498,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M443" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
       <c r="N443" t="inlineStr">
         <is>
           <t>Procore, Salesforce</t>
@@ -34168,11 +33512,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
           <t>Fire Alarm Project Manager</t>
@@ -34223,16 +33563,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
       <c r="N444" t="inlineStr">
         <is>
           <t>Procore, Salesforce</t>
@@ -34245,11 +33577,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -34300,16 +33628,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
       <c r="N445" t="inlineStr">
         <is>
           <t>Microsoft Office</t>
@@ -34322,11 +33642,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
           <t>Division 8 Project Coordinator</t>
@@ -34377,16 +33693,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
       <c r="N446" t="inlineStr">
         <is>
           <t>MS Office, Outlook, NAVISION, PROTECH</t>
@@ -34399,11 +33707,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
           <t>Mechanical Project Manager - RoyalAire Mechanical</t>
@@ -34454,16 +33758,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
       <c r="N447" t="inlineStr">
         <is>
           <t>Microsoft Office, MS Project, PlanGrid, Bluebeam</t>
@@ -34476,11 +33772,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
           <t>Project Manager/Engineer - Water Treatment</t>
@@ -34531,16 +33823,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
       <c r="N448" t="inlineStr">
         <is>
           <t>AutoCAD Civil 3D, Primavera P6, Microsoft Project, Microsoft Excel, Microsoft Word, Microsoft Outlook, Microsoft Teams</t>
@@ -34553,11 +33837,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
           <t>Project Manager/Engineer - Water Treatment</t>
@@ -34608,16 +33888,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M449" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
       <c r="N449" t="inlineStr">
         <is>
           <t>AutoCAD Civil 3D, Primavera P6, Microsoft Project, Excel, Word, Outlook, Teams</t>
@@ -34630,11 +33902,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
           <t>Project Manager/Engineer - Water Treatment</t>
@@ -34685,16 +33953,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
       <c r="N450" t="inlineStr">
         <is>
           <t>AutoCAD Civil 3D, Primavera P6, Microsoft Project, Excel, Word, Outlook, Teams</t>
@@ -34707,11 +33967,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -34762,16 +34018,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M451" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
       <c r="N451" t="inlineStr">
         <is>
           <t>Email, Spreadsheets, Documents</t>
@@ -34784,11 +34032,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
           <t>Assistant Project Manager - Commercial</t>
@@ -34839,16 +34083,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
       <c r="N452" t="inlineStr">
         <is>
           <t>Microsoft Office, Accounting software</t>
@@ -34861,11 +34097,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -34916,16 +34148,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M453" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
       <c r="N453" t="inlineStr">
         <is>
           <t>Google Analytics, Monday.com, Hubspot</t>
@@ -34938,11 +34162,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -34993,16 +34213,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
       <c r="N454" t="inlineStr">
         <is>
           <t>Microsoft Office, ERP, CRM</t>
@@ -35015,11 +34227,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
           <t>Project Manager, Lighting controls</t>
@@ -35070,16 +34278,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
       <c r="N455" t="inlineStr">
         <is>
           <t>Microsoft Office, ERP/CRM, Lutron, Crestron, Q-Sys, Biamp</t>
@@ -35092,11 +34292,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
           <t>Project Manager/Community Playspace Build Manager</t>
@@ -35147,21 +34343,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N456" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
       <c r="O456" t="inlineStr">
         <is>
           <t>2026-05-22 02:33:15 PM CDT</t>
@@ -35169,11 +34353,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -35224,16 +34404,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
       <c r="N457" t="inlineStr">
         <is>
           <t>Microsoft Project, Microsoft Office</t>
@@ -35246,11 +34418,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
           <t>Drupal Upgrade Project Manager</t>
@@ -35301,16 +34469,8 @@
           <t>Contract</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M458" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
       <c r="N458" t="inlineStr">
         <is>
           <t>Jira, Drupal, OpenScholar, Agile</t>
@@ -35323,11 +34483,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
           <t>M&amp;A Site Activation Project Manager</t>
@@ -35378,16 +34534,8 @@
           <t>Contract</t>
         </is>
       </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
       <c r="N459" t="inlineStr">
         <is>
           <t>Epic, EHR, Healthcare IT</t>
@@ -35400,11 +34548,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
           <t>Executive Project Manager</t>
@@ -35455,16 +34599,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M460" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
       <c r="N460" t="inlineStr">
         <is>
           <t>Google Drive, Microsoft Office</t>
@@ -35477,11 +34613,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
           <t>Construction Project Manager</t>
@@ -35532,16 +34664,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
       <c r="N461" t="inlineStr">
         <is>
           <t>Microsoft Project, Microsoft Office, Bluebeam, Construction management software</t>
@@ -35554,11 +34678,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
           <t>Social Media and Marketing Project Manager</t>
@@ -35609,16 +34729,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
       <c r="N462" t="inlineStr">
         <is>
           <t>Meta Business Suite, Facebook Ads Manager, ClickUp, Asana, Monday.com, Google Workspace, Microsoft Office, Adobe Creative Cloud</t>
@@ -35631,11 +34743,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
           <t>Project Manager II (HVAC Multifamily)</t>
@@ -35686,16 +34794,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
       <c r="N463" t="inlineStr">
         <is>
           <t>SAGE CRE</t>
@@ -35708,11 +34808,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -35763,16 +34859,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
       <c r="N464" t="inlineStr">
         <is>
           <t>CMMS</t>
@@ -35785,11 +34873,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -35840,16 +34924,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
       <c r="N465" t="inlineStr">
         <is>
           <t>MS Project, ERP systems</t>
@@ -35862,11 +34938,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
           <t>Commercial Landscape - Project Manager</t>
@@ -35917,16 +34989,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M466" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
       <c r="N466" t="inlineStr">
         <is>
           <t>Salesforce, Microsoft Office, Project Management Software, Photoshop, Adobe Creative Suite, AutoCAD, ProLandscape</t>
@@ -35939,11 +35003,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
           <t>Project Manager II</t>
@@ -35994,16 +35054,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M467" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
       <c r="N467" t="inlineStr">
         <is>
           <t>ERP, Microsoft Office, Project</t>
@@ -36016,11 +35068,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
           <t>Project Manager - Commercial Paint(required)</t>
@@ -36071,16 +35119,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M468" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
       <c r="N468" t="inlineStr">
         <is>
           <t>Planswift, Procore, BuildingConnected, Plan Grid, Microsoft Office</t>
@@ -36093,11 +35133,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
           <t>Project Manager - Commercial Flooring Coating (epoxy, resinous etc....)</t>
@@ -36148,16 +35184,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M469" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
       <c r="N469" t="inlineStr">
         <is>
           <t>Planswift, Procore, BuildingConnected, Plan Grid, MS Office Suite</t>
@@ -36170,11 +35198,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
           <t>Project Manager - Commercial Paint(required)</t>
@@ -36225,16 +35249,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M470" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
       <c r="N470" t="inlineStr">
         <is>
           <t>Planswift, Procore, BuildingConnected, PlanGrid, MS Office</t>
@@ -36247,11 +35263,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
           <t>Project Manager - Commercial Construction</t>
@@ -36302,16 +35314,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M471" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
       <c r="N471" t="inlineStr">
         <is>
           <t>Planswift, Procore, BuildingConnected, PlanGrid, MS Office</t>
@@ -36324,11 +35328,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
           <t>DOJ - Project Coordinator</t>
@@ -36379,16 +35379,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M472" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
       <c r="N472" t="inlineStr">
         <is>
           <t>Microsoft Office</t>
@@ -36401,11 +35393,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
           <t>Transaction &amp; Project Coordinator</t>
@@ -36456,16 +35444,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M473" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
       <c r="N473" t="inlineStr">
         <is>
           <t>Microsoft Office, Juniper Square, CrowdStreet</t>
@@ -36478,11 +35458,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
           <t>Project Manager (Field / Construction / Environmental)</t>
@@ -36533,21 +35509,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M474" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N474" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="inlineStr"/>
       <c r="O474" t="inlineStr">
         <is>
           <t>2026-05-22 02:29:28 PM CDT</t>
@@ -36555,11 +35519,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
           <t>Sales Project Coordinator</t>
@@ -36610,16 +35570,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M475" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
       <c r="N475" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, CRM</t>
@@ -36632,11 +35584,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
           <t>CCBHC Implementation Project Manager</t>
@@ -36687,16 +35635,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M476" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
       <c r="N476" t="inlineStr">
         <is>
           <t>EHR, data reporting platforms</t>
@@ -36709,11 +35649,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
           <t>Construction Project Manager</t>
@@ -36764,21 +35700,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M477" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N477" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="inlineStr"/>
       <c r="O477" t="inlineStr">
         <is>
           <t>2026-05-22 02:28:41 PM CDT</t>
@@ -36786,11 +35710,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
           <t>Project Manager, Industrial Self-Perform</t>
@@ -36841,16 +35761,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M478" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
       <c r="N478" t="inlineStr">
         <is>
           <t>construction management software</t>
@@ -36863,11 +35775,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
           <t>Commercial Operations Project Coordinator</t>
@@ -36918,16 +35826,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M479" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
       <c r="N479" t="inlineStr">
         <is>
           <t>HubSpot, Airtable, Google Drive</t>
@@ -36940,11 +35840,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
           <t>Electrical Engineer III / Electrical MEP Project Manager</t>
@@ -36995,16 +35891,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M480" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
       <c r="N480" t="inlineStr">
         <is>
           <t>AutoCAD, Revit, Microsoft Word, Microsoft Excel, Outlook, Teams</t>
@@ -37017,11 +35905,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
           <t>Electrical Engineer III / Electrical MEP Project Manager</t>
@@ -37072,16 +35956,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M481" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
       <c r="N481" t="inlineStr">
         <is>
           <t>AutoCAD, Revit, Microsoft Office</t>
@@ -37094,11 +35970,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -37149,16 +36021,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M482" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
       <c r="N482" t="inlineStr">
         <is>
           <t>Microsoft Office, Presentation software</t>
@@ -37171,11 +36035,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -37226,16 +36086,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M483" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
       <c r="N483" t="inlineStr">
         <is>
           <t>Newforma, Submittal Exchange, Procore, OptCenter, Outlook</t>
@@ -37248,11 +36100,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
           <t>Project Manager I</t>
@@ -37303,16 +36151,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M484" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
       <c r="N484" t="inlineStr">
         <is>
           <t>Project management software</t>
@@ -37325,11 +36165,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
           <t>Project Manager - Airports</t>
@@ -37380,21 +36216,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M485" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N485" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="inlineStr"/>
       <c r="O485" t="inlineStr">
         <is>
           <t>2026-05-22 02:28:09 PM CDT</t>
@@ -37402,11 +36226,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -37457,16 +36277,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M486" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
       <c r="N486" t="inlineStr">
         <is>
           <t>Procore, Microsoft Project, Microsoft Office Suite</t>
@@ -37479,11 +36291,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
           <t>Trade Show Project Manager</t>
@@ -37534,16 +36342,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
       <c r="N487" t="inlineStr">
         <is>
           <t>Microsoft Office, Project management software</t>
@@ -37556,11 +36356,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
           <t>Project Manager-Warehousing</t>
@@ -37611,16 +36407,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
       <c r="N488" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Excel, Design tool</t>
@@ -37633,11 +36421,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
           <t>Engineering Project Manager</t>
@@ -37688,16 +36472,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M489" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
       <c r="N489" t="inlineStr">
         <is>
           <t>AutoCAD, ArcGIS, AutoTURN, Microsoft Office, Drone operations, Vehicle tracking</t>
@@ -37710,11 +36486,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -37765,16 +36537,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M490" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
       <c r="N490" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, Excel</t>
@@ -37787,11 +36551,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -37842,16 +36602,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M491" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
       <c r="N491" t="inlineStr">
         <is>
           <t>MS Office, ERP, Blueprints reading</t>
@@ -37864,11 +36616,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -37919,16 +36667,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M492" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
       <c r="N492" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft Outlook</t>
@@ -37941,11 +36681,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
           <t>Environmental Project Manager</t>
@@ -37996,21 +36732,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M493" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N493" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
       <c r="O493" t="inlineStr">
         <is>
           <t>2026-05-22 02:27:33 PM CDT</t>
@@ -38018,11 +36742,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -38073,16 +36793,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M494" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
       <c r="N494" t="inlineStr">
         <is>
           <t>Microsoft Office, Project Management tools</t>
@@ -38095,11 +36807,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
           <t>Electrical Project Manager</t>
@@ -38150,16 +36858,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M495" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
       <c r="N495" t="inlineStr">
         <is>
           <t>Microsoft Office</t>
@@ -38172,11 +36872,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
           <t>AV Project Manager</t>
@@ -38227,16 +36923,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M496" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
       <c r="N496" t="inlineStr">
         <is>
           <t>Procore, Smartsheet, Bluebeam, Autodesk, Microsoft Excel, Microsoft Office</t>
@@ -38249,11 +36937,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
           <t>AV Project Manager</t>
@@ -38304,16 +36988,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
       <c r="N497" t="inlineStr">
         <is>
           <t>Bluebeam, Smartsheet, Procore, Autodesk, Microsoft Excel, Microsoft Office</t>
@@ -38326,11 +37002,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
           <t>Technical Project Manager</t>
@@ -38381,16 +37053,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
       <c r="N498" t="inlineStr">
         <is>
           <t>PMP, Gantt charts, Work breakdown structure</t>
@@ -38403,11 +37067,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
           <t>Engineering Project Manager</t>
@@ -38458,21 +37118,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr"/>
       <c r="O499" t="inlineStr">
         <is>
           <t>2026-05-22 02:26:58 PM CDT</t>
@@ -38480,11 +37128,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
           <t>Technical Project Manager</t>
@@ -38535,16 +37179,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M500" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
       <c r="N500" t="inlineStr">
         <is>
           <t>Microsoft Power Apps, Microsoft Power Automate, Power BI, Microsoft Azure, Agile</t>
@@ -38557,11 +37193,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
           <t>Project Manager – Data &amp; Business Transformation</t>
@@ -38612,16 +37244,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M501" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
       <c r="N501" t="inlineStr">
         <is>
           <t>Jira, Smartsheet, MS Project, Asana, SharePoint, Teams, Confluence, Microsoft Excel, PowerPoint, Power BI, Tableau</t>
@@ -38634,11 +37258,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
           <t>Project Manager (Mid-Senior) – Data &amp; Business Transformation</t>
@@ -38689,16 +37309,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L502" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M502" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
       <c r="N502" t="inlineStr">
         <is>
           <t>Jira, Smartsheet, MS Project, Asana, Confluence, SharePoint, Microsoft Teams, Microsoft Excel, PowerPoint, Power BI, Tableau, Power Apps, Power Automate, SAP, AVEVA</t>
@@ -38711,11 +37323,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -38766,16 +37374,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L503" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M503" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
       <c r="N503" t="inlineStr">
         <is>
           <t>Word, Excel, Outlook</t>
@@ -38788,11 +37388,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
           <t>Internship : Project Engineer/Project Manager</t>
@@ -38843,16 +37439,8 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="L504" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M504" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
       <c r="N504" t="inlineStr">
         <is>
           <t>Word, Excel, Outlook</t>
@@ -38865,11 +37453,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -38920,16 +37504,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L505" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M505" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
       <c r="N505" t="inlineStr">
         <is>
           <t>construction project management software</t>
@@ -38942,11 +37518,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -38997,16 +37569,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M506" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
       <c r="N506" t="inlineStr">
         <is>
           <t>construction project management software</t>
@@ -39019,11 +37583,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -39074,21 +37634,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L507" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M507" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N507" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr"/>
       <c r="O507" t="inlineStr">
         <is>
           <t>2026-05-22 02:26:17 PM CDT</t>
@@ -39096,11 +37644,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
           <t>Project Coordinator (2nd/3rd Shift)</t>
@@ -39151,16 +37695,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M508" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
       <c r="N508" t="inlineStr">
         <is>
           <t>Microsoft Office, G-Suite, Salesforce</t>
@@ -39173,11 +37709,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
           <t>Assistant Project Manager (2nd/3rd Shift)</t>
@@ -39228,16 +37760,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L509" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M509" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
       <c r="N509" t="inlineStr">
         <is>
           <t>Microsoft Office, G-Suite, Salesforce, Service management system</t>
@@ -39250,11 +37774,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
           <t>Project Manager – Public Safety (Westchester, IL)</t>
@@ -39305,21 +37825,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L510" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M510" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N510" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr"/>
       <c r="O510" t="inlineStr">
         <is>
           <t>2026-05-22 02:26:09 PM CDT</t>
@@ -39327,11 +37835,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
           <t>Project Manager East TN</t>
@@ -39382,16 +37886,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L511" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M511" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
       <c r="N511" t="inlineStr">
         <is>
           <t>Buildertrend</t>
@@ -39404,11 +37900,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
           <t>Reconstruction Project Manager</t>
@@ -39459,21 +37951,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L512" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M512" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N512" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr"/>
       <c r="O512" t="inlineStr">
         <is>
           <t>2026-05-22 02:25:56 PM CDT</t>
@@ -39481,11 +37961,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -39536,16 +38012,8 @@
           <t>Contract</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M513" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
       <c r="N513" t="inlineStr">
         <is>
           <t>Project Management Software, Digital communication tools</t>
@@ -39558,11 +38026,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -39613,16 +38077,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M514" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
       <c r="N514" t="inlineStr">
         <is>
           <t>Microsoft Outlook, Microsoft Word, Microsoft Excel, AutoCAD</t>
@@ -39635,11 +38091,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
           <t>Learning and Development Coordinator</t>
@@ -39690,16 +38142,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M515" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
       <c r="N515" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Office</t>
@@ -39712,11 +38156,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -39767,16 +38207,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M516" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
       <c r="N516" t="inlineStr">
         <is>
           <t>Google Suite, Project management software</t>
@@ -39789,11 +38221,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
           <t>Project Manager, External Affairs, Detroit</t>
@@ -39844,21 +38272,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L517" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M517" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N517" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr"/>
       <c r="O517" t="inlineStr">
         <is>
           <t>2026-05-22 02:24:19 PM CDT</t>
@@ -39866,11 +38282,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
           <t>Scheduler - Dispatcher - Project Coordinator</t>
@@ -39921,21 +38333,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L518" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M518" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N518" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr"/>
       <c r="O518" t="inlineStr">
         <is>
           <t>2026-05-22 02:23:36 PM CDT</t>
@@ -39943,11 +38343,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
           <t>Technical Project Coordinator</t>
@@ -39998,16 +38394,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L519" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M519" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
       <c r="N519" t="inlineStr">
         <is>
           <t>Monday.com, Microsoft Word, Microsoft Excel</t>
@@ -40020,11 +38408,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
           <t>Corrosion Control Project Manager (Job ID : 4205)</t>
@@ -40075,16 +38459,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M520" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
       <c r="N520" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Microsoft Project</t>
@@ -40097,11 +38473,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
           <t>Corrosion Control Project Manager (Job ID : 4210)</t>
@@ -40152,16 +38524,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L521" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M521" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
       <c r="N521" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Microsoft Project, NAVSEA Instructions</t>
@@ -40174,11 +38538,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
           <t>Corrosion Control Project Manager (Job ID : 4263)</t>
@@ -40229,16 +38589,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M522" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
       <c r="N522" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Microsoft Project, NAVSEA Instructions</t>
@@ -40251,11 +38603,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
           <t>Electrical Project Manager</t>
@@ -40306,16 +38654,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L523" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M523" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
       <c r="N523" t="inlineStr">
         <is>
           <t>Accubid estimating software, Microsoft Office, Project management software</t>
@@ -40328,11 +38668,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
           <t>Electrical Project Manager</t>
@@ -40383,16 +38719,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M524" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
       <c r="N524" t="inlineStr">
         <is>
           <t>MS Office, Estimating software, Project management software, Accubid</t>
@@ -40405,11 +38733,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -40460,16 +38784,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M525" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
       <c r="N525" t="inlineStr">
         <is>
           <t>Microsoft Office, MS Project, Project Management Software</t>
@@ -40482,11 +38798,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -40537,16 +38849,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L526" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M526" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
       <c r="N526" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, Adobe Acrobat, Newforma, AIA Software (MasterSpecs), Adobe InDesign, UPS Software</t>
@@ -40559,11 +38863,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
           <t>PROJECT MANAGER</t>
@@ -40614,16 +38914,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M527" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
       <c r="N527" t="inlineStr">
         <is>
           <t>Microsoft Office, Project management software</t>
@@ -40636,11 +38928,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
           <t>Project Manager - Print</t>
@@ -40691,16 +38979,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M528" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
       <c r="N528" t="inlineStr">
         <is>
           <t>Microsoft Office, Enterprise 32</t>
@@ -40713,11 +38993,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -40768,16 +39044,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M529" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
       <c r="N529" t="inlineStr">
         <is>
           <t>Microsoft Office Suite</t>
@@ -40790,11 +39058,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
           <t>IT Project Coordinator</t>
@@ -40845,16 +39109,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M530" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
       <c r="N530" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, Atlassian Suite, Elastic, ServiceNow</t>
@@ -40867,11 +39123,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
           <t>Survey Project Manager- Energy</t>
@@ -40922,16 +39174,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
       <c r="N531" t="inlineStr">
         <is>
           <t>Microsoft Office, AutoCAD</t>
@@ -40944,11 +39188,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -40999,21 +39239,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M532" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N532" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr"/>
       <c r="O532" t="inlineStr">
         <is>
           <t>2026-05-22 02:21:43 PM CDT</t>
@@ -41021,11 +39249,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
           <t>Technical Project Manager</t>
@@ -41076,16 +39300,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M533" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
       <c r="N533" t="inlineStr">
         <is>
           <t>Microsoft Office, Panda application, PMAL</t>
@@ -41098,11 +39314,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
           <t>Project Manager / Service Delivery Manager</t>
@@ -41153,16 +39365,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M534" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
       <c r="N534" t="inlineStr">
         <is>
           <t>ITIL, MCITP, PMP, Six Sigma Black Belt</t>
@@ -41175,11 +39379,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -41230,21 +39430,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L535" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M535" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N535" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="inlineStr"/>
       <c r="O535" t="inlineStr">
         <is>
           <t>2026-05-22 02:21:28 PM CDT</t>
@@ -41252,11 +39440,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -41307,16 +39491,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L536" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M536" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
       <c r="N536" t="inlineStr">
         <is>
           <t>Microsoft Office</t>
@@ -41329,11 +39505,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -41384,16 +39556,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L537" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M537" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
       <c r="N537" t="inlineStr">
         <is>
           <t>Microsoft Office</t>
@@ -41406,11 +39570,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
           <t>Division 10 Project Manager</t>
@@ -41461,21 +39621,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M538" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N538" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="inlineStr"/>
       <c r="O538" t="inlineStr">
         <is>
           <t>2026-05-22 02:21:26 PM CDT</t>
@@ -41483,11 +39631,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
           <t>Exterior Project Manager</t>
@@ -41538,21 +39682,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M539" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N539" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="inlineStr"/>
       <c r="O539" t="inlineStr">
         <is>
           <t>2026-05-22 02:21:26 PM CDT</t>
@@ -41560,11 +39692,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
           <t>Motorcycle Mechanic &amp; Project Manager</t>
@@ -41615,16 +39743,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M540" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
       <c r="N540" t="inlineStr">
         <is>
           <t>Diagnostic tools, Computer</t>
@@ -41637,11 +39757,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A541" t="inlineStr"/>
       <c r="B541" t="inlineStr">
         <is>
           <t>Reconstruction Project Manager</t>
@@ -41692,16 +39808,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M541" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
       <c r="N541" t="inlineStr">
         <is>
           <t>Xactimate, Excel, Word, Outlook</t>
@@ -41714,11 +39822,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A542" t="inlineStr"/>
       <c r="B542" t="inlineStr">
         <is>
           <t>Restoration Project Manager</t>
@@ -41769,16 +39873,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M542" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
       <c r="N542" t="inlineStr">
         <is>
           <t>Xactimate, Symbility, Time and Material (T&amp;M) Software, Microsoft Excel, Job management software</t>
@@ -41791,11 +39887,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A543" t="inlineStr"/>
       <c r="B543" t="inlineStr">
         <is>
           <t>Construction Project Manager (Commercial)</t>
@@ -41846,16 +39938,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M543" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
       <c r="N543" t="inlineStr">
         <is>
           <t>Microsoft Project, Procore, Sage 100, Microsoft Office</t>
@@ -41868,11 +39952,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A544" t="inlineStr"/>
       <c r="B544" t="inlineStr">
         <is>
           <t>Construction Project Manager</t>
@@ -41923,16 +40003,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L544" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M544" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
       <c r="N544" t="inlineStr">
         <is>
           <t>Procore, Microsoft Project, Sage 100, Microsoft Office</t>
@@ -41945,11 +40017,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A545" t="inlineStr"/>
       <c r="B545" t="inlineStr">
         <is>
           <t>Construction Project Manager</t>
@@ -42000,16 +40068,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
       <c r="N545" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, Sage 100, Procore</t>
@@ -42022,11 +40082,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A546" t="inlineStr"/>
       <c r="B546" t="inlineStr">
         <is>
           <t>Construction Project Coordinator</t>
@@ -42077,16 +40133,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M546" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
       <c r="N546" t="inlineStr">
         <is>
           <t>Microsoft Office, Procore, Sage 100</t>
@@ -42099,11 +40147,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A547" t="inlineStr"/>
       <c r="B547" t="inlineStr">
         <is>
           <t>Service Project Manager</t>
@@ -42154,21 +40198,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L547" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M547" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N547" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+      <c r="N547" t="inlineStr"/>
       <c r="O547" t="inlineStr">
         <is>
           <t>2026-05-22 02:20:55 PM CDT</t>
@@ -42176,11 +40208,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A548" t="inlineStr"/>
       <c r="B548" t="inlineStr">
         <is>
           <t>Project Manager - Fire Sprinkler</t>
@@ -42231,16 +40259,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L548" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M548" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
       <c r="N548" t="inlineStr">
         <is>
           <t>AutoCAD, HydraBID, HydraCALC, HydraLIST, HydraCAD, Viewpoint</t>
@@ -42253,11 +40273,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A549" t="inlineStr"/>
       <c r="B549" t="inlineStr">
         <is>
           <t>Project Manager - Fire Sprinkler</t>
@@ -42308,16 +40324,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M549" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
       <c r="N549" t="inlineStr">
         <is>
           <t>AutoCAD, HydraBID, HydraCALC, HydraLIST, HydraCAD, Viewpoint</t>
@@ -42330,11 +40338,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A550" t="inlineStr"/>
       <c r="B550" t="inlineStr">
         <is>
           <t>Project Manager - Fire Sprinkler</t>
@@ -42385,16 +40389,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L550" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M550" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
       <c r="N550" t="inlineStr">
         <is>
           <t>AutoCAD, HydraBID, HydraCALC, HydraLIST, HydraCAD, Viewpoint</t>
@@ -42407,11 +40403,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A551" t="inlineStr"/>
       <c r="B551" t="inlineStr">
         <is>
           <t>Project Coordinator - Permitting Group</t>
@@ -42462,16 +40454,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L551" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M551" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
       <c r="N551" t="inlineStr">
         <is>
           <t>Microsoft Office, Project Management Software, CAD</t>
@@ -42484,11 +40468,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A552" t="inlineStr"/>
       <c r="B552" t="inlineStr">
         <is>
           <t>Project Manager - Eagle</t>
@@ -42539,16 +40519,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L552" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M552" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
       <c r="N552" t="inlineStr">
         <is>
           <t>Microsoft Office Suite, Viewpoint, Procore (plus)</t>
@@ -42561,11 +40533,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A553" t="inlineStr"/>
       <c r="B553" t="inlineStr">
         <is>
           <t>Project Manager-CT</t>
@@ -42616,21 +40584,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L553" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M553" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N553" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
+      <c r="N553" t="inlineStr"/>
       <c r="O553" t="inlineStr">
         <is>
           <t>2026-05-22 02:19:06 PM CDT</t>
@@ -42638,11 +40594,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A554" t="inlineStr"/>
       <c r="B554" t="inlineStr">
         <is>
           <t>Project Manager-NE</t>
@@ -42693,21 +40645,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M554" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N554" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
+      <c r="N554" t="inlineStr"/>
       <c r="O554" t="inlineStr">
         <is>
           <t>2026-05-22 02:19:06 PM CDT</t>
@@ -42715,11 +40655,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A555" t="inlineStr"/>
       <c r="B555" t="inlineStr">
         <is>
           <t>Project Manager II</t>
@@ -42770,16 +40706,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L555" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M555" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
       <c r="N555" t="inlineStr">
         <is>
           <t>EClinical Data Capture, GCP, FDA Regulations, Project Management Software, Data Management Systems</t>
@@ -42792,11 +40720,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A556" t="inlineStr"/>
       <c r="B556" t="inlineStr">
         <is>
           <t>Student Marketing Project Manager</t>
@@ -42847,16 +40771,8 @@
           <t>Part Time</t>
         </is>
       </c>
-      <c r="L556" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M556" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
       <c r="N556" t="inlineStr">
         <is>
           <t>Microsoft Teams, Canva, Meta Business Suite, Facebook, LinkedIn, TikTok, Instagram, Canva, Microsoft Teams</t>
@@ -42869,11 +40785,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A557" t="inlineStr"/>
       <c r="B557" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -42924,21 +40836,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M557" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N557" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr"/>
+      <c r="N557" t="inlineStr"/>
       <c r="O557" t="inlineStr">
         <is>
           <t>2026-05-22 02:17:26 PM CDT</t>
@@ -42946,11 +40846,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A558" t="inlineStr"/>
       <c r="B558" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -43001,16 +40897,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L558" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M558" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr"/>
       <c r="N558" t="inlineStr">
         <is>
           <t>Microsoft Project, AutoCAD, BIM, Excel</t>
@@ -43023,11 +40911,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A559" t="inlineStr"/>
       <c r="B559" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -43078,21 +40962,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M559" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N559" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="inlineStr"/>
       <c r="O559" t="inlineStr">
         <is>
           <t>2026-05-22 02:16:41 PM CDT</t>
@@ -43100,11 +40972,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A560" t="inlineStr"/>
       <c r="B560" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -43155,21 +41023,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L560" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M560" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N560" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr"/>
+      <c r="N560" t="inlineStr"/>
       <c r="O560" t="inlineStr">
         <is>
           <t>2026-05-22 02:16:41 PM CDT</t>
@@ -43177,11 +41033,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A561" t="inlineStr"/>
       <c r="B561" t="inlineStr">
         <is>
           <t>Project Manager, Discovery &amp; Preclinical Development</t>
@@ -43232,16 +41084,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M561" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr"/>
       <c r="N561" t="inlineStr">
         <is>
           <t>MS Project, JIRA, SharePoint</t>
@@ -43254,11 +41098,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A562" t="inlineStr"/>
       <c r="B562" t="inlineStr">
         <is>
           <t>Merchandising Project Coordinator (Luxe Promo)</t>
@@ -43309,16 +41149,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L562" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M562" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr"/>
       <c r="N562" t="inlineStr">
         <is>
           <t>ESKO WebCenter, Wrike, Mediabox, IWD</t>
@@ -43331,11 +41163,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A563" t="inlineStr"/>
       <c r="B563" t="inlineStr">
         <is>
           <t>Merchandising Project Coordinator (Luxe Promo)</t>
@@ -43386,16 +41214,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L563" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M563" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr"/>
       <c r="N563" t="inlineStr">
         <is>
           <t>ESKO WebCenter, Wrike, Mediabox, IWD, AI tools</t>
@@ -43408,11 +41228,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A564" t="inlineStr"/>
       <c r="B564" t="inlineStr">
         <is>
           <t>OSP Project Manager</t>
@@ -43463,16 +41279,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M564" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr"/>
       <c r="N564" t="inlineStr">
         <is>
           <t>AutoCAD, MicroStation, Bluebeam</t>
@@ -43485,11 +41293,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A565" t="inlineStr"/>
       <c r="B565" t="inlineStr">
         <is>
           <t>Surveying Project Manager</t>
@@ -43540,16 +41344,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M565" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr"/>
       <c r="N565" t="inlineStr">
         <is>
           <t>CAD, Trimble, Microsoft Office, ACAD/Civil 3D, MicroStation</t>
@@ -43562,11 +41358,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A566" t="inlineStr"/>
       <c r="B566" t="inlineStr">
         <is>
           <t>Surveying Project Manager</t>
@@ -43617,16 +41409,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M566" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr"/>
       <c r="N566" t="inlineStr">
         <is>
           <t>CAD, Trimble, Trimble Business Center, AutoCAD Civil 3D, MicroStation, Microsoft Word, Microsoft Excel</t>
@@ -43639,11 +41423,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A567" t="inlineStr"/>
       <c r="B567" t="inlineStr">
         <is>
           <t>OSP Project Manager</t>
@@ -43694,16 +41474,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M567" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr"/>
       <c r="N567" t="inlineStr">
         <is>
           <t>AutoCAD, MicroStation, Bluebeam</t>
@@ -43716,11 +41488,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A568" t="inlineStr"/>
       <c r="B568" t="inlineStr">
         <is>
           <t>PROJECT MANAGER</t>
@@ -43771,16 +41539,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L568" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M568" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr"/>
       <c r="N568" t="inlineStr">
         <is>
           <t>MS Office, MS Project, Procore</t>
@@ -43793,11 +41553,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A569" t="inlineStr"/>
       <c r="B569" t="inlineStr">
         <is>
           <t>PROJECT MANAGER</t>
@@ -43848,16 +41604,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L569" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M569" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr"/>
       <c r="N569" t="inlineStr">
         <is>
           <t>Microsoft Office, MS Project, Procore</t>
@@ -43870,11 +41618,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A570" t="inlineStr"/>
       <c r="B570" t="inlineStr">
         <is>
           <t>PROJECT MANAGER</t>
@@ -43925,16 +41669,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M570" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr"/>
       <c r="N570" t="inlineStr">
         <is>
           <t>Procore, Construction management software</t>
@@ -43947,11 +41683,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A571" t="inlineStr"/>
       <c r="B571" t="inlineStr">
         <is>
           <t>PROJECT MANAGER</t>
@@ -44002,16 +41734,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M571" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr"/>
       <c r="N571" t="inlineStr">
         <is>
           <t>MS Project, Procore, Microsoft Office</t>
@@ -44024,11 +41748,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A572" t="inlineStr"/>
       <c r="B572" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -44079,21 +41799,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M572" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N572" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr"/>
+      <c r="N572" t="inlineStr"/>
       <c r="O572" t="inlineStr">
         <is>
           <t>2026-05-22 02:15:24 PM CDT</t>
@@ -44101,11 +41809,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A573" t="inlineStr"/>
       <c r="B573" t="inlineStr">
         <is>
           <t>Entry level Project Coordinator</t>
@@ -44156,16 +41860,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M573" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr"/>
       <c r="N573" t="inlineStr">
         <is>
           <t>MS Office</t>
@@ -44178,11 +41874,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A574" t="inlineStr"/>
       <c r="B574" t="inlineStr">
         <is>
           <t>Assistant Project Coordinator</t>
@@ -44233,16 +41925,8 @@
           <t>Part Time</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M574" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr"/>
       <c r="N574" t="inlineStr">
         <is>
           <t>Microsoft Office, Procore</t>
@@ -44255,11 +41939,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A575" t="inlineStr"/>
       <c r="B575" t="inlineStr">
         <is>
           <t>Water/Wastewater Project Manager</t>
@@ -44310,16 +41990,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M575" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr"/>
       <c r="N575" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Microsoft Project, Microsoft Teams, Microsoft Outlook</t>
@@ -44332,11 +42004,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A576" t="inlineStr"/>
       <c r="B576" t="inlineStr">
         <is>
           <t>Water Project Manager - Lubbock</t>
@@ -44387,16 +42055,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M576" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr"/>
       <c r="N576" t="inlineStr">
         <is>
           <t>CAD software, Microsoft Word, Microsoft Excel, Microsoft PowerPoint, Microsoft Project, Microsoft Teams, Microsoft Outlook</t>
@@ -44409,11 +42069,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A577" t="inlineStr"/>
       <c r="B577" t="inlineStr">
         <is>
           <t>Water Project Manager - Amarillo</t>
@@ -44464,16 +42120,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M577" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr"/>
       <c r="N577" t="inlineStr">
         <is>
           <t>MS Word, MS Excel, PowerPoint, Project, Teams, Outlook</t>
@@ -44486,11 +42134,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A578" t="inlineStr"/>
       <c r="B578" t="inlineStr">
         <is>
           <t>Project Manager - Water/Wastewater</t>
@@ -44541,16 +42185,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L578" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M578" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr"/>
       <c r="N578" t="inlineStr">
         <is>
           <t>MS Word, Excel, PowerPoint, Project, Outlook</t>
@@ -44563,11 +42199,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A579" t="inlineStr"/>
       <c r="B579" t="inlineStr">
         <is>
           <t>CRM Project Manager</t>
@@ -44618,16 +42250,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L579" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M579" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr"/>
       <c r="N579" t="inlineStr">
         <is>
           <t>CRM software</t>
@@ -44640,11 +42264,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A580" t="inlineStr"/>
       <c r="B580" t="inlineStr">
         <is>
           <t>Project Manager, Pre-Construction (Nationwide)</t>
@@ -44695,21 +42315,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L580" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M580" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N580" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr"/>
+      <c r="N580" t="inlineStr"/>
       <c r="O580" t="inlineStr">
         <is>
           <t>2026-05-22 02:01:07 PM CDT</t>
@@ -44717,11 +42325,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A581" t="inlineStr"/>
       <c r="B581" t="inlineStr">
         <is>
           <t>Project Manager, Operations (Nationwide)</t>
@@ -44772,21 +42376,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L581" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M581" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N581" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr"/>
+      <c r="N581" t="inlineStr"/>
       <c r="O581" t="inlineStr">
         <is>
           <t>2026-05-22 02:01:07 PM CDT</t>
@@ -45013,11 +42605,7 @@
           <t>Providing essential public services and infrastructure to Florida residents.</t>
         </is>
       </c>
-      <c r="N584" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N584" t="inlineStr"/>
       <c r="O584" t="inlineStr">
         <is>
           <t>2026-05-22 12:59:45 PM CDT</t>
@@ -45321,11 +42909,7 @@
           <t>Software platform for school websites, communications, and enrollment management.</t>
         </is>
       </c>
-      <c r="N588" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N588" t="inlineStr"/>
       <c r="O588" t="inlineStr">
         <is>
           <t>2026-05-22 11:04:07 AM CDT</t>
@@ -45475,11 +43059,7 @@
           <t>Global professional services firm specializing in engineering and architecture.</t>
         </is>
       </c>
-      <c r="N590" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N590" t="inlineStr"/>
       <c r="O590" t="inlineStr">
         <is>
           <t>2026-05-22 10:49:50 AM CDT</t>
@@ -45487,11 +43067,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A591" t="inlineStr"/>
       <c r="B591" t="inlineStr">
         <is>
           <t>Project Manager III</t>
@@ -45542,16 +43118,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L591" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M591" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr"/>
       <c r="N591" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Project, Microsoft PowerPoint, Earned Value Management, Deltek Costpoint, Primavera P6</t>
@@ -45949,233 +43517,3168 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
+      <c r="A597" t="inlineStr"/>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>HVAC Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=196722&amp;clientkey=BEA6CD6B7AFB990F461B19F45FE34C98</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Houston, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Senior Project Manager with detail orientation; able to coordinate VDC-driven HVAC projects in Houston; strong coordination, scheduling, and documentation skills.</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr"/>
+      <c r="N597" t="inlineStr"/>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr"/>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4189979</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Lakewood, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>$100k-$120k/yr, $48-$57/hr</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>Experience in architectural millwork or commercial construction; Bachelor's in Construction Management or equivalent; ability to read architectural/shop drawings; strong organization, communication, and PM skills; proficient in MS Office and project management systems.</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr"/>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>Microsoft Office, project management systems</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>2026-05-21 03:09:08 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr"/>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>JDH - Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=319500&amp;clientkey=12C2C4F1A8DDB21A9D45C2C49D4F1962</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Mount Sterling, Kentucky, United States</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>Able to work independently, strong problem solving, proficient in Microsoft Office, well organized, good communicator.</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr"/>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>HVAC Senior Project Manager</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=196722&amp;clientkey=BEA6CD6B7AFB990F461B19F45FE34C98</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>Houston, Texas, United States</t>
-        </is>
-      </c>
-      <c r="F597" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H597" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J597" t="inlineStr">
-        <is>
-          <t>Senior Project Manager with detail orientation; able to coordinate VDC-driven HVAC projects in Houston; strong coordination, scheduling, and documentation skills.</t>
-        </is>
-      </c>
-      <c r="K597" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L597" t="inlineStr">
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6154255.careers?ShowJob=554109573</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Astoria, New York, United States</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>$130k-$150k/yr, $62-$72/hr</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Construction Engineering or related; 2 years of urban infrastructure/public/commercial/construction experience; full-time, 8am-5pm; strong communication and leadership skills.</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M597" t="inlineStr">
+      <c r="M600" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N597" t="inlineStr">
+      <c r="N600" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O597" t="inlineStr">
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:28:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6154255.careers?ShowJob=554109574</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Astoria, New York, United States</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>$70k-$100k/yr, $33-$48/hr</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>Construction management or engineering background with strong communication, reading drawings, and software skills.</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>AutoCAD, Procore, Microsoft Word, Microsoft Excel, Microsoft PowerPoint</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:28:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6154255.careers?ShowJob=570908324</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Astoria, New York, United States</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>$65k-$70k/yr, $31-$33/hr</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Construction management experience and/or engineering degree; strong communication; proficient in MS Office; read architectural plans; AutoCAD and Procore preferred.</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>AutoCAD, Procore, Word, Excel, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:28:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Implementation Project Manager</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>https://secure.yourpayrollhr.com/ta/TPC0209.careers?ShowJob=419674434</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Ann Arbor, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>2+ years software project management; strong client-facing and internal communication; PMP or related certification preferred.</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>Jira, Microsoft Project, CRM tools</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:26:49 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>https://secure2.entertimeonline.com/ta/TELTECH.careers?ShowJob=386038215</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Phoenix, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>3+ years in telecommunications field; US experience in telecom/security or wireless; high school diploma preferred; proficient in construction drawings; strong communication and leadership; travel flexibility.</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>Word, Excel, PowerPoint, Project, CAD, Visio, Accounting systems</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:23:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>https://secure2.entertimeonline.com/ta/TELTECH.careers?ShowJob=386038216</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Phoenix, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>3+ years in telecommunications; high school diploma; handling multiple people; ability to read drawings; proficient with Word, Excel, PowerPoint, Project, CAD, Visio; focus on safety and budget.</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>Word, Excel, PowerPoint, Project, CAD, Visio, Accounting Systems</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:23:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>https://secure2.entertimeonline.com/ta/KPAY33632703.careers?ShowJob=688007563</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>High school diploma, 1+ year related experience; sales support or project coordination preferred; proficient with Windows and project software; strong organizational skills.</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Microsoft Windows, Proprietary quoting software, OMS, Pella proprietary systems</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:23:28 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Project Manager - Metal Fabrication</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>https://secure6.saashr.com/ta/6190123.careers?ShowJob=688573072</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>2+ years project management in manufacturing; degree or technical diploma in PM/engineering; PMP a plus; CAD proficiency; travel 10%</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>CAD, MS Office</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:22:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Construction Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6212015.careers?ShowJob=570907104</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Indianapolis, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>$80k-$100k/yr, $38-$48/hr</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Assist in managing construction projects, coordinating resources, timelines, budgets, and vendor relations from bidding to delivery.</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:19:33 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Material Handling Project Manager </t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>https://secure8.yourpayrollhr.com/ta/MGH7316.careers?ShowJob=721964417</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree (or higher); 3+ years in material handling/automation; proven project leadership; strong communication; willingness to travel; driver’s license.</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Microsoft Project, AutoCAD</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:19:27 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Engineering Development Pathway: Site Manager to Project Manager</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>https://secure8.yourpayrollhr.com/ta/MGH7316.careers?ShowJob=721974789</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>High school diploma required; Bachelor’s in construction management or engineering preferred; basic computer skills; PMP or PM certification preferred.</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft Outlook, Microsoft Teams, Field management software</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:19:12 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6216656.careers?ShowJob=587707491</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Wahiawa, Hawaii, United States</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent experience; proficient in MS Office, SharePoint, MS Project, and TEAMS; knowledge of military health facility construction and transition; US citizen eligible for security clearance.</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel, PowerPoint, Word, SharePoint, Microsoft Project, Teams</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:19:24 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Project Coordinator -Engineering</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6216432.careers?ShowJob=587721617</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Magnolia, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>$41k-$58k/yr, $20-$28/hr</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; entry-level project coordination experience desirable; strong organization, communication, and PM software skills; analytical and detail-oriented.</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Project Management Software, Microsoft Excel, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:52 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6216432.careers?ShowJob=587721620</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Magnolia, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>$65k-$80k/yr, $31-$38/hr</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in a relevant field; PMP/PRINCE2 asset; proven PM experience; PM tools proficiency; experience in Lighting/Construction or NDT desirable.</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>Project Management Software, Microsoft Excel, Microsoft PowerPoint</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:50 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager </t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6215675.careers?ShowJob=604444110</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>$65k-$85k/yr, $31-$40/hr</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Traveling Project Manager with 1+ year experience; high school diploma; leadership; travel 85%; ability to manage onsite teams.</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:38 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6215110.careers?ShowJob=587703157</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Saint Paul, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>$100k-$128k/yr, $48-$61/hr</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Experience managing commercial construction projects, scheduling, budgeting, and leadership.</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:34 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Reconstruction Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6206051.careers?ShowJob=587674867</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Carrollton, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>$65k-$80k/yr, $31-$38/hr</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Coordinate projects, manage AR, customer service; 2+ years in disaster restoration; bachelor’s degree or equivalent experience.</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>CRM, Microsoft Office, Windows, Internet</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>MIT Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6206051.careers?ShowJob=587703408</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Carrollton, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>$45k-$65k/yr, $21-$31/hr</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>1–3 years in restoration, construction, or similar industry; strong admin skills; excellent communication; able to work in fast-paced environment.</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Xactimate, Salesforce, Moisture mapping / drying logs</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:18 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Reconstruction Project Manager</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6206051.careers?ShowJob=587703899</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Tucson, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>$65k-$95k/yr, $31-$45/hr</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>3+ years field management in construction; OSHA 10/30; Procore and Excel proficiency; strong leadership and coordination.</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Procore, Microsoft Excel, Scheduling tools</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:16 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Contents Project Manager</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>https://secure7.saashr.com/ta/6206051.careers?ShowJob=587708847</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Carrollton, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>$75k-$90k/yr, $36-$43/hr</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>2+ years project management; restoration experience preferred; strong organizational, communication, and customer service skills; driver’s license; travel as needed.</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Salesforce, Restoration software</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:18:06 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App Project Manager </t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>https://secure.entertimeonline.com/ta/HRMGMT10.careers?ShowJob=822226309</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Costa Mesa, California, United States</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>$110k-$135k/yr, $52-$64/hr</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree and 3–5+ years in project management, digital platforms, mobile apps, or growth initiatives. Knowledge of mobile apps, loyalty programs, CRM, or consumer engagement platforms.</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Firebase, Mixpanel, Amplitude, CRM systems, Loyalty platforms</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:16:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>IT Project Manager (Onsite - VA)</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>https://secure2.saashr.com/ta/Akumen.careers?ShowJob=788699205</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Springfield, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>Manages IT project delivery; PMP required; Bachelor’s in related field; 4+ years IT; 3+ years technical writing; 3+ years client-facing; clearance required.</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>MS Office, SharePoint, MS Project, ServiceNow ITSM</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:16:46 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Roebbelen Contracting</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>https://secure6.saashr.com/ta/6176321.careers?ShowJob=705069120</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Dublin, California, United States</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>$105k-$135k/yr, $50-$64/hr</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>Bachelor’s in CM/engineering/architecture or related; 3+ years construction management support; OSHA safety knowledge; proficient with project controls and MS Office; Procore/Bluebeam/Primavera familiarity.</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>https://roebbelen.com</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>General contracting and construction management services.</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Procore, Bluebeam, Sure Trak, Primavera</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:47:58 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Brault</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4194687</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>San Dimas, California, United States</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>$54k-$66k/yr, $26-$32/hr</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>Coordinate projects with cross-functional teams; ensure timelines, deliverables, and documentation are tracked and reported.</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>https://brault.us</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>Provides revenue cycle and practice management for physician groups.</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Microsoft Project, SharePoint, OneNote, PowerPoint, Excel</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:45:32 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Foxconn</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>https://foxconnwi.pinpointhq.com/en/postings/41ff2fc9-0fe9-4351-919c-c6b0904ab57e</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Mount Pleasant, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Engineering or Business; PMP preferred; 2+ years project coordination in manufacturing; PCBA experience; ability to stand and lift up to 25 lbs.</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>https://foxconn.com</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>World's largest contract manufacturer of electronic products and components.</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Project management software, Data analytics tools</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:26:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Foxconn</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>https://foxconnwi.pinpointhq.com/en/postings/35fe279e-82e9-4311-ab85-c683df88dfa9</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Mount Pleasant, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Bachelor’s in Industrial/Manufacturing/Electrical Engineering or Supply Chain; 1-3 years project management experience; PMP preferred; hands-on, detail oriented; proficient in Office 365; able to manage multiple projects.</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>https://foxconn.com</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>World's largest contract manufacturer of electronic products and components.</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>Office 365, PMP, Project Management Software, SharePoint, Teams, Excel, Word, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:25:35 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Foxconn</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Facility Project Manager</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>https://foxconnwi.pinpointhq.com/en/postings/5caf8fbe-f4d3-42f1-a82c-c5893c0eb30d</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Mount Pleasant, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>Manage planning, coordination, and execution of facility construction and improvement projects; oversee schedules, budgets, vendor coordination, and compliance.</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>https://foxconn.com</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>World's largest contract manufacturer of electronic products and components.</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Project Management Software, Document Control Systems</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:25:35 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>MJ Hughes Construction</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Project Manager - Heavy Civil</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>https://mjhughes.pinpointhq.com/en/postings/37f01fb1-4f38-42c1-9d04-2af0a58f93cb</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Vancouver, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>$140k-$170k/yr, $67-$81/hr</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Leadership experience in construction management; budgeting, scheduling, QA/QC; degree in Construction Management or related field; proficiency in MS Project, Primavera, Bluebeam; highway/bridge experience preferred.</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>https://mjhughes.com</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>Heavy civil contractor specializing in concrete, earthwork, and utilities.</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>MS Project, Primavera, Bluebeam, HCSS HeavyBid, HCSS HeavyJob</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:26:10 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Brooks Building Solutions</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager - HVAC/Controls</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>https://brookssolutions.pinpointhq.com/en/postings/e300f5c3-cead-40cd-a4d4-ffd9cee50b0b</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Palmetto, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>$53k-$70k/yr, $25-$33/hr</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Assist in planning, scheduling, budgeting, and coordinating building automation projects; support stakeholders; learn and apply project management and technical skills.</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>https://brookssolutions.net</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr"/>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:25:35 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Brooks Building Solutions</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager - HVAC/Controls</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>https://brookssolutions.pinpointhq.com/en/postings/fff91d24-5bcc-4164-ad9c-e2a4b803752c</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Orlando or Longwood</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>$53k-$70k/yr, $25-$33/hr</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Assistant project management role supporting planning, scheduling, budgeting, vendor coordination, and documentation for building automation projects.</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>https://brookssolutions.net</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr"/>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>Project management tools, CAD/drawing software</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:25:35 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Chesapeake Controls</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junior Project Manager (Construction) </t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>https://chesapeakecontrols.pinpointhq.com/en/postings/ae5be21a-6c7b-42e1-9b9b-748713a3582b</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Chesapeake, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>$55k-$95k/yr, $26-$45/hr</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Business, Project Management, or related field; 1-3 years coordinating projects; proficient with MS Office; strong organization and communication; valid VA driver’s license.</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>https://chesapeakecontrols.com</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr"/>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Outlook, Word, Excel</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:25:35 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Stonefield Engineering &amp; Design</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Project Manager – Traffic/Transportation</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.pinpointhq.com/en/postings/6f0fa61a-0dda-4120-b81b-1e2a1211d907</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Asbury Park, New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>$90k-$180k/yr, $43-$86/hr</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Bachelor of Science in Civil Engineering; licensed Professional Engineer; 4+ years traffic engineering; Proficiency in Highway Capacity Software and Synchro/SimTraffic; familiarity with NJDOT/NYSDOT/PennDOT; strong communication and organizational skills.</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.com</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr"/>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>AutoCAD, Highway Capacity Software, Synchro/SimTraffic</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:12:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Stonefield Engineering &amp; Design</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Project Manager – Traffic/Transportation</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.pinpointhq.com/en/postings/04c64abd-b63f-4a1b-992f-8418e3eb302e</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>$90k-$180k/yr, $43-$86/hr</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>4+ years in traffic engineering with PE license; BS in Civil Engineering; proficient in HCS and Synchro/SimTraffic; NJDOT/NYSDOT knowledge; strong communication and teamwork.</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.com</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr"/>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>AutoCAD, Highway Capacity Software, Synchro/SimTraffic, GIS, 3-D modeling</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:12:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Stonefield Engineering &amp; Design</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Project Manager – Site/Civil</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.pinpointhq.com/en/postings/ca580ac7-fc93-4000-8242-b7f0dffe2dc4</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>$90k-$180k/yr, $43-$86/hr</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Bachelor of Science in Civil Engineering; licensed Professional Engineer; 4+ years site/grading design; AutoCAD proficiency; strong teamwork, communication, and organization; Civil 3D/HydroCAD a plus.</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.com</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr"/>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>AutoCAD, Civil 3D, HydroCAD</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:12:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Stonefield Engineering &amp; Design</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Project Manager – Site/Civil</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.pinpointhq.com/en/postings/acda5006-a051-42e4-a49d-d0b3d5800157</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Birmingham, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>$90k-$180k/yr, $43-$86/hr</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Bachelor of Science in Civil Engineering; licensed PE; 4+ years site/grading design; AutoCAD proficiency; team player with strong communication and organization; Civil 3D/HydroCAD a plus.</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>https://stonefieldeng.com</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr"/>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>AutoCAD, Civil 3D, HydroCAD</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:12:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Product Developer/Project Manager (Turnkey/Fragrance)</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>https://innovativebeautygroup.recruitee.com/o/product-developerproject-manager-turnkeyfragrance</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>$72k-$85k/yr, $34-$40/hr</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Bachelor's in science/cosmetics, 3-5 years in PM or product development, fragrance industry experience preferred, Wrike/ClickUp experience preferred.</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>Wrike, ClickUp</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:16:51 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ClimeCo LLC - Project Coordinator- IT</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4193323</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>$65k-$75k/yr, $31-$36/hr</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>3+ years IT project coordination; remote work; strong PM tool skills; SDLC familiarity.</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>Jira, Confluence, Asana, Monday.com, Notion, Basecamp</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:43:18 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>https://pridestaff.phenompro.com/us/en/job/574807/Assistant-Project-Manager</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Tuscaloosa, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>$41k-$52k/yr, $20-$25/hr</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>0–4 years in construction/mechanical projects; degree preferred in CM/Engineering; strong organization and communication; proficient with MS Office and PM software.</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Temporary, Temporary, Temporary</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Project Management Software, Microsoft Excel, Microsoft Word, Isometrics Interpretation, ASME Codes, BIM/VDC, Quality Control Documentation</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4189979</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>Lakewood, Colorado, United States</t>
-        </is>
-      </c>
-      <c r="F598" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G598" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I598" t="inlineStr">
-        <is>
-          <t>$100k-$120k/yr, $48-$57/hr</t>
-        </is>
-      </c>
-      <c r="J598" t="inlineStr">
-        <is>
-          <t>Experience in architectural millwork or commercial construction; Bachelor's in Construction Management or equivalent; ability to read architectural/shop drawings; strong organization, communication, and PM skills; proficient in MS Office and project management systems.</t>
-        </is>
-      </c>
-      <c r="K598" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L598" t="inlineStr">
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>https://yellowstone.recruitee.com/o/junior-project-manager-4</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>St. Clair Shores, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>$68k-$68k/yr, $32-$32/hr</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Construction experience minimal; strong reading of drawings; Procore/Bluebeam/Microsoft Project skills; valid license and vehicle.</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M598" t="inlineStr">
+      <c r="M638" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N598" t="inlineStr">
-        <is>
-          <t>Microsoft Office, project management systems</t>
-        </is>
-      </c>
-      <c r="O598" t="inlineStr">
-        <is>
-          <t>2026-05-21 03:09:08 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>JDH - Project Coordinator</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=319500&amp;clientkey=12C2C4F1A8DDB21A9D45C2C49D4F1962</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>Mount Sterling, Kentucky, United States</t>
-        </is>
-      </c>
-      <c r="F599" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G599" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H599" t="inlineStr">
-        <is>
-          <t>Entry Level</t>
-        </is>
-      </c>
-      <c r="I599" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J599" t="inlineStr">
-        <is>
-          <t>Able to work independently, strong problem solving, proficient in Microsoft Office, well organized, good communicator.</t>
-        </is>
-      </c>
-      <c r="K599" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L599" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M599" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N599" t="inlineStr">
-        <is>
-          <t>Microsoft Office</t>
-        </is>
-      </c>
-      <c r="O599" t="inlineStr">
-        <is>
-          <t>2026-05-20 07:00:00 PM CDT</t>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Procore, Bluebeam, Microsoft Project, Microsoft Excel, Microsoft Word</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>2026-05-21 08:53:28 AM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O638"/>
+  <dimension ref="A1:O735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43708,11 +43708,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A600" t="inlineStr"/>
       <c r="B600" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -43763,21 +43759,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L600" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M600" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N600" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr"/>
+      <c r="N600" t="inlineStr"/>
       <c r="O600" t="inlineStr">
         <is>
           <t>2026-05-22 03:28:51 PM CDT</t>
@@ -43785,11 +43769,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A601" t="inlineStr"/>
       <c r="B601" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -43840,16 +43820,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L601" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M601" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr"/>
       <c r="N601" t="inlineStr">
         <is>
           <t>AutoCAD, Procore, Microsoft Word, Microsoft Excel, Microsoft PowerPoint</t>
@@ -43862,11 +43834,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A602" t="inlineStr"/>
       <c r="B602" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
@@ -43917,16 +43885,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L602" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M602" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr"/>
       <c r="N602" t="inlineStr">
         <is>
           <t>AutoCAD, Procore, Word, Excel, PowerPoint</t>
@@ -43939,11 +43899,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
           <t>Implementation Project Manager</t>
@@ -43994,16 +43950,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L603" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M603" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr"/>
       <c r="N603" t="inlineStr">
         <is>
           <t>Jira, Microsoft Project, CRM tools</t>
@@ -44016,11 +43964,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A604" t="inlineStr"/>
       <c r="B604" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -44071,16 +44015,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M604" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr"/>
       <c r="N604" t="inlineStr">
         <is>
           <t>Word, Excel, PowerPoint, Project, CAD, Visio, Accounting systems</t>
@@ -44093,11 +44029,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A605" t="inlineStr"/>
       <c r="B605" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -44148,16 +44080,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L605" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M605" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr"/>
       <c r="N605" t="inlineStr">
         <is>
           <t>Word, Excel, PowerPoint, Project, CAD, Visio, Accounting Systems</t>
@@ -44170,11 +44094,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -44225,16 +44145,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L606" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M606" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr"/>
       <c r="N606" t="inlineStr">
         <is>
           <t>Microsoft Windows, Proprietary quoting software, OMS, Pella proprietary systems</t>
@@ -44247,11 +44159,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A607" t="inlineStr"/>
       <c r="B607" t="inlineStr">
         <is>
           <t xml:space="preserve"> Project Manager - Metal Fabrication</t>
@@ -44302,16 +44210,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L607" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M607" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr"/>
       <c r="N607" t="inlineStr">
         <is>
           <t>CAD, MS Office</t>
@@ -44324,11 +44224,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A608" t="inlineStr"/>
       <c r="B608" t="inlineStr">
         <is>
           <t>Construction Assistant Project Manager</t>
@@ -44379,21 +44275,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L608" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M608" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N608" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr"/>
+      <c r="N608" t="inlineStr"/>
       <c r="O608" t="inlineStr">
         <is>
           <t>2026-05-22 03:19:33 PM CDT</t>
@@ -44401,11 +44285,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A609" t="inlineStr"/>
       <c r="B609" t="inlineStr">
         <is>
           <t xml:space="preserve">Material Handling Project Manager </t>
@@ -44456,16 +44336,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L609" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M609" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr"/>
       <c r="N609" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, AutoCAD</t>
@@ -44478,11 +44350,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A610" t="inlineStr"/>
       <c r="B610" t="inlineStr">
         <is>
           <t>Engineering Development Pathway: Site Manager to Project Manager</t>
@@ -44533,16 +44401,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L610" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M610" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr"/>
       <c r="N610" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft Outlook, Microsoft Teams, Field management software</t>
@@ -44555,11 +44415,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A611" t="inlineStr"/>
       <c r="B611" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -44610,16 +44466,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L611" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M611" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr"/>
       <c r="N611" t="inlineStr">
         <is>
           <t>Microsoft Office, Excel, PowerPoint, Word, SharePoint, Microsoft Project, Teams</t>
@@ -44632,11 +44480,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A612" t="inlineStr"/>
       <c r="B612" t="inlineStr">
         <is>
           <t>Project Coordinator -Engineering</t>
@@ -44687,16 +44531,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L612" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M612" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr"/>
       <c r="N612" t="inlineStr">
         <is>
           <t>Project Management Software, Microsoft Excel, PowerPoint</t>
@@ -44709,11 +44545,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A613" t="inlineStr"/>
       <c r="B613" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -44764,16 +44596,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L613" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M613" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr"/>
       <c r="N613" t="inlineStr">
         <is>
           <t>Project Management Software, Microsoft Excel, Microsoft PowerPoint</t>
@@ -44786,11 +44610,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A614" t="inlineStr"/>
       <c r="B614" t="inlineStr">
         <is>
           <t xml:space="preserve">Project Manager </t>
@@ -44841,21 +44661,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L614" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M614" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N614" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr"/>
+      <c r="N614" t="inlineStr"/>
       <c r="O614" t="inlineStr">
         <is>
           <t>2026-05-22 03:18:38 PM CDT</t>
@@ -44863,11 +44671,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A615" t="inlineStr"/>
       <c r="B615" t="inlineStr">
         <is>
           <t>Construction Project Manager</t>
@@ -44918,21 +44722,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L615" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M615" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N615" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr"/>
+      <c r="N615" t="inlineStr"/>
       <c r="O615" t="inlineStr">
         <is>
           <t>2026-05-22 03:18:34 PM CDT</t>
@@ -44940,11 +44732,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A616" t="inlineStr"/>
       <c r="B616" t="inlineStr">
         <is>
           <t>Reconstruction Project Coordinator</t>
@@ -44995,16 +44783,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L616" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M616" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr"/>
       <c r="N616" t="inlineStr">
         <is>
           <t>CRM, Microsoft Office, Windows, Internet</t>
@@ -45017,11 +44797,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A617" t="inlineStr"/>
       <c r="B617" t="inlineStr">
         <is>
           <t>MIT Project Coordinator</t>
@@ -45072,16 +44848,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L617" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M617" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr"/>
       <c r="N617" t="inlineStr">
         <is>
           <t>Xactimate, Salesforce, Moisture mapping / drying logs</t>
@@ -45094,11 +44862,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A618" t="inlineStr"/>
       <c r="B618" t="inlineStr">
         <is>
           <t>Reconstruction Project Manager</t>
@@ -45149,16 +44913,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L618" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M618" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr"/>
       <c r="N618" t="inlineStr">
         <is>
           <t>Procore, Microsoft Excel, Scheduling tools</t>
@@ -45171,11 +44927,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A619" t="inlineStr"/>
       <c r="B619" t="inlineStr">
         <is>
           <t>Contents Project Manager</t>
@@ -45226,16 +44978,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M619" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr"/>
       <c r="N619" t="inlineStr">
         <is>
           <t>Salesforce, Restoration software</t>
@@ -45248,11 +44992,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A620" t="inlineStr"/>
       <c r="B620" t="inlineStr">
         <is>
           <t xml:space="preserve">App Project Manager </t>
@@ -45303,16 +45043,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L620" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M620" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr"/>
       <c r="N620" t="inlineStr">
         <is>
           <t>Firebase, Mixpanel, Amplitude, CRM systems, Loyalty platforms</t>
@@ -45325,11 +45057,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A621" t="inlineStr"/>
       <c r="B621" t="inlineStr">
         <is>
           <t>IT Project Manager (Onsite - VA)</t>
@@ -45380,16 +45108,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L621" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M621" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr"/>
       <c r="N621" t="inlineStr">
         <is>
           <t>MS Office, SharePoint, MS Project, ServiceNow ITSM</t>
@@ -45925,11 +45645,7 @@
         </is>
       </c>
       <c r="M628" t="inlineStr"/>
-      <c r="N628" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N628" t="inlineStr"/>
       <c r="O628" t="inlineStr">
         <is>
           <t>2026-05-22 01:25:35 PM CDT</t>
@@ -46375,310 +46091,7711 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
+      <c r="A635" t="inlineStr"/>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Product Developer/Project Manager (Turnkey/Fragrance)</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>https://innovativebeautygroup.recruitee.com/o/product-developerproject-manager-turnkeyfragrance</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>$72k-$85k/yr, $34-$40/hr</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Bachelor's in science/cosmetics, 3-5 years in PM or product development, fragrance industry experience preferred, Wrike/ClickUp experience preferred.</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr"/>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>Wrike, ClickUp</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:16:51 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr"/>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ClimeCo LLC - Project Coordinator- IT</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4193323</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>$65k-$75k/yr, $31-$36/hr</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>3+ years IT project coordination; remote work; strong PM tool skills; SDLC familiarity.</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr"/>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>Jira, Confluence, Asana, Monday.com, Notion, Basecamp</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:43:18 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr"/>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>https://pridestaff.phenompro.com/us/en/job/574807/Assistant-Project-Manager</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Tuscaloosa, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>$41k-$52k/yr, $20-$25/hr</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>0–4 years in construction/mechanical projects; degree preferred in CM/Engineering; strong organization and communication; proficient with MS Office and PM software.</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Temporary, Temporary, Temporary</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr"/>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Project Management Software, Microsoft Excel, Microsoft Word, Isometrics Interpretation, ASME Codes, BIM/VDC, Quality Control Documentation</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr"/>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>https://yellowstone.recruitee.com/o/junior-project-manager-4</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>St. Clair Shores, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>$68k-$68k/yr, $32-$32/hr</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Construction experience minimal; strong reading of drawings; Procore/Bluebeam/Microsoft Project skills; valid license and vehicle.</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr"/>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Procore, Bluebeam, Microsoft Project, Microsoft Excel, Microsoft Word</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>2026-05-21 08:53:28 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>ATI Restoration</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/atiexternal/cx/job-details?reqId=5001199256606</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah, United States</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Three years of superintendent experience in all phases of construction; requires asbestos/lead/mold certifications, llCRC AMRT, OSHA 30, valid state driver’s license, forklift certification; bilingual English/Spanish encouraged.</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>https://atirestoration.com</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>Providing disaster recovery, property restoration, and environmental remediation services.</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>MS Office, Xactimate, Salesforce.com</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:18:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>ATI Restoration</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/atiexternal/cx/job-details?reqId=5001200701806</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah, United States</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>Three years of construction project management; MS Office, Xactimate, Salesforce; OSHA 30; bilingual English/Spanish encouraged.</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>https://atirestoration.com</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>Providing disaster recovery, property restoration, and environmental remediation services.</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>MS Office, Xactimate, Salesforce.com</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:18:49 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>ATI Restoration</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/atiexternal/cx/job-details?reqId=5001199860606</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Cleveland or Elyria</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>Oversee multiple projects; 3+ years superintendent experience; MS Office, Xactimate, Salesforce; valid driver’s license; travel required.</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>https://atirestoration.com</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>Providing disaster recovery, property restoration, and environmental remediation services.</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>MS Office, Xactimate, Salesforce.com</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:18:49 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Oxford PharmaGenesis</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>https://pharmagenesisweb.eploy.net/vacancies/1342/project-manager.html</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Manage medical communications projects from initiation to delivery with publication focus; strong organizational, budgeting, and client reporting skills.</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Full Time, Temporary, Contract, Internship, Seasonal, Volunteer</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>https://pharmagenesis.com</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>Independent health science consultancy providing medical communication services.</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>Product Developer/Project Manager (Turnkey/Fragrance)</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>https://innovativebeautygroup.recruitee.com/o/product-developerproject-manager-turnkeyfragrance</t>
-        </is>
-      </c>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E635" t="inlineStr">
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:05:43 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>City of Sioux City</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Project Manager (Engineering) (Civil Service)</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>https://www.governmentjobs.com/careers/siouxcity/jobs/5353650</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Sioux City, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>$73k-$101k/yr, $35-$48/hr</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in engineering/architecture or related field; 3 years professional-level project management experience; civil project budgeting and scheduling; driver’s license required.</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>https://sioux-city.org</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>Providing municipal services and local governance to Sioux City residents.</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>AutoCAD, Microsoft Project, Excel, Word</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:04:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>City of Lancaster</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Learning and Development Manager</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>https://www.governmentjobs.com/careers/cityoflancasterpa/jobs/5338692</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Lancaster, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>$65k-$85k/yr, $31-$40/hr</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Bachelor's in HR/related; 3+ years HR; 5 years L&amp;D preferred; public sector experience preferred.</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>https://cityoflancasterpa.gov</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>Provides municipal services and governance to Lancaster residents.</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>LMS, ERP, Microsoft Office, Multimedia Learning Tools, Virtual meeting platforms</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>2026-05-22 05:19:38 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Carrier</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>https://carriernoam.workgr8.com/jobs/10543</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Pasadena, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>3+ years in project management; high school diploma; able to climb ladders and lift up to 20 lbs; valid vehicle insurance.</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>https://carrier.com</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>Manufactures HVAC, refrigeration, and fire safety systems.</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>Building Automation Software, WebCTRL, TCP/IP networks</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>2026-05-22 05:00:11 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>DSG</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Project Manager - Waterworks</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=d1dae87c-e1a3-4bc5-bd27-e41412a48f6c&amp;jobId=584972</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Otsego, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>$112112k-$187408k/yr, $53900-$90100/hr</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>Project management, customer coordination, budgeting, and product knowledge in waterworks.</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>https://dsgsupply.com</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>Wholesale distributor of electrical, plumbing, and HVAC construction supplies.</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>ERP (Eclipse)</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:58:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>West Star Aviation</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Associate Project Manager</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>https://weststaraviation.workgr8.com/jobs/1398</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>East Alton, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>$60k-$65k/yr, $28-$31/hr</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Project management tools experience; high school diploma; airframe license beneficial; aviation training beneficial; valid driver’s license ideal; willingness to travel; strong communication and organizational skills.</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>https://weststaraviation.com</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>Provides maintenance, repair, and overhaul services for business aircraft.</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>MS Project, Smartsheet, Celoxis</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:33:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Royston Group</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=656e8949-0006-43d5-b316-7f5d0510cd40&amp;jobId=957176</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Bell Gardens, California, United States</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>$39k-$47k/yr, $19-$23/hr</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>Entry-level project coordinator; HS diploma; strong communication, multitasking, MS Office; problem solving; detail-oriented; able to work independently; team oriented.</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>https://royston-group.com</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>Manufacturer of retail fixtures, signage, and refrigeration systems.</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel, Word, ABBA, Sign Resource QuickBase</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:06:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Stronghouse</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Coordinator </t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/stronghouse/jobs/4253982009</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Des Moines, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>2–5 years project coordination; construction/roofing experience preferred; proficient in CRM, Microsoft Office; Canva; AccuLynx; bilingual a plus.</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>https://stronghousebrands.com</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>Provides roofing and exterior home remodeling services.</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>CRM, AccuLynx, Canva, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:44:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>ServiceMaster DSI</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=451b6061-dc7f-4156-a7d5-26564afeed8a&amp;jobId=608956</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Stallings or Charlotte</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>$70k-$90k/yr, $33-$43/hr</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Prior disaster restoration experience; restoration estimating in Xactimate &amp; Symbility; attention to detail; strong communication; valid driver’s license; travel availability; background check/drug screen</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>https://servicemasterdsi.com</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>Provides residential and commercial disaster restoration and cleaning services.</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Xactimate, Symbility, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:35:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>ServiceMaster DSI</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=09e40c0f-90ac-45d4-81a4-c1b561400fd1&amp;jobId=608956</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Stallings, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>$70k-$90k/yr, $33-$43/hr</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>Disaster restoration experience; estimating using Xactimate/Symbility; strong communication and organization; valid driver’s license; willing to travel; pass background and drug test.</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>https://smdsi.com</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>Provides residential and commercial disaster restoration and reconstruction services.</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>Xactimate, Symbility</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:35:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>VGM Group</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=d4a749e0-8609-43ae-8083-df79fc771079&amp;jobId=571401</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Waterloo, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>Coordinate multiple projects, manage meetings and docs, maintain timelines and stakeholder communication.</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>https://vgmgroup.com</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>Provides specialized business services and healthcare management solutions.</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>JIRA Software, Kasaya, Web-based content management systems, Microsoft Office 365, Cross-functional collaboration tools</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:34:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Generate Capital</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/generate/5580609d-ec6b-4bb4-8ca8-dd81be483154</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>$110k-$130k/yr, $52-$62/hr</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>2+ years in development administration and/or project management; some solar PV experience preferred; strong organizational, communication, and problem-solving skills.</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>https://generatecapital.com</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>Finances, builds, and operates sustainable energy and resource infrastructure.</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:29:08 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Post Brothers</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=2c72c3ac-9037-4db5-8bc0-f4c24744d94e&amp;jobId=574327</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>$100k-$130k/yr, $48-$62/hr</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Minimum 3 years in professional construction management or engineering; Bachelor's degree; proficient in AutoCAD, Revit, BIM, and Procore; strong coordination and safety oversight.</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>https://postrents.com</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>Develops and manages luxury multifamily residential properties.</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>AutoCAD, Revit, BIM, MS Project, Omniplan, Procore</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:14:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Lyra Technology Group</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/lyratechgroup/jobs/5229449008</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Frisco, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>$100k-$120k/yr, $48-$57/hr</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Full-time Project Manager coordinating IT projects, resources, docs, and client/vendor communication; leadership for project team; ensure delivery on time and budget.</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>https://lyratechgroup.com</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>Operates a global portfolio of managed IT service providers.</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>Project Management Software, Scheduling Tools, Documentation Tools, Billing and Invoicing Systems</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:10:02 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Lincare</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/externallincarecareers/cx/job-details?reqId=5001200806806</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Clearwater, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>High school diploma or GED; ability to multitask; good written/verbal communication and organizational skills; computer skills; professional customer service phone skills; knowledge of word processing software; able to lift up to 10 pounds occasionally.</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>https://lincare.com</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>Provides home respiratory therapy and durable medical equipment services.</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>Word Processing</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:50:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Precision AQ</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/precisionaq/jobs/6004676004</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>$40k-$55k/yr, $19-$26/hr</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>1-2 years in project administration; bachelor’s degree; strong MS Office; excellent communication; detail-oriented; able to manage multiple projects.</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>https://precisionaq.com</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>Provides commercialization and market access services for pharmaceutical companies.</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:50:07 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Precision Medicine Group</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/precisionmedicinegroup/jobs/6004664004</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>$40k-$55k/yr, $19-$26/hr</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>1-2 years in project administration; familiar with SOW/MSA; strong communication; proficient in MS Office; detail-oriented and deadline-driven.</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>https://precisionmedicinegrp.com</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>Provides research and commercialization services for life sciences companies.</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:49:06 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Associate Project Manager</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/grouppmx/jobs/4257791009</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Wilmington, Delaware, United States</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>$105k-$120k/yr, $50-$57/hr</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Business, Construction Management, Engineering, or related field; 2–5 years of project coordination or assistant project management experience; proficient in MS Office; PMIS/PM tools familiarity.</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>MS Project, Smartsheet, PMIS, Microsoft Office Suite</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:47:48 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/babcockwilcoxcareers/cx/job-details?reqId=5001193135606</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Akron, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Experienced construction project manager responsible for site leadership, safety, quality, cost, schedule, and client coordination.</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>Primavera, Budgeting tools</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:45:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/talcareers/cx/job-details?reqId=5001198086706</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Greenfield, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>High school diploma required; associate degree preferred. Strong data management, communication, and PLM experience; eligible to work in the USA without sponsorship.</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>Microsoft Office, PowerBI, SharePoint, Excel</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:44:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Project Manager Autonomous Vehicles</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/talcareers/cx/job-details?reqId=5001178350900</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Georgetown, Kentucky, United States</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Bachelor's in Engineering or Technology; 2-5 years PM experience; PMP/MS/MBA a plus; must be able to travel; eligible to work in USA without sponsorship.</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Microsoft Project, Excel</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:44:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/talcareers/cx/job-details?reqId=5001190365300</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Noblesville, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Bachelor's degree required; project management experience; proficient in MS Office and MS Project; background in Material Handling, Robotics, Manufacturing or Packaging; eligible to work in the USA without sponsorship.</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Microsoft Visio, MS Project, MS Office</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:44:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Software Project Manager</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/talcareers/cx/job-details?reqId=5001155820300</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Indianapolis or Louisville</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Bachelor's in Engineering with 3-5 years exp; PMP a plus; strong MS Office, MS Project; SQL/Oracle databases; prior PM experience; US work eligibility.</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Microsoft Project, SQL Server, Oracle</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:44:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/southwest-fluid-products-inc-project-manager-a6f874a9-85dc-4566-9150-03a81913cc32</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Weatherford, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>4-7 years in project management for water/wastewater or industrial projects; OSHA 30; Texas Wastewater license; PMP encouraged but not required.</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:41:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/nlpartners-llc-project-manager-5a9e591e-67dc-4aae-86ef-4cf39efbc79e</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Pasco, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>$52k-$72k/yr, $25-$35/hr</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>4+ years in project management/operations; proven multi-project leadership; strong financial/analytical skills; excellent communication; proficient with PM tools; willing to travel; bachelor’s preferred; trades/home services experience preferred.</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>Asana, Monday, ClickUp, Excel, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:41:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/mission-construction-inc-project-manager-61bb09dd-b50d-4da3-ba7a-99a46a78c8cf</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Eden Prairie, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Manage commercial construction projects, coordinate subcontractors and schedules, ensure project milestones are met.</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:41:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/manatee-energy-operations-project-manager-8c59e217-1bab-455f-a385-1fe8fba75e4e</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Cambridge, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>$95k-$110k/yr, $45-$52/hr</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>3-5 years managing complex residential projects; proven process documentation; experience managing stakeholders and subcontractors; tech-forward; systems thinking.</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>Project management software, Automation tools</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:41:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/flow-builders-inc-project-manager-3f596f12-39ae-4a28-9549-9e08a4141cc0</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Carlsbad, California, United States</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>4+ years PM experience in commercial/residential construction; Procore/Microsoft Project; strong leadership, communication; travel to Southern California; degree preferred.</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>Procore, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:40:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>MGAC</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Junior - Mid Project Manager- Cost Focus</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mgac/jobs/4257777009</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Richmond, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>$110k-$140k/yr, $52-$67/hr</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>3+ years construction project management; 2+ years cost management; experience with critical environment projects; MEP in ground-up builds; strong communication; Bachelor’s or Associate in construction-related field; cost focus.</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>https://mgac.com</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Provides project management and owner representation for construction projects.</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:39:30 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Project Coordinator, Corporate Relations</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/association-of-cancer-care-centers-project-coordinator-corporate-relations-a4a36b18-84f8-4908-a495-a0ee3b30fa08</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>$52k-$78k/yr, $25-$37/hr</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree preferred; 3-5 years administrative/coordination experience; healthcare or association experience preferred.</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Salesforce (CRM), Database and document management systems</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:39:18 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/paint-bros-ma-project-manager-ba2818f6-907c-46c7-adf7-96f321405a2c</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Haverhill, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>$45k-$66k/yr, $22-$32/hr</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Experience in painting, drywall, construction, or related field; valid driver’s license; strong communication; organized; CRM skills; leadership.</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>CRM software, Project management software</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:39:18 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/jt-roselle-lighting-inc-project-manager-1e139a9b-6305-4908-9237-dc224261200c</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Plainview, New York, United States</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>$105k-$150k/yr, $50-$72/hr</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in PM/Engineering/Architecture or related field; 3-5 years in lighting project management; strong leadership, budgeting, scheduling; MS Office; ERP/Stack familiarity; OSHA 10; PMP a plus.</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Acumatica ERP, Stack, Estimating Software</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:38:18 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/kreative-core-technologies-project-manager-e06a490f-8285-49b9-9a99-a0862a83e446</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Technical PM with ERP and public-sector delivery experience; remote, consulting environment; governance, risk, and stakeholder management.</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>ERP, Project Management Tools, SIT, UAT</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:38:18 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/extreme-panel-technologies-project-coordinator-fbe92c03-db1b-4df7-952b-f9293b7c3047</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Cottonwood, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>$52k-$62k/yr, $25-$30/hr</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Entry-level to mid-level project coordination with 1–5 years of related experience; on-site in Cottonwood, MN; strong organizational and communication skills.</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>AutoCAD</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:38:18 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Collier County</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Project Manager II</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>https://www.governmentjobs.com/careers/collier/jobs/5352994</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Naples, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>$71k-$116k/yr, $34-$55/hr</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in a related field; 3 years experience; 4 additional years if no degree; fingerprinting; Florida driver’s license.</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>https://collier.gov</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>Provides essential public services and administration for local residents.</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:22:46 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Lumin8 Transportation Technologies</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=2ea0d6dd-d104-4b54-b37d-58026df56940&amp;jobId=566720</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Ashland, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>$110k-$135k/yr, $52-$64/hr</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>1-3 years in commercial electrical/roadway construction; bachelor’s in CM/CE/related field; read blueprints; proficient with Bluebeam/Adobe/MS Office; strong communication; cost/quantity takeoffs; ERP data entry; subcontractor management.</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>https://lumin8.com</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Installs and maintains smart traffic and transportation infrastructure.</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Bluebeam, Adobe Acrobat, Microsoft Outlook, Microsoft Word, Microsoft Excel, Spectrum ERP</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:22:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Lumin8 Transportation Technologies</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=2ea0d6dd-d104-4b54-b37d-58026df56940&amp;jobId=566715</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Wilson, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>$100k-$125k/yr, $48-$60/hr</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>1-3 years construction experience; BS in Construction Management, Construction Engineering, Civil Engineering or related field; ability to read blueprints; proficient with project software; strong communication and analytical skills.</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>https://lumin8.com</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>Installs and maintains smart traffic and transportation infrastructure.</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>Bluebeam, Adobe Acrobat, Microsoft Outlook, Microsoft Word, Microsoft Excel, Spectrum ERP</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:20:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Flooring Services Builder Resources</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/fsbuilderresources/cx/job-details?reqId=5001187806706</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Carrollton, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>Customer service experience, high school diploma, MS Office, strong communication.</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>https://fsbuilderresources.com</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr"/>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:18:56 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Roofstock</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Maintenance Project Coordinator (Temp)</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/roofstock/jobs/8561098002</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>$60k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree or equivalent; property/vendor management experience preferred; proficient with Google Apps, Microsoft Office, Slack; strong organization and communication; remote work capable; authorized to work in the U.S.</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Full Time, Temporary</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>https://roofstock.com</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Online marketplace for investing in single-family rental homes.</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Google Applications, Microsoft Office, Slack</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:16:50 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Matrix Technologies</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>https://matrix-technologies-inc.breezy.hr/p/982dd35c923a-project-manager</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Cincinnati, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>$87k-$120k/yr, $41-$57/hr</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in engineering, construction management, or architecture; PE and/or PMP preferred; 4+ years PM; 7+ years engineering; travel required.</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>https://matrixti.com</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>Provides industrial engineering, automation, and systems integration services.</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>Project Management Software, Scheduling Tools</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:15:38 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>BankUnited</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Corporate Governance</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/bankunitedexternal/cx/job-details?reqId=5001200644906</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Miami Lakes, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>2-5 years in project coordination or similar role; experience in regulated/structured environment a plus; strong PowerPoint/Excel; detail-oriented; strong communication.</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>https://bankunited.com</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Provides commercial and consumer banking and financial services.</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>PowerPoint, Excel</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:03:58 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Benecard Services</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Project Manager, Enterprise Programs</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=a72298ea-3808-4935-a1ac-07d4d323bbbc&amp;jobId=590924</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Mechanicsburg or Bonita Springs</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2+ years PM experience; high school diploma; strong communication; MS Office; ability to define requirements; manage scope, timelines, risks; on-site in FL or PA.</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>https://benecard.com</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Provides prescription and vision health benefit management services.</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Microsoft Office, JIRA, SharePoint</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:51:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Alert Alarm Hawaii</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>SRP Project Manager (Maui)</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>https://alertalarm.breezy.hr/p/9533f7556d07-srp-project-manager-maui</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Wailuku, Hawaii, United States</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>$83k-$83k/yr, $39-$39/hr</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Manage medium to large-scale commercial security system projects; oversee staff, budgets, schedules, quality and safety; travel within Hawaii.</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>https://alertalarmhawaii.com</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Provides security and fire safety solutions across the Hawaiian islands.</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Microsoft Office, MS Project</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:45:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>O'Connell Electric Company</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>https://www.oconnellelectric.com/careers-apply?gh_jid=6004579004</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Syracuse, New York, United States</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>$70k-$87k/yr, $33-$41/hr</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Two or more years of experience supporting management functions for construction projects; associates degree preferred; driver’s license required; proficient with MS Office and project software.</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr"/>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Full-service electrical contractor for construction and utility infrastructure projects.</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Microsoft Office, MS Project, Procore, Primavera P6, Accubid estimating software, Cloud tools</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:32:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Comfort Systems of Montana</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HVAC Commercial New Construction Project Manager </t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>https://comfortsystemsofmt.betterteam.com/hvac-commercial-new-construction-project-manager</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Bozeman, Montana, United States</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>$70k-$100k/yr, $33-$48/hr</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Manage planning, coordination, and execution of HVAC installations; 1-3 years PM experience; organize, communicate, vendor management.</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>https://comfortsystemsofmt.com</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Local HVAC contractor providing installation and repair services.</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Wrightsoft, Estimating</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:19:43 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>ByVerTek</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=74ed8849-59d6-4443-9938-20f1d87fbd45&amp;jobId=568922</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Boca Raton, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree required; strong PM skills; proficient in Word/Excel; telecom or construction experience preferred; CAPM or PMP a plus.</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>https://byvertek.com</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Provides turnkey broadband infrastructure construction and engineering services.</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Pivot Tables, VLOOKUP</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:12:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>829 Studios</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Project Manager, Web</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/829studios/d81b9248-5a7c-4bd3-ba9b-5034d45b2b34</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>$70k-$75k/yr, $33-$36/hr</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>3 years of PM experience, agency experience preferred; expertise in website development processes; cross-functional collaboration; client-facing; proficient with Google Workspace, design tools (Figma), and project management tools (ClickUp).</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>https://829studios.com</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Integrated digital marketing agency providing data-driven strategy and web development.</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>WordPress, Drupal, Shopify, Google Workspace, Figma, ClickUp</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:41:42 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>American Restoration</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=edd4d11c-3bc4-45e9-9e68-1078ed7e65e1&amp;jobId=579328</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Nashville, Tennessee, United States</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>$60k-$75k/yr, $28-$36/hr</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>2+ years in construction/restoration/remodeling; proven project management and supervisory experience; driver’s license required; IICRC certification preferred.</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>https://amrestoration.com</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Provides property damage restoration and reconstruction services.</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:35:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Apex Companies</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Associate Project Manager</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/apexcompanies/jobs/5229070008</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Miami, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>BS in geology/hydrogeology/environmental science/engineering; 4+ years environmental field experience; P.G./P.E. preferred; Florida familiarity; 40-hour HAZWOPER preferred; valid driver's license.</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>https://apexcos.com</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Provides environmental consulting, civil engineering, and water infrastructure services.</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:29:16 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Zeta Global</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/zetaglobal/jobs/5985580004</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Nashville, Tennessee, United States</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>$125k-$140k/yr, $60-$67/hr</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>3–6+ years in technical project/program management; cross-functional leadership; strong communication; stakeholder management; experience with system integrations and data flows.</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Provides an AI-powered marketing platform for enterprise customer engagement.</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:52:03 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Element U.S. Space &amp; Defense</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Project Manager II</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=4072bebf-da88-4780-99d3-f63c2d2fb582&amp;jobId=544924</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Camden, Arkansas, United States</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Manages multiple customer projects; ensures on-time, on-budget delivery; strong customer engagement; requires 3+ years PM experience.</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>https://elementdefense.com</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Testing and evaluation services for space and defense industries.</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>MS Office, ERP, Project Scheduling Software</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:32:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Knight Electric</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Electrical Project Manager - Southeast</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>https://jobs.gem.com/knight-electric-inc-/am9icG9zdDqaBO5XvvxvFmcClQ81UUKp</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Atlanta or Alpharetta</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>$125k-$150k/yr, $60-$72/hr</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2+ years in electrical project management; experience with commercial electrical projects; travel up to 50%; proficient in Bluebeam or Procore; valid driver’s license; background check required.</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>https://knightelectricinc.com</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Provides electrical contracting and lighting services for commercial retail projects.</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Bluebeam, Procore, Microsoft Excel, MS Office</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:54:21 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Project Manager II, GEMS, NA Startup</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10428279/project-manager-ii-gems-na-startup</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Austin or Boston or Austin or Nashville or Bellevue or Arlington or New York or Irving</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>$66k-$142k/yr, $31-$68/hr</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; 3+ years program or project management; MS Office; data-driven; cross-functional teamwork.</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>https://amazon.com</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Global online retail and cloud computing technology provider.</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Data Analysis Tools</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Project Manager II, GEMS, NA Startup</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10428280/project-manager-ii-gems-na-startup</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Austin, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>$74k-$129k/yr, $35-$62/hr</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>3+ years program or project management; Bachelor's degree; MS Office; data-driven; cross-functional experience.</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>https://amazon.com</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Global online retail and cloud computing technology provider.</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Data analysis tools</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>B&amp;D Industries</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>https://banddindustries.applicantstack.com/x/detail/a2kyz9j1j6sj</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Albany, New York, United States</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>Assist planning, scheduling, cost tracking, risk management, and coordination for construction projects; requires 2+ years experience, associate degree, PM certification desired.</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>https://banddindustries.com</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Provides electrical, plumbing, and HVAC services for industrial properties.</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>BIM, 3D Construction, Trimble, QA Program, Safety Plan</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Santa Cruz City Schools</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager Construction &amp; Facilities - 40 Hours - 12 Months </t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>https://www.edjoin.org/Home/JobPosting/2227748</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Santa Cruz, California, United States</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>Three years supervisory-level experience in DSA construction and facilities projects; bachelor’s degree or related experience with substitution rules.</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>https://sccs.net</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Operates public K-12 schools in Santa Cruz, California.</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>TriMark USA</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager </t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/trimarkusa/candidateportal/jobs/25793</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Irvine, California, United States</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>$73k-$91k/yr, $35-$43/hr</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2-4 years PM experience; Bachelor's degree or equivalent; foodservice/distribution experience preferred; background check.</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>https://trimarkusa.com</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Distributes commercial kitchen equipment and provides foodservice design services.</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>TriMark USA</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/trimarkusa/candidateportal/jobs/25760</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Winston-Salem or Knoxville</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Coordinate projects, manage purchasing, input orders, track POs, and support project team.</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>https://trimarkusa.com</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Distributes commercial kitchen equipment and provides foodservice design services.</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>MS Word, MS Excel, MS Outlook, ERP system</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>TriMark USA</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/trimarkusa/candidateportal/jobs/25748</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Albany, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Coordinate projects, manage logistics, and support project team; strong admin skills; hybrid work in Albany, GA</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Full Time, Contract, Internship, Temporary, Part Time, Seasonal, Volunteer</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>https://trimarkusa.com</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Distributes commercial kitchen equipment and provides foodservice design services.</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>TriMark USA</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/trimarkusa/candidateportal/jobs/25752</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Albany or Knoxville or Tampa</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>1-2 years admin/coordinator experience; HS diploma; construction industry experience preferred; background check after offer.</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>https://trimarkusa.com</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Distributes commercial kitchen equipment and provides foodservice design services.</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>MS Word, MS Excel, Outlook, ERP system</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>PBS Systems</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Automotive Project Manager</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/pbssystems/candidateportal/jobs/10561</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Arlington, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>1-3 years in automotive dealership or auto industry; knowledge of SDLC and PM processes; strong MS Office skills; ability to travel Canada/USA up to 2 weeks per month.</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Full Time, Temporary, Contract, Internship, Seasonal, Volunteer</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>https://pbssystems.com</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Provides integrated dealership management software for automotive retailers.</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Office Suite</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Great Northern Corporation</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Assembly/Fulfillment Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/gnc/candidateportal/jobs/10023</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>$49k-$68k/yr, $24-$33/hr</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Coordinate assembly and fulfillment, schedule management, quality inspections, ERP usage, lean manufacturing, SOPs.</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>https://greatnortherncorp.com</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Manufactures sustainable paper-based packaging and retail display solutions.</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>ERP system, Excel, Word, Outlook</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>PBS Systems</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Automotive Project Manager</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/pbssystems/103772/jobs/10557</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Arlington, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>1-3 years in automotive dealership; solid SDLC knowledge; strong MS Office; willing to travel Canada/USA up to 2 weeks per month; high school diploma; PMP is a strong asset.</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>https://pbssystems.com</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Provides integrated management software for automotive dealerships.</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Microsoft Office Suite</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Korn Ferry</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Project Coordinator, Executive Search (West Coast)</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>https://kornferry.tal.net/vx/mobile-0/appcentre-ext/brand-4/candidate/so/pm/1/pl/3/opp/26439-Project-Coordinator-Executive-Search-West-Coast/en-GB?instant=apply</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Coordinate executive-search engagements; admin support; travel planning; client interaction; MS Office proficiency; Salesforce experience a plus.</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>https://kornferry.com</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Global organizational consulting and talent management firm.</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Salesforce, PowerPoint, Word, Excel, Searcher Express</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Korn Ferry</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Project Coordinator, Executive Search</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>https://kornferry.tal.net/vx/mobile-0/appcentre-ext/brand-4/candidate/so/pm/1/pl/3/opp/26440-Project-Coordinator-Executive-Search/en-GB?instant=apply</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>Project coordination experience; strong communication, scheduling, and document management skills; proficient with Word, Excel, PowerPoint; experience with Salesforce preferred.</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>https://kornferry.com</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Global organizational consulting and talent management firm.</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Word, Excel, PowerPoint, Salesforce</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Diversified Maintenance</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Project Manager - Janitorial</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>https://diversifiedm-aus.icims.com/jobs/1598839/project-manager---janitorial/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Raleigh, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>Must have 3+ years operational janitorial experience; 2+ years management; English fluency; strong communication; ability to lead and multitask.</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>https://diversifiedm.com</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Provides commercial janitorial and facilities maintenance services.</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Diversified Maintenance</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Project Manager - Janitorial</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>https://diversifiedm-aus.icims.com/jobs/1598842/project-manager---janitorial/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Raleigh, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>High school diploma; 2+ years management; 3+ years operational janitorial experience; English proficiency; multitasking; customer service; leadership.</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>https://diversifiedm.com</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Provides commercial janitorial and facilities maintenance services.</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>The Cook &amp; Boardman Group</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/cookboardman/candidateportal/jobs/17516</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Birmingham or Birmingham</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>Proficient with Microsoft Office; basic computer skills; must pass background check and drug screen.</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>https://cookandboardman.com</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Distributes architectural doors and provides integrated security solutions.</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel, Word, Outlook</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Allied Universal</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Project Manager - Janitorial</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>https://aujscareers-aus.icims.com/jobs/1599283/project-manager---janitorial/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Tucson, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>$60k-$60k/yr, $29-$29/hr</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2 years housekeeping management experience; bilingual Spanish/English; strong customer service; proficient in Excel, Word, PowerPoint.</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>https://aus.com</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Provides professional security guarding and facility maintenance services.</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Excel, Word, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Quanta Services</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager - Mission Critical - Colorado Springs</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>https://careers-quanta.icims.com/jobs/15803/assistant-project-manager---mission-critical---colorado-springs/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Aurora or Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>$80k-$125k/yr, $38-$60/hr</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>Supports project planning, coordination, scheduling, cost tracking, and documentation for mission-critical electrical projects.</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>https://quantaservices.com</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Specialized infrastructure solutions for energy and utility industries.</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Procore, Bluebeam, Accubid</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Quanta Services</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Project Manager - Mission Critical - Colorado Springs</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>https://careers-quanta.icims.com/jobs/15804/project-manager---mission-critical---colorado-springs/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Aurora, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>$102k-$158k/yr, $49-$76/hr</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>Lead planning, execution, and delivery of mission-critical electrical projects; manage schedule, resources, and budget; ensure quality and safety.</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>https://quantaservices.com</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Specialized infrastructure solutions for energy and utility industries.</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Procore, Bluebeam, Accubid, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Quanta Services</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager - Mission Critical</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>https://careers-quanta.icims.com/jobs/15798/assistant-project-manager---mission-critical/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Cheyenne, Wyoming, United States</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>Assist in planning, coordinating, and executing mission-critical electrical projects; strong communication and safety focus.</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>https://quantaservices.com</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Specialized infrastructure solutions for energy and utility industries.</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Microsoft Office Suite, Procore, Bluebeam, Accubid</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Quanta Services</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Project Manager - Civil</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>https://careers-quanta.icims.com/jobs/15792/project-manager---civil/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Coalville, Utah, United States</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Lead and manage civil construction projects across the western U.S.; manage scope, schedule, budget, and client relationships.</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>https://quantaservices.com</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Specialized infrastructure solutions for energy and utility industries.</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Project Manager Intern - Harrisburg</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>https://careers-emcorgroup.icims.com/jobs/50130/project-manager-intern---harrisburg/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Harrisburg, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>Pursuing a Bachelor’s degree in Construction Management or related field; high school diploma or GED; knowledge of sprinkler systems; advanced MS Office skills; MS Project experience a plus.</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Full Time, Internship</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>https://mecojax.com</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Provides electrical and technology infrastructure construction and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Microsoft Office, MS Projects, Sprinkler systems knowledge</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Project Manager Trainee</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>https://careers-emcorgroup.icims.com/jobs/50107/project-manager-trainee/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Fremont, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Trainee program for Project Manager with degree in construction/engineering; strong MS Office; scheduling experience preferred.</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>https://mecojax.com</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Provides electrical and technology infrastructure construction and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Microsoft Office, MS Project, Scheduling software</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>https://careers-emcorgroup.icims.com/jobs/50115/project-manager/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Plain City, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>High school diploma or GED; 3-5 years electrical construction experience; proficient in Microsoft Office; familiar with Accubid, AutoCAD, Revit; familiarity with PM/document control software.</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>https://mecojax.com</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Provides electrical and technology infrastructure construction and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Accubid, AutoCAD, Revit, Project management/document control software</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Project Manager Intern - Reading</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>https://careers-emcorgroup.icims.com/jobs/50131/project-manager-intern---reading/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Reading, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>High School or GED; enrolled full-time in a Bachelor's program (Construction Management or similar) as a junior or higher; knowledge of sprinkler systems; proficient in Microsoft Office; MS Projects a plus.</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>https://mecojax.com</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Provides electrical and technology infrastructure construction and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Microsoft Office, MS Project</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Prime Healthcare</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>https://careers-primehealthcare.icims.com/jobs/263889/project-manager/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Ontario, California, United States</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>$51k-$112k/yr, $24-$54/hr</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>Two+ years of project management experience; healthcare/revenue cycle knowledge preferred; bachelor’s degree preferred.</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>https://primehealthcare.com</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Operates community hospitals and provides healthcare services.</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>TI Communities</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Project Manager, Technical Solutions - Dallas, TX</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>http://ticommunities.hrmdirect.com/employment/view.php?req=3722569</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Dallas or Irving</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>3+ years PM experience; Bachelor's degree; manage technology/IT infra projects; Agile/Waterfall; vendor management; strong communication.</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>https://ticommunities.com</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Manages and enhances workforce housing with resident enrichment programs.</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>Smartsheet, Asana, Agile, Waterfall, Project Management</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Hausmann Construction</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Project Coordinator / Administrative Assistant - Kansas City</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>http://hausmann.hrmdirect.com/employment/view.php?req=3722394</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Kansas City, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>Support project management with contract prep, compliance tracking, and administrative tasks; experience with construction software preferred.</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>https://hausmannconstruction.com</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>General contractor providing construction management and design-build services.</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Procore, Sage Software</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>State of Minnesota</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Information Technology Spec 3 - Project Manager</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>https://careers.mn.gov/psc/mnjobacc/MNCAREERSACCESSIBLE/HRCR/c/HRS_HRAM_FL.HRS_CG_SEARCH_FL.GBL?Page=HRS_APP_JBPST_FL&amp;Action=U&amp;FOCUS=Applicant&amp;SiteId=1002&amp;JobOpeningId=94427&amp;PostingSeq=1</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Bloomington, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>$69k-$114k/yr, $33-$54/hr</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>Three years of progressive IT project management experience; strong planning, communication, and relationship-building skills; bachelor’s degree or PM certifications preferred.</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>https://mn.gov</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Minnesota state government entity providing essential public services.</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>MS Project, Smartsheet, Jira</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Ben Quie &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Residential Remodeling Project Manager</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>https://benquieandsons.applicantpro.com/jobs/4097220</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>St Paul, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>$85k-$95k/yr, $40-$45/hr</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>3-7 years of residential construction or project management; strong scheduling, budgeting, field coordination, and client communication.</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>https://benquieandsons.com</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>Provides design-build remodeling and historic home restoration services.</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>JobTread, Microsoft Office, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>HJD Capital</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Electrical Project Manager</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>https://hjdcapital.applicantpool.com/jobs/1304901</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>$85k-$125k/yr, $40-$60/hr</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>Proven experience as an electrical project manager with blueprint literacy and strong negotiation skills.</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>https://hjdcapital.com</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Provider of electrical, utility, and general construction services.</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>MS Office, MS Project, Bluebeam, Spreadsheets</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Golden Star Technology</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>IT/AV Project Manager</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>https://gstinc.applicantpro.com/jobs/4097177</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Cerritos, California, United States</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>$45k-$75k/yr, $21-$36/hr</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>Minimum three years in enterprise project management; PMP certification preferred; strong MS Office; excellent client communication; IT/AV project experience.</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>https://gstinc.com</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Provides integrated IT, audiovisual, and managed technology solutions.</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Gaming Capital Group</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Technical Project Coordinator  (OK, Newcastle)</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>https://recruiting.myapps.paychex.com/appone/MainInfoReq.asp?R_ID=7157391&amp;B_ID=91&amp;fid=1&amp;SearchScreenID=13402&amp;ssbgcolor=#FFFFFF</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Newcastle, Oklahoma, United States</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>Coordinate technical projects; assist game performance analysts; produce CAD drawings; data entry and compliance checks.</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>https://gamingcapitalgroup.com</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Financing and maintaining electronic gaming equipment for casinos.</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Tailwind Voice &amp; Data</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager </t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>https://tailwindvoiceanddata.bamboohr.com/careers/160</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Minnetonka, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>$65k-$80k/yr, $31-$38/hr</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>Experienced project manager with 3+ years in infrastructure/telecom projects; strong communication; ability to manage budgets, schedules, and client relationships.</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr"/>
+      <c r="M727" t="inlineStr"/>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>John McNeil Studio</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>https://johnmcneilstudio.bamboohr.com/careers/162</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Berkeley, California, United States</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>$90k-$120k/yr, $43-$57/hr</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>Senior-level project leadership with strong client, team coordination, budgeting, and schedule management; excellent communication and organization.</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>https://johnmcneilstudio.com</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Provides integrated branding, design, and creative production services.</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Turner Construction</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Interiors Project Manager - (New York City)</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>https://turnerconstruction.csod.com/ux/ats/careersite/1/home/requisition/20259?c=Turnerconstruction</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
         <is>
           <t>New York, New York, United States</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr">
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>$135k-$170k/yr, $64-$81/hr</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>Manage interiors projects, develop plans, lead meetings, ensure safety and budgets, and pursue business development.</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>https://turnerconstruction.com</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Manages and constructs large-scale commercial and infrastructure projects.</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Turner Construction</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Interiors Project Manager - (New York City)</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>https://turnerconstruction.csod.com/ux/ats/careersite/1/home/requisition/20259?c=turnerconstruction</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>$135k-$170k/yr, $64-$81/hr</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>Manage daily project activities and lead business development for Interiors Division; oversee safety and quality across multiple projects.</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>https://turnerconstruction.com</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>Constructs and manages large-scale commercial and infrastructure buildings.</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>IMI</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Steel Construction Project Coordinator-NOT REMOTE</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>https://imi.bamboohr.com/careers/163</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Sedalia, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>$80k-$100k/yr, $38-$48/hr</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>Experienced project coordinator with strong organizational and communication skills; proficient in coordinating drawings, submittals, RFIs, and change orders; knowledge of Tekla (ERP) and safety compliance.</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>https://imi-inc.com</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Fabricates and installs structural steel and miscellaneous metal products.</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Tekla, ERP, MS Office</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>One Hat One Hand</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>https://onehatonehand.bamboohr.com/careers/81</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
         <is>
           <t>3+ YOE</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr">
+      <c r="G732" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I635" t="inlineStr">
-        <is>
-          <t>$72k-$85k/yr, $34-$40/hr</t>
-        </is>
-      </c>
-      <c r="J635" t="inlineStr">
-        <is>
-          <t>Bachelor's in science/cosmetics, 3-5 years in PM or product development, fragrance industry experience preferred, Wrike/ClickUp experience preferred.</t>
-        </is>
-      </c>
-      <c r="K635" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L635" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M635" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N635" t="inlineStr">
-        <is>
-          <t>Wrike, ClickUp</t>
-        </is>
-      </c>
-      <c r="O635" t="inlineStr">
-        <is>
-          <t>2026-05-22 09:16:51 AM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>ClimeCo LLC - Project Coordinator- IT</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4193323</t>
-        </is>
-      </c>
-      <c r="D636" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E636" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F636" t="inlineStr">
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>$95k-$110k/yr, $45-$52/hr</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>Project management with design sensibility; experience in interior design/architecture/event production; Rhino 3D modeling; read/redline architectural drawings.</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>https://onehatonehand.com</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Design and fabrication for public art and architectural spaces.</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Rhino, Adobe Creative Suite, Bluebeam, Asana, Instagantt, GSuite, Procore</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Fessler &amp; Bowman</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Project Manager </t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>https://fesslerbowman.bamboohr.com/careers/885</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Raleigh, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
         <is>
           <t>3+ YOE</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="H636" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I636" t="inlineStr">
-        <is>
-          <t>$65k-$75k/yr, $31-$36/hr</t>
-        </is>
-      </c>
-      <c r="J636" t="inlineStr">
-        <is>
-          <t>3+ years IT project coordination; remote work; strong PM tool skills; SDLC familiarity.</t>
-        </is>
-      </c>
-      <c r="K636" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L636" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M636" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N636" t="inlineStr">
-        <is>
-          <t>Jira, Confluence, Asana, Monday.com, Notion, Basecamp</t>
-        </is>
-      </c>
-      <c r="O636" t="inlineStr">
-        <is>
-          <t>2026-05-22 08:43:18 AM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>Bachelor's in Construction Management or equivalent; 3+ years construction experience; basic civil construction knowledge; strong communication and organizational skills; familiarity with Procore and MS Project.</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>https://fesslerbowman.com</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Specializing in commercial concrete and civil earthwork services.</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Procore, Microsoft Project, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Batchelor &amp; Kimball</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>https://pridestaff.phenompro.com/us/en/job/574807/Assistant-Project-Manager</t>
-        </is>
-      </c>
-      <c r="D637" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr">
-        <is>
-          <t>Tuscaloosa, Alabama, United States</t>
-        </is>
-      </c>
-      <c r="F637" t="inlineStr">
-        <is>
-          <t>Entry Level (0+ YOE)</t>
-        </is>
-      </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H637" t="inlineStr">
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>https://bkimechanical.bamboohr.com/careers/407</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Birmingham, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
         <is>
           <t>Entry Level</t>
         </is>
       </c>
-      <c r="I637" t="inlineStr">
-        <is>
-          <t>$41k-$52k/yr, $20-$25/hr</t>
-        </is>
-      </c>
-      <c r="J637" t="inlineStr">
-        <is>
-          <t>0–4 years in construction/mechanical projects; degree preferred in CM/Engineering; strong organization and communication; proficient with MS Office and PM software.</t>
-        </is>
-      </c>
-      <c r="K637" t="inlineStr">
-        <is>
-          <t>Temporary, Temporary, Temporary</t>
-        </is>
-      </c>
-      <c r="L637" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M637" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N637" t="inlineStr">
-        <is>
-          <t>Project Management Software, Microsoft Excel, Microsoft Word, Isometrics Interpretation, ASME Codes, BIM/VDC, Quality Control Documentation</t>
-        </is>
-      </c>
-      <c r="O637" t="inlineStr">
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>$70k-$80k/yr, $33-$38/hr</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>Entry-level to mid-level construction project support; manage schedules, budgets, docs; travel to Birmingham, AL; proficient with MS Projects.</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>https://bkimechanical.com</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Mechanical and plumbing construction for complex commercial facilities.</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Microsoft Office, Excel, Word</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>Junior Project Manager</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>https://yellowstone.recruitee.com/o/junior-project-manager-4</t>
-        </is>
-      </c>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr">
-        <is>
-          <t>St. Clair Shores, Michigan, United States</t>
-        </is>
-      </c>
-      <c r="F638" t="inlineStr">
-        <is>
-          <t>Entry Level (0+ YOE)</t>
-        </is>
-      </c>
-      <c r="G638" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H638" t="inlineStr">
-        <is>
-          <t>Entry Level</t>
-        </is>
-      </c>
-      <c r="I638" t="inlineStr">
-        <is>
-          <t>$68k-$68k/yr, $32-$32/hr</t>
-        </is>
-      </c>
-      <c r="J638" t="inlineStr">
-        <is>
-          <t>Construction experience minimal; strong reading of drawings; Procore/Bluebeam/Microsoft Project skills; valid license and vehicle.</t>
-        </is>
-      </c>
-      <c r="K638" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L638" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M638" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N638" t="inlineStr">
-        <is>
-          <t>Procore, Bluebeam, Microsoft Project, Microsoft Excel, Microsoft Word</t>
-        </is>
-      </c>
-      <c r="O638" t="inlineStr">
-        <is>
-          <t>2026-05-21 08:53:28 AM CDT</t>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Forté Specialty Contractors</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>https://fortedesignbuild.bamboohr.com/careers/89</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>$80k-$90k/yr, $38-$43/hr</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>2+ years framing/drywall experience; bachelor's degree preferred and may substitute for experience; Procore and scheduling software experience; strong communication; luxury construction experience preferred.</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>https://fortedesignbuild.com</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Builds luxury residential estates and themed experiential commercial spaces.</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Procore, Project Scheduling Software</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O735"/>
+  <dimension ref="A1:O768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46647,11 +46647,7 @@
           <t>Independent health science consultancy providing medical communication services.</t>
         </is>
       </c>
-      <c r="N642" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N642" t="inlineStr"/>
       <c r="O642" t="inlineStr">
         <is>
           <t>2026-05-22 06:05:43 PM CDT</t>
@@ -47494,11 +47490,7 @@
           <t>Finances, builds, and operates sustainable energy and resource infrastructure.</t>
         </is>
       </c>
-      <c r="N653" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N653" t="inlineStr"/>
       <c r="O653" t="inlineStr">
         <is>
           <t>2026-05-22 02:29:08 PM CDT</t>
@@ -47891,11 +47883,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A659" t="inlineStr"/>
       <c r="B659" t="inlineStr">
         <is>
           <t>Associate Project Manager</t>
@@ -47946,16 +47934,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L659" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M659" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr"/>
       <c r="N659" t="inlineStr">
         <is>
           <t>MS Project, Smartsheet, PMIS, Microsoft Office Suite</t>
@@ -47968,11 +47948,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A660" t="inlineStr"/>
       <c r="B660" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48023,16 +47999,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L660" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M660" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr"/>
       <c r="N660" t="inlineStr">
         <is>
           <t>Primavera, Budgeting tools</t>
@@ -48045,11 +48013,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A661" t="inlineStr"/>
       <c r="B661" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -48100,16 +48064,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L661" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M661" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr"/>
       <c r="N661" t="inlineStr">
         <is>
           <t>Microsoft Office, PowerBI, SharePoint, Excel</t>
@@ -48122,11 +48078,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A662" t="inlineStr"/>
       <c r="B662" t="inlineStr">
         <is>
           <t>Project Manager Autonomous Vehicles</t>
@@ -48177,16 +48129,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M662" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr"/>
       <c r="N662" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, Excel</t>
@@ -48199,11 +48143,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A663" t="inlineStr"/>
       <c r="B663" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48254,16 +48194,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L663" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M663" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr"/>
       <c r="N663" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Word, Microsoft Visio, MS Project, MS Office</t>
@@ -48276,11 +48208,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A664" t="inlineStr"/>
       <c r="B664" t="inlineStr">
         <is>
           <t>Software Project Manager</t>
@@ -48331,16 +48259,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L664" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M664" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr"/>
       <c r="N664" t="inlineStr">
         <is>
           <t>Microsoft Office, Microsoft Project, SQL Server, Oracle</t>
@@ -48353,11 +48273,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A665" t="inlineStr"/>
       <c r="B665" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48408,21 +48324,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L665" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M665" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N665" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr"/>
+      <c r="N665" t="inlineStr"/>
       <c r="O665" t="inlineStr">
         <is>
           <t>2026-05-22 01:41:19 PM CDT</t>
@@ -48430,11 +48334,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A666" t="inlineStr"/>
       <c r="B666" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48485,16 +48385,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L666" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M666" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr"/>
       <c r="N666" t="inlineStr">
         <is>
           <t>Asana, Monday, ClickUp, Excel, Google Workspace</t>
@@ -48507,11 +48399,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A667" t="inlineStr"/>
       <c r="B667" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48562,21 +48450,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L667" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M667" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N667" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr"/>
+      <c r="N667" t="inlineStr"/>
       <c r="O667" t="inlineStr">
         <is>
           <t>2026-05-22 01:41:19 PM CDT</t>
@@ -48584,11 +48460,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A668" t="inlineStr"/>
       <c r="B668" t="inlineStr">
         <is>
           <t>Operations Project Manager</t>
@@ -48639,16 +48511,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L668" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M668" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr"/>
       <c r="N668" t="inlineStr">
         <is>
           <t>Project management software, Automation tools</t>
@@ -48661,11 +48525,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A669" t="inlineStr"/>
       <c r="B669" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48716,16 +48576,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L669" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M669" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr"/>
       <c r="N669" t="inlineStr">
         <is>
           <t>Procore, Microsoft Project</t>
@@ -48803,11 +48655,7 @@
           <t>Provides project management and owner representation for construction projects.</t>
         </is>
       </c>
-      <c r="N670" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N670" t="inlineStr"/>
       <c r="O670" t="inlineStr">
         <is>
           <t>2026-05-22 01:39:30 PM CDT</t>
@@ -48815,11 +48663,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A671" t="inlineStr"/>
       <c r="B671" t="inlineStr">
         <is>
           <t>Project Coordinator, Corporate Relations</t>
@@ -48870,16 +48714,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L671" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M671" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr"/>
       <c r="N671" t="inlineStr">
         <is>
           <t>Microsoft Office, Salesforce (CRM), Database and document management systems</t>
@@ -48892,11 +48728,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A672" t="inlineStr"/>
       <c r="B672" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -48947,16 +48779,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L672" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M672" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr"/>
       <c r="N672" t="inlineStr">
         <is>
           <t>CRM software, Project management software</t>
@@ -48969,11 +48793,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A673" t="inlineStr"/>
       <c r="B673" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -49024,16 +48844,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L673" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M673" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr"/>
       <c r="N673" t="inlineStr">
         <is>
           <t>Microsoft Office, Acumatica ERP, Stack, Estimating Software</t>
@@ -49046,11 +48858,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A674" t="inlineStr"/>
       <c r="B674" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -49101,16 +48909,8 @@
           <t>Contract</t>
         </is>
       </c>
-      <c r="L674" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M674" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr"/>
       <c r="N674" t="inlineStr">
         <is>
           <t>ERP, Project Management Tools, SIT, UAT</t>
@@ -49123,11 +48923,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A675" t="inlineStr"/>
       <c r="B675" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -49178,16 +48974,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L675" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M675" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr"/>
       <c r="N675" t="inlineStr">
         <is>
           <t>AutoCAD</t>
@@ -49265,11 +49053,7 @@
           <t>Provides essential public services and administration for local residents.</t>
         </is>
       </c>
-      <c r="N676" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N676" t="inlineStr"/>
       <c r="O676" t="inlineStr">
         <is>
           <t>2026-05-22 01:22:46 PM CDT</t>
@@ -50258,11 +50042,7 @@
           <t>Provides property damage restoration and reconstruction services.</t>
         </is>
       </c>
-      <c r="N689" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N689" t="inlineStr"/>
       <c r="O689" t="inlineStr">
         <is>
           <t>2026-05-22 10:35:00 AM CDT</t>
@@ -50408,11 +50188,7 @@
           <t>Provides an AI-powered marketing platform for enterprise customer engagement.</t>
         </is>
       </c>
-      <c r="N691" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N691" t="inlineStr"/>
       <c r="O691" t="inlineStr">
         <is>
           <t>2026-05-22 09:52:03 AM CDT</t>
@@ -50870,11 +50646,7 @@
           <t>Operates public K-12 schools in Santa Cruz, California.</t>
         </is>
       </c>
-      <c r="N697" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N697" t="inlineStr"/>
       <c r="O697" t="inlineStr">
         <is>
           <t>2026-05-22 02:00:00 AM CDT</t>
@@ -50947,11 +50719,7 @@
           <t>Distributes commercial kitchen equipment and provides foodservice design services.</t>
         </is>
       </c>
-      <c r="N698" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N698" t="inlineStr"/>
       <c r="O698" t="inlineStr">
         <is>
           <t>2026-05-22 02:00:00 AM CDT</t>
@@ -51101,11 +50869,7 @@
           <t>Distributes commercial kitchen equipment and provides foodservice design services.</t>
         </is>
       </c>
-      <c r="N700" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N700" t="inlineStr"/>
       <c r="O700" t="inlineStr">
         <is>
           <t>2026-05-21 11:00:00 PM CDT</t>
@@ -51640,11 +51404,7 @@
           <t>Provides commercial janitorial and facilities maintenance services.</t>
         </is>
       </c>
-      <c r="N707" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N707" t="inlineStr"/>
       <c r="O707" t="inlineStr">
         <is>
           <t>2026-05-21 11:00:00 PM CDT</t>
@@ -51717,11 +51477,7 @@
           <t>Provides commercial janitorial and facilities maintenance services.</t>
         </is>
       </c>
-      <c r="N708" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N708" t="inlineStr"/>
       <c r="O708" t="inlineStr">
         <is>
           <t>2026-05-21 11:00:00 PM CDT</t>
@@ -52179,11 +51935,7 @@
           <t>Specialized infrastructure solutions for energy and utility industries.</t>
         </is>
       </c>
-      <c r="N714" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N714" t="inlineStr"/>
       <c r="O714" t="inlineStr">
         <is>
           <t>2026-05-21 11:00:00 PM CDT</t>
@@ -52564,11 +52316,7 @@
           <t>Operates community hospitals and provides healthcare services.</t>
         </is>
       </c>
-      <c r="N719" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N719" t="inlineStr"/>
       <c r="O719" t="inlineStr">
         <is>
           <t>2026-05-21 11:00:00 PM CDT</t>
@@ -53249,11 +52997,7 @@
           <t>Provides integrated branding, design, and creative production services.</t>
         </is>
       </c>
-      <c r="N728" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N728" t="inlineStr"/>
       <c r="O728" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
@@ -53326,11 +53070,7 @@
           <t>Manages and constructs large-scale commercial and infrastructure projects.</t>
         </is>
       </c>
-      <c r="N729" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N729" t="inlineStr"/>
       <c r="O729" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
@@ -53403,11 +53143,7 @@
           <t>Constructs and manages large-scale commercial and infrastructure buildings.</t>
         </is>
       </c>
-      <c r="N730" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N730" t="inlineStr"/>
       <c r="O730" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
@@ -53794,6 +53530,2539 @@
         </is>
       </c>
       <c r="O735" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Hy-Tek Intralogistics</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883d07f5232ae017f8a495c5012e6&amp;id=8a78839f9e46f5dc019e51394c3b4097&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>Oversees multiple projects, manages scope, schedule, resources, budgets, risks, and stakeholder communications.</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>https://hy-tek.com</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Integrator of warehouse automation and material handling systems.</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>AutoCAD, Microsoft Office, Project, Teams, SharePoint</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:17:40 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>BCH Mechanical</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Mechanical Project Manager - RoyalAire Mechanical</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883d06abc7c06016ac72b50ca0c00&amp;id=8a7887a19e46f5e2019e515b9bbe47aa</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Tampa, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>1-3 years construction experience on commercial sites; College graduate; Proficient in Microsoft Office and scheduling/construction software (MS Project, PlanGrid, Bluebeam)</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>https://bchmechanical.com</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>Mechanical contractor providing HVAC, plumbing, and piping services.</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Microsoft Office, MS Project, PlanGrid, Bluebeam</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:12:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Tucson Indian Center</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Native Connections Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4196056</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Tucson, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>$40k-$52k/yr, $19-$25/hr</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Coordinate and evaluate the Native Connections Program; build partnerships; deliver trainings; track data and report monthly.</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>https://ticenter.org</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>Providing health, wellness, and social services to Native Americans.</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>MS Office, Data collection tools, ASIST, QPR, Survey tools</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:19:31 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>SPL</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Project Manager – Environmental Lab Services</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4196040</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Conroe, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Science, Business, or related field; 1-2 years client/project management; environmental/lab experience preferred; proficient in MS Office and CRM; LIMS experience preferred.</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>https://spllabs.com</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>Provides laboratory testing and metrology for energy and environmental industries.</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Microsoft Office, CRM, LIMS</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:13:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Gillespie Group</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4195572</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Lansing, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>Assist in development and construction project management, vendor coordination, budgeting, and reporting; 1–3 years experience; associate degree required; MS Office proficiency; driving license; background check.</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>https://gillespie-group.com</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Develops and manages residential and commercial real estate properties.</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:11:57 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Powerhouse</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Commercial Construction</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4195669</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Crowley, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>2+ years experience in large customer interface; construction environment preferred; degree preferred; passing MVR/background/drug tests.</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>https://powerhousenow.com</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>Nationwide facilities maintenance and multi-site enhancement services.</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>2026-05-22 05:41:50 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Northwell Health</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>https://eppr.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/182516</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Manhasset, New York, United States</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>$70k-$116k/yr, $33-$56/hr</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent; 1-3 years of relevant project management experience.</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr"/>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>Provides clinical healthcare services through a hospital network.</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>2026-05-22 05:09:32 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Customer Project Manager - Key Accounts</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>https://careers.se.com/jobs/121240?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Nashville or Chicago or Dallas or Houston or St. Louis or Louisville or Raleigh or Boston or Costa Mesa</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>$101k-$152k/yr, $48-$73/hr</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>Bachelor's in Electrical Engineering with 2+ years PM experience; 25% travel; US-based; CT time zone; PMP desirable; MS Office and Visio; strong communication and teamwork.</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>https://se.com</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>Provider of energy management and industrial automation solutions.</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>MS Office, Visio, Project Management Software</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>2026-05-22 04:45:06 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Ashtel Studios</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Assistant Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3421884</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Ontario, California, United States</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>$49k-$60k/yr, $24-$29/hr</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>2+ years in project coordination, strong communication, organization, multitasking, and proficiency with Monday.com.</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>https://ashtelstudios.com</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>Designs and manufactures personal care and oral care products.</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Monday.com</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>2026-05-22 04:40:14 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Cherokee Federal</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Remote Healthcare IT Project Manager</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>https://ibtcjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/42568</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>$85k-$95k/yr, $40-$45/hr</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>PMP certification required; healthcare IT experience preferred; data transformation and multi-vendor project experience; ability to coordinate subcontractors; must obtain Public Trust clearance.</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>https://cherokee-federal.com</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Provides specialized professional and technical services to federal government agencies.</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>2026-05-22 04:18:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Chicago Housing Authority</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Project Manager, Grants</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>https://fa-ewik-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/1337</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Chicago, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>$75k-$85k/yr, $36-$40/hr</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; 3+ years grant writing; proven grant success; strong writing; research skills; grant management software; able to manage multiple projects; housing or social services preferred.</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>https://thecha.org</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Provides affordable housing and community services for Chicago residents.</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Grants.gov, Microsoft Word, Excel, PowerPoint, Outlook, MS Office</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>2026-05-22 04:09:12 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Project Manager I-Medical Education</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>https://careers.mountsinai.org/jobs/3038265?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>$65k-$98k/yr, $31-$47/hr</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; 3-5+ years in project management or operations; multi-project management; process improvement experience.</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>https://mountsinai.org</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Provides comprehensive hospital, clinical, and medical research services.</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Microsoft Office 365</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>2026-05-22 03:38:43 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Project Manager I-Medical Education</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>https://ejis.fa.us6.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/3038265</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>$65k-$98k/yr, $31-$47/hr</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>Bachelor's degree required; 3-5+ years in PM/operations; strong execution and process improvement; PMP preferred.</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>https://mountsinai.org</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Integrated academic medical system providing patient care and research.</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Microsoft Office 365</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:49:34 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>SynergyBuilt</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3421644</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Nashville, Tennessee, United States</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>Experience in construction or fast-paced operations; strong organizational and communication skills; ability to manage multiple priorities; proficient with systems and documentation; proactive with accountability.</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>https://synergybuilt.net</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Nashville-based general contractor providing full-service renovation and restoration solutions.</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>ERP, CRM, Document Management Systems</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>2026-05-22 02:18:44 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Duval Sign Solutions</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3421575</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Jacksonville, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>$57k-$65k/yr, $27-$31/hr</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>1-2+ years PM experience in signage, construction, or related trades; strong organizational and communication skills; able to manage multiple projects; proficient with Microsoft Office and project tracking systems.</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>https://duvalsignsolutions.com</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Provides custom business signage design, fabrication, and installation services.</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Project tracking software</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:56:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>The Jamar Company</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Field Engineer/Assistant Project Manager - National Operations</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>https://jobs.ourcareerpages.com/job/990933</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Duluth, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>$67k-$101k/yr, $32-$48/hr</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>Technical or bachelor's degree in a related field or 2+ years assisting industrial/commercial projects; strong MS Office and MS Project skills; excellent communication and organizational abilities; travel up to 75%.</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>https://jamarcompany.com</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Specialty contractor providing mechanical, industrial, and architectural building services.</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Microsoft Project, iPad, iPhone</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:55:38 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>City of Atlanta</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Project Manager I</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>https://ehxr.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/33914</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>$68k-$70k/yr, $32-$33/hr</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in related field; at least 3 years in procurement/project management/contract administration/strategic sourcing; master’s degree and certifications preferred.</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>https://atlantaga.gov</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Provides municipal governance and public services for Atlanta residents.</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>ERP software, eProcurement systems</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:26:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Mercy Health Services</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Construction Project Manager I</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>https://careers.mdmercy.com/jobs/15683</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>$64k-$116k/yr, $31-$56/hr</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>BA/BS preferred with PM orientation; 1-5 years in Construction Management or Architecture; strong MS Office; familiarity with project software.</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>https://mdmercy.com</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>Providing hospital, primary, and long-term health care services.</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Office Suite, Project Management Software</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:19:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>SCA Health</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Tech Project Manager</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>https://careers.sca.health/jobs/46621?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>$100k-$120k/yr, $48-$57/hr</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>3-5+ years hands-on project management; experience in waterfall and agile (Scrum/Kanban); PMP preferred; strong communication and leadership; Office 365, Teams, SharePoint, Project experience; ServiceNow a plus; Azure a plus.</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>https://sca.health</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Operator of ambulatory surgery centers and specialty practice clinics.</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Microsoft Office 365, Teams, SharePoint, Project, ServiceNow, Azure</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:00:40 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Ogletree Deakins</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Project Manager - Finance (Immigration Business Unit Support)</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>https://careers.ogletree.com/jobs/6501?lang=en-us</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Greenville, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Business Administration or related field with 4+ years in a law firm or professional services finance; PMP preferred; experience with Aderant and immigration tools; strong communication and client service.</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>https://ogletree.com</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Provides legal representation for management in employment matters.</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Document Management Systems, Aderant, case management systems, Immigration Financial Tool (IFT)</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:49:05 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>IES Holdings</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>https://joinus.ies-co.com/jobs/23054</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Cedar Rapids, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>$90k-$140k/yr, $43-$67/hr</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>High School diploma required; bachelor’s degree preferred; 5+ years supervisory/managerial experience; 5+ years telecommunications/related field; proficient in MS Office; valid driving; ability to manage multiple tasks; able to define and scope projects.</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>https://ies-co.com</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Provider of integrated electrical and technology infrastructure services.</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Microsoft Office (Word, Excel, MS Project), Punch tools, Crimp tools, Krone/3M/BIX, Voltmeter, Testers</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:30:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Wachter</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/wachter/b898656b-03f9-4021-8083-8738b4f91ec8/apply</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Mount Laurel, New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>$0k-$0k/yr, $0-$0/hr</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>PM with 2+ years experience; budgets, schedules, vendor coordination; IT and security project experience preferred.</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr"/>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Integrates technology and electrical systems for businesses nationwide.</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Microsoft Office, ServiceNow</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:16:04 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Prime Healthcare Services</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>https://primehealthcare.jibeapply.com/jobs/263889</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Ontario, California, United States</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>$0k-$0k/yr, $0-$0/hr</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>Two+ years of experience; Bachelor's degree preferred; project management experience preferred; knowledge of healthcare revenue cycle preferred.</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>https://primehealthcare.com</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Prime Healthcare operates a nationwide network of acute care hospitals.</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:29:54 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Project Manager, Construction</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>https://apply-arco.icims.com/jobs/11413/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Canton, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>BS in Construction/Engineering/Architecture with a 3.0 GPA; 3-5 years design/build construction; cold storage experience; proficiency in Word, Excel, Outlook, and Microsoft Project.</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Provides design-build construction for industrial and commercial facilities.</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Word, Excel, Outlook</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:50:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Project Manager, Government Services</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>https://apply-arco.icims.com/jobs/11410/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Riverside, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>BS in Construction/Engineering/Architecture with 3.0+ GPA; 3-5 years design/build experience; cold storage preferred; proficient with Word, Excel, Outlook, MS Project.</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Provides design-build construction for industrial and commercial facilities.</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Word, Excel, Outlook</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:57:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>ARCO Design/Build</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Project Manager, Construction</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>https://apply-arco.icims.com/jobs/11409/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Riverside, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>BS in Construction/Engineering/Architecture; 3-5 years design/build experience; cold storage experience preferred; proficient with MS Office and MS Project.</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>https://arcodb.com</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Provides design-build construction for industrial and commercial facilities.</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Word, Excel, Outlook, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:54:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Paul Davis Restoration</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Project Manager - Construction</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3421110</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Appleton, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>Seasoned construction professional with leadership experience, strong communication, and ability to manage multiple reconstruction projects from start to finish.</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>https://pauldavis.com</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Provides property damage restoration and construction services.</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:49:15 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>CRDN Team Crouch</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3420922</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>North Little Rock, Arkansas, United States</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>$50k-$50k/yr, $24-$24/hr</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>Experience in restoration, insurance claims, or project management; knowledge of Xactimate; strong customer service and communication; ability to manage multiple projects; valid driver’s license and local travel.</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>https://crdntx.com</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Provides contents restoration services for disaster-damaged homes and businesses.</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Xactimate</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:47:14 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>SERVPRO of Alexandria/Marlton/Morningside</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Reconstruction Project Manager - Entry Level</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3420750</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Alexandria, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>$48k-$50k/yr, $23-$24/hr</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>Entry-level Reconstruction Project Manager; HS diploma; construction/coordination experience preferred; strong organizational and communication skills; valid driving record; ability to travel; background check; smartphone required.</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>https://servproalexandriava.com</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>Provides emergency property restoration and professional cleaning services.</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:20:26 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Quanta Services</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Project Manager - Mission Critical</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>https://careers-quanta.icims.com/jobs/15799/project-manager---mission-critical/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Cheyenne, Wyoming, United States</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>Experience leading mission-critical electrical projects; strong planning, scheduling, budgeting, and stakeholder management; willing to travel; data center experience preferred.</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>https://quantaservices.com</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>Specialized infrastructure solutions for energy and utility industries.</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Procore, Bluebeam, Accubid</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Rainbow International of Kanawha and Putnam Counties</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>https://app.careerplug.com/jobs/3420604</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Saint Albans, West Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>$46k-$46k/yr, $22-$22/hr</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>3+ years in construction project management; ability to manage schedules, crews, subcontractors, and budgets; read blueprints; valid driver’s license; OSHA certification preferred.</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>https://rainbowrestoration.com</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>Professional property restoration and cleaning services for damaged homes.</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:47:58 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>BHI</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager- Wireless and Communications</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>https://bhico.applicantpro.com/jobs/4096956</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Provo or Vernal</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>$75k-$80k/yr, $36-$38/hr</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>Construction management degree or equivalent experience; proficient in project management software; understanding of RFIs and Submittals; excellent problem solving and communication; ability to travel or relocate.</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>https://bhico.com</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>General contractor providing multi-disciplinary construction and engineering services.</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Project management software</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Burning Man Project</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Project Manager, Regeneration</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>http://apply.burningman.org/apply/4mUtT2cXND/Project-Manager-Regeneration</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>San Francisco or Reno</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>$98k-$110k/yr, $47-$52/hr</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>3+ years in project management, sustainability, or event production; strong presentation skills; able to manage multiple priorities; data and reporting experience.</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>https://burningman.org</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>Produces the annual Burning Man event in Black Rock City.</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Asana, Google Drive, Google Slides, Google Sheets</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
         </is>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O768"/>
+  <dimension ref="A1:O770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53986,11 +53986,7 @@
           <t>Nationwide facilities maintenance and multi-site enhancement services.</t>
         </is>
       </c>
-      <c r="N741" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N741" t="inlineStr"/>
       <c r="O741" t="inlineStr">
         <is>
           <t>2026-05-22 05:41:50 PM CDT</t>
@@ -54059,11 +54055,7 @@
           <t>Provides clinical healthcare services through a hospital network.</t>
         </is>
       </c>
-      <c r="N742" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N742" t="inlineStr"/>
       <c r="O742" t="inlineStr">
         <is>
           <t>2026-05-22 05:09:32 PM CDT</t>
@@ -55287,11 +55279,7 @@
           <t>Prime Healthcare operates a nationwide network of acute care hospitals.</t>
         </is>
       </c>
-      <c r="N758" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N758" t="inlineStr"/>
       <c r="O758" t="inlineStr">
         <is>
           <t>2026-05-22 11:29:54 AM CDT</t>
@@ -55595,11 +55583,7 @@
           <t>Provides property damage restoration and construction services.</t>
         </is>
       </c>
-      <c r="N762" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N762" t="inlineStr"/>
       <c r="O762" t="inlineStr">
         <is>
           <t>2026-05-22 10:49:15 AM CDT</t>
@@ -55903,11 +55887,7 @@
           <t>Professional property restoration and cleaning services for damaged homes.</t>
         </is>
       </c>
-      <c r="N766" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N766" t="inlineStr"/>
       <c r="O766" t="inlineStr">
         <is>
           <t>2026-05-21 10:47:58 PM CDT</t>
@@ -56065,6 +56045,160 @@
       <c r="O768" t="inlineStr">
         <is>
           <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>NICE</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Client Services Project Manager, CX</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>https://boards.eu.greenhouse.io/nice/jobs/4817745101?gh_jid=4817745101</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>Project management of customer-facing software and AI-enabled delivery projects; 0-4 years PM experience; familiarity with AI, SaaS, Agile; PMP or AI cert a plus.</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>https://nice.com</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>Provides AI-powered software for customer engagement and financial compliance.</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Smartsheet, Jira, MS Project, Salesforce, AI concepts</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:48:06 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Toyota Automated Logistics</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Controls Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/talcareers/cx/job-details?reqId=5001198708706</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Indianapolis or Maryland Heights</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>Experience with MS Office and ERP systems; strong organization and communication; able to analyze data; eligible to work in the USA long term.</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>https://toyota-automated-logistics.com</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Integrated warehouse automation systems, software, and lifecycle services.</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Microsoft Dynamics 365, Power BI, Excel, MS Office Suite</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>2026-05-22 01:44:29 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O770"/>
+  <dimension ref="A1:O771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56202,6 +56202,83 @@
         </is>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Doctors HealthCare Plans</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Quality Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>http://doctorshealthcareplansinc.applytojob.com/apply/HTn3JfGD3s/Quality-Project-Coordinator</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Coral Gables, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>Entry-level role supporting quality initiatives; associate or bachelor’s preferred; 1-2 years healthcare administration/coordination; HIPAA familiarity; strong organization and MS Office skills.</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>https://doctorshcp.com</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Provides Medicare Advantage health insurance and managed care services.</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Shared document platforms</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>2026-05-21 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O771"/>
+  <dimension ref="A1:O773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56279,6 +56279,160 @@
         </is>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Brightcore Energy</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/brightcoreenergy/jobs/5145929007</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Armonk or Brooklyn or Rock Tavern or New Windsor</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>$90k-$130k/yr, $43-$62/hr</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Construction Management or related field; 3-5+ years PM experience in construction; geothermal experience preferred; travel NYC/NJ; Procore and Monday.com preferred.</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>https://brightcoreenergy.com</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>Provides turn-key clean energy and efficiency solutions for commercial clients.</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Procore, Monday.com</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>2026-05-23 07:43:41 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>https://careers-emcorgroup.icims.com/jobs/50108/project-manager/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Dayton, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>High School diploma; 3-5 years electrical construction experience; proficient with MS Office; familiar with project management software.</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>https://mecojax.com</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Provides electrical and technology infrastructure construction and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Teams, Outlook, Word, Excel, AutoCAD, Revit, Accubid, project management/document control software</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O773"/>
+  <dimension ref="A1:O774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56433,6 +56433,83 @@
         </is>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Harkcon</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=15aa7385-7aee-410b-90e3-5972b600f083&amp;jobId=613210</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Mobile, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>Part-time Project Manager with 4+ years PM, 5+ years relevant experience (CG/maritime preferred); BA/BS; MS Office proficiency; prior government contract experience desired.</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>https://harkcon.com</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Provides organizational performance and training solutions to federal agencies.</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Microsoft Office Suite</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>2026-05-23 11:34:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O774"/>
+  <dimension ref="A1:O775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56510,6 +56510,83 @@
         </is>
       </c>
     </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>M5 Utilities</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Project Manager -Dry Utilities</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>https://m5utilities.bamboohr.com/careers/67</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Boerne, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>Experience in construction project management; PMP desirable.</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>https://m5utilities.com</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>Installs and maintains underground utility infrastructure and water pipelines.</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>MS Office Suite, Construction Management Software</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O775"/>
+  <dimension ref="A1:O777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56587,6 +56587,160 @@
         </is>
       </c>
     </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Project Manager-Commercial Audio Visual</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/diversified/candidateportal/jobs/19533</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Concord or Boston or Hartford</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>$88k-$120k/yr, $42-$57/hr</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>3+ years experience as a Project Manager in commercial construction trades or AV environments; strong communication, leadership, scheduling, budgeting; knowledge of AV installations and low-voltage work; PMP or AVIXA CTS desirable.</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>https://onediversified.com</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Designs and builds integrated audiovisual and media technology solutions.</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>CAD, Project Management Software, Microsoft Office, AV systems, Communication Tools</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>2026-05-24 12:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Reeder Distributors</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>https://reederdistributors.applicantpro.com/jobs/4097325</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Fort Worth, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>$60k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>Experience as Project Coordinator or similar in construction/contracting; strong documentation and scheduling skills; proficient in MS Office and QuickBooks.</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>https://reederdistributors.com</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Distributes fuels and lubricants and installs automotive shop equipment.</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>QuickBooks, Microsoft Excel, Microsoft Outlook, CRM software</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>2026-05-23 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O777"/>
+  <dimension ref="A1:O779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56741,6 +56741,156 @@
         </is>
       </c>
     </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Rocket Travel by Agoda</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager, Enterprise Partnerships (Rocket Travel by Agoda) </t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/rocketmiles/jobs/7955947</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Chicago, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>$94k-$120k/yr, $45-$57/hr</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>3+ years project management in tech/travel fintech or partner-facing environment. End-to-end ownership with strong communication and analytical skills. Proficiency with PM tools; PMP/PMI-ACP/PRINCE2 preferred.</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>https://rockettravel.com</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Providing white-label travel booking and loyalty reward solutions.</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>Jira, Asana, Monday.com, Smartsheet</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>2026-05-24 10:44:56 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Statewide Windows &amp; Doors</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Project Coordinator Impact Windows</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>https://statewideimpactwindows.hireclick.com/jb/project-coordinator-impact-windows/view/245891</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Boynton Beach, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>3-5 years of project coordination experience for window projects; completing window permit applications.</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>https://statewideimpactwindows.com</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr"/>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>2026-05-24 11:40:39 AM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O779"/>
+  <dimension ref="A1:O782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56880,14 +56880,241 @@
         </is>
       </c>
       <c r="M779" t="inlineStr"/>
-      <c r="N779" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N779" t="inlineStr"/>
       <c r="O779" t="inlineStr">
         <is>
           <t>2026-05-24 11:40:39 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Bertelsmann</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Project Manager/Industrial Engineer (Las Vegas, NV, US, NV 89115)</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>https://jobsearch.createyourowncareer.com/ARVATO/job/Las-Vegas-Project-ManagerIndustrial-Engineer-NV-NV-89115/1396856633/</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>$39k-$39k/yr, $19-$19/hr</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>Bachelor's in Engineering or Industrial Engineering; 3+ years in logistics engineering, robotics, or supply chain automation; experience with robotics integration and project management.</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>https://bertelsmann.com</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Global media, services, and education conglomerate.</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>AutoCAD, Excel, Lean Six Sigma, Robotics, Automation technologies</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>2026-05-24 10:25:10 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>National Park Service</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>General Engineer/Landscape Architect/Architect/Civil Engineer/Mechanical Engineer (Project Manager)</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>https://www.usajobs.gov/job/870462300</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Anchorage or Denali Park</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>$103k-$134k/yr, $49-$64/hr</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>Project Manager role requiring engineering/architecture skills; contract oversight, COR duties, funding requests, site development experience, and supervision of technical staff.</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>https://nps.gov</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>Manages and preserves US national parks and historic sites.</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>CAD, Maintenance Management Systems</t>
+        </is>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>National Park Service</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>General Engineer/Landscape Architect/Architect/Civil Engineer/Mechanical Engineer (Project Manager)</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>https://www.usajobs.gov/job/870461800</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Anchorage or Denali Park</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>$103k-$134k/yr, $49-$64/hr</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>Professional engineering or architecture license; project management and COR experience; ability to supervise staff and manage construction contracts.</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Full Time, Part Time, Contract, Internship, Temporary, Seasonal, Volunteer</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>https://nps.gov</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>Manages and preserves US national parks and historic sites.</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>CAD, Maintenance Management Systems</t>
+        </is>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O782"/>
+  <dimension ref="A1:O800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57118,6 +57118,1360 @@
         </is>
       </c>
     </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Delaware Valley Paving</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Site Project Manager-Superintendent</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883d0910ff3290191341e9dd20a9a&amp;id=8a78839f9db1e847019db6407ec212da&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Tampa, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>Experience as Site Project Manager or Superintendent in paving/heavy civil construction; travel weekly (~9 months/year); strong leadership and communication; knowledge of safety standards; read plans; valid driver’s licence.</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>https://delawarevalleypaving.com</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>Full-service commercial asphalt and concrete paving contractor.</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Delaware Valley Paving</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Site Project Manager-Superintendent</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883d0910ff3290191341e9dd20a9a&amp;id=8a78839f9db1e847019db63fc2081272&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah, United States</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>Experience as Site Project Manager or Superintendent in paving/heavy civil construction; travel weekly; strong leadership and communication; safety knowledge; read construction plans; valid driver’s license.</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>https://delawarevalleypaving.com</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>Full-service commercial asphalt and concrete paving contractor.</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Delaware Valley Paving</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Site Project Manager-Superintendent</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883d0910ff3290191341e9dd20a9a&amp;id=8a78839f9db1e847019db640cd5c12ea&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Dallas, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>Experience as Site Project Manager or Superintendent in paving/heavy civil construction; willing to travel weekly (~9 months/yr); strong leadership, communication, and safety knowledge; read/interpret construction plans; valid driver’s license.</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>https://delawarevalleypaving.com</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>Full-service commercial asphalt and concrete paving contractor.</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Delaware Valley Paving</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Site Project Manager-Superintendent</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883d0910ff3290191341e9dd20a9a&amp;id=8a78839f9db1e847019db64100e512f8&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Boston, Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>Travel-heavy paving project management; on-site supervision; safety and quality compliance; strong communication and leadership.</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>https://delawarevalleypaving.com</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>Full-service commercial asphalt and concrete paving contractor.</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>GCS-SIGAL</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883c698ed62e701994d78608511c3&amp;id=8a7885ac9959821a01995e50df9945f1&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Washington, District of Columbia, United States</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>BS or MS in Engineering, Construction Management, Architecture, or related field; 3-5 years of construction experience; or combination of education and experience.</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>https://gcs-sigal.com</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr"/>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Procore, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>GCS-SIGAL</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883c698ed62e701994d78608511c3&amp;id=8a78859e98ed6378019958b3c9a7794a&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>$114k-$114k/yr, $54-$54/hr</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>Master’s degree in Civil Engineering, Construction Management, Architecture, or related field; 1 year commercial construction experience; Procore or similar PM software and MS Office proficiency.</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>https://gcs-sigal.com</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr"/>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>Procore, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>UMC, Inc.</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Plumbing Project Manager</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>https://recruitingbypaycor.com/career/JobIntroduction.action?clientId=8a7883c69b1375e0019b147acfcc00cb&amp;id=8a7885a89be7cb6b019c2a16cfae0787&amp;source=&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Denver, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>$90k-$110k/yr, $43-$52/hr</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>High school diploma or GED; 4 years licensed journeyman plumber; 3-5 years project manager in construction or plumbing; multi-family experience; strong organizational, interpersonal, initiative, and communication skills.</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>https://umc.us</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>Commercial plumbing and HVAC installation for construction projects.</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Field View, Bluebeam, Vista by Viewpoint</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:14:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Honest Exteriors</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Sales Project Manager</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/honest-exteriors-llc-sales-project-manager-8cc524d7-0bfd-491f-a705-d03b403620ff</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Eden Prairie, Minnesota, United States</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>$120k-$180k/yr, $57-$86/hr</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>Experience in exterior sales or construction; base + uncapped commission; manage sales and projects; driver’s license.</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>https://honestexteriors.com</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>Provider of residential roofing, siding, and exterior remodeling services.</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:20:12 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>pocstock</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>AI Project Manager</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>https://jobs.gusto.com/postings/pocstock-career-center-ai-project-manager-e3a3c562-4024-4b5e-8275-8ae89d39c8ec</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Newark, New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>$50k-$80k/yr, $24-$38/hr</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>2-5+ years in project management, data operations, or related roles; strong stakeholder management; experience with AI systems; PMP preferred but not required.</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>https://pocstock.com</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>Diversity-focused stock media agency and AI dataset provider.</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>AI, Project management software</t>
+        </is>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:20:12 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>The Whiting-Turner Contracting Company</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>https://jobs.silkroad.com/whitingturner/careers/jobs/2327?embedded=true</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>State College, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>$74k-$230k/yr, $35-$110/hr</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>3+ years to 20+ years in construction; ability to lead teams, manage schedule and costs; strong communication; BS in engineering/construction; experience with subcontracting and project accounting.</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>https://whiting-turner.com</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr"/>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Scheduling software, Project accounting</t>
+        </is>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>The Whiting-Turner Contracting Company</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Project Manager/Estimator</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>https://jobs.silkroad.com/whitingturner/careers/jobs/3104?embedded=true</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Las Vegas or Las Vegas</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>3+ years experience; strong pre-construction and estimating skills; leadership, scheduling, subcontract coordination, communication.</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>https://whiting-turner.com</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr"/>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>Estimating software, Project management software, Scheduling software</t>
+        </is>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>The Whiting-Turner Contracting Company</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>https://jobs.silkroad.com/whitingturner/careers/jobs/1953?embedded=true</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Los Angeles or San Diego or Irvine or Murrieta</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>$74k-$230k/yr, $35-$110/hr</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>3+ years to 20+ years of project management experience on complex commercial construction projects; leadership, scheduling, cost control, safety and quality focus; effective communication; experience with subcontract coordination and project accounting.</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>https://whiting-turner.com</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr"/>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>Scheduling software</t>
+        </is>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>The Whiting-Turner Contracting Company</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>https://jobs.silkroad.com/whitingturner/careers/jobs/2962?embedded=true</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Raleigh, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>3-10 years of construction project management; lead teams; plan, schedule, and manage costs; ensure safety and quality.</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>https://whiting-turner.com</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr"/>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Scheduling software, Project management software</t>
+        </is>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Slifco Electric</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Electrical Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>https://slifcoelectric.pinpointhq.com/en/postings/94616ab6-ffcc-4fd8-99ca-1ec7f6846f9c</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Sterling Heights, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Bachelor’s in Construction Management or Electrical Engineering; strong organizational and communication skills; proficiency with Microsoft Office; quick learner; able to work in a fast-paced construction environment.</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>https://slifcoelectric.com</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr"/>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>Microsoft Office, BIM, General computer systems</t>
+        </is>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:53:23 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Slifco Electric</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Electrical Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>https://slifcoelectric.pinpointhq.com/en/postings/1eac479b-6972-4695-bb59-295a51366c35</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Charleston, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Assist with bidding, estimating, contract reviews, meetings; support scheduling, costs, client relations; learn and grow in electrical construction management.</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>https://slifcoelectric.com</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr"/>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>Microsoft Office, BIM, Virtual modeling tools</t>
+        </is>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:53:23 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Jacob Sunrooms, Exteriors &amp; Baths</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Residential Project Coordinator - Fairview Heights, IL Office</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>http://jacobsunroomexteriorsbaths.applytojob.com/apply/mkM2yIPcCN/Residential-Project-Coordinator-Fairview-Heights-IL-Office</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Fairview Heights, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Coordinate project timelines, manage client and subcontractor communications, track milestones, and support project management in home improvement projects.</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>https://jacobsunroom.com</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>Installs residential sunrooms, windows, and provides bathroom remodeling services.</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>Microsoft Office, CRM/database (Access), QuickBooks</t>
+        </is>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Hillis-Carnes Engineering Associates</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Construction Materials Testing Project Manager - Frederick, MD</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>https://hcea.applicantpro.com/jobs/4094439</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Frederick, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>$65k-$75k/yr, $31-$36/hr</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in construction management, Civil Engineering, or Geology; 3-5 years field or project management in geotechnical engineering or construction materials testing; EIT/PE preferred; backlog management of $1-3M; client communication; supervising field staff; certifications a plus.</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>https://hcea.com</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>Provides geotechnical, environmental, and construction material engineering services.</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>Project Management Software, Estimating/Bidding Tools, Geotechnical software</t>
+        </is>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Systemair</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Project Manager, PMP</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/pp52028/candidateportal/jobs/780</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Remote, Oregon, United States</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>$80k-$90k/yr, $38-$43/hr</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>PM professional with PMP, manufacturing project experience, strong communication and MS 365 skills.</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>https://systemair.com</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>Manufacturer of energy-efficient ventilation and air quality solutions.</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>2026-05-23 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O800"/>
+  <dimension ref="A1:O802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57184,11 +57184,7 @@
           <t>Full-service commercial asphalt and concrete paving contractor.</t>
         </is>
       </c>
-      <c r="N783" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N783" t="inlineStr"/>
       <c r="O783" t="inlineStr">
         <is>
           <t>2026-05-25 03:14:29 AM CDT</t>
@@ -57261,11 +57257,7 @@
           <t>Full-service commercial asphalt and concrete paving contractor.</t>
         </is>
       </c>
-      <c r="N784" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N784" t="inlineStr"/>
       <c r="O784" t="inlineStr">
         <is>
           <t>2026-05-25 03:14:29 AM CDT</t>
@@ -57338,11 +57330,7 @@
           <t>Full-service commercial asphalt and concrete paving contractor.</t>
         </is>
       </c>
-      <c r="N785" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N785" t="inlineStr"/>
       <c r="O785" t="inlineStr">
         <is>
           <t>2026-05-25 03:14:29 AM CDT</t>
@@ -57415,11 +57403,7 @@
           <t>Full-service commercial asphalt and concrete paving contractor.</t>
         </is>
       </c>
-      <c r="N786" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N786" t="inlineStr"/>
       <c r="O786" t="inlineStr">
         <is>
           <t>2026-05-25 03:14:29 AM CDT</t>
@@ -57715,11 +57699,7 @@
           <t>Provider of residential roofing, siding, and exterior remodeling services.</t>
         </is>
       </c>
-      <c r="N790" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N790" t="inlineStr"/>
       <c r="O790" t="inlineStr">
         <is>
           <t>2026-05-25 02:20:12 AM CDT</t>
@@ -58461,14 +58441,160 @@
           <t>Manufacturer of energy-efficient ventilation and air quality solutions.</t>
         </is>
       </c>
-      <c r="N800" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N800" t="inlineStr"/>
       <c r="O800" t="inlineStr">
         <is>
           <t>2026-05-23 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>The Whiting-Turner Contracting Company</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>https://jobs.silkroad.com/whitingturner/careers/jobs/2910?embedded=true</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Columbus, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>3+ years experience managing complex commercial construction projects; strong leadership, scheduling, cost control, safety and quality focus; BS in Engineering, Engineering Technology, Construction Management or Construction Technology; excellent communication and problem-solving.</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>https://whiting-turner.com</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr"/>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>Scheduling software, Project management software</t>
+        </is>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>R1 RCM</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>https://r1rcm.wd1.myworkdayjobs.com/r1rcm/job/Remote-USA/Project-Manager_R260000003001</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>$52k-$97k/yr, $25-$46/hr</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Minimum two years in project management; strong communication; detail-oriented; proficiency with Salesforce, Mission Control, Copilot.</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>https://r1rcm.com</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>Provides revenue cycle management and automation for healthcare providers.</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>Salesforce, Mission Control, Copilot</t>
+        </is>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>2026-05-23 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O802"/>
+  <dimension ref="A1:O807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58598,6 +58598,391 @@
         </is>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Project Manager - Implementation </t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/vts/jobs/4699106005</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>$65k-$85k/yr, $31-$40/hr</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Entry-level PM with AI-first mindset; strong communication, structured planning, multitasking, growth-oriented.</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>https://vts.com</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>Provides a unified platform for commercial real estate operations.</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:33:44 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Huble</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Technical CRM Project Manager (USA)</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>https://jobs.workable.com/view/74Y8a1ErnvvzV4cQzXLzgV/remote-technical-crm-project-manager-(usa)-in-chicago-at-huble</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Chicago or United States</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>$90k-$100k/yr, $43-$48/hr</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent; mid-level experience in systems integrations/CRM implementations; experience in consultancy/agency/software development preferred.</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>https://huble.com</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>Provides HubSpot CRM implementation and digital business consultancy services.</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>HubSpot, CRM, Project Management</t>
+        </is>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:12:58 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Performance Hospitality</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager, Real Estate Development and Construction</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=300410&amp;clientkey=50C935C19319F7553BBAF7E7C187C6C8</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Minimum 2 years in development, asset management or similar leadership; proven track record managing large-scale projects; strong financial, budgeting and forecasting skills; excellent negotiation and communication abilities; adaptable in a fast-paced environment.</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>https://performancehospitality.com</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>Provides management and asset services for lifestyle hotels and resorts.</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>InSite Group</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager, Real Estate Development and Construction</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>https://www.paycomonline.net/v4/ats/web.php/jobs/ViewJobDetails?job=300410&amp;clientkey=ED29350392643C6DEF5D9DC75DA5F36E</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>Minimum 2 years in development or asset management leadership; track record managing large development projects; budgeting/forecasting; negotiation and communication skills; fast-paced environment.</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>https://insiteus.com</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>Develops and manages hospitality and residential real estate properties.</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Republic Services</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Field Project Manager</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>https://republic.wd5.myworkdayjobs.com/republic/job/Clayton-NJ-USA/Field-Project-Manager_R-175985</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Clayton, New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>$82k-$113k/yr, $39-$54/hr</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree preferred; 2+ years field-related work; strong MS Office skills; knowledge of environmental regulations; valid driver’s license.</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>https://republicservices.com</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>Provides waste collection, recycling, and environmental services.</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O807"/>
+  <dimension ref="A1:O839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58664,11 +58664,7 @@
           <t>Provides a unified platform for commercial real estate operations.</t>
         </is>
       </c>
-      <c r="N803" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N803" t="inlineStr"/>
       <c r="O803" t="inlineStr">
         <is>
           <t>2026-05-25 09:33:44 AM CDT</t>
@@ -58818,11 +58814,7 @@
           <t>Provides management and asset services for lifestyle hotels and resorts.</t>
         </is>
       </c>
-      <c r="N805" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N805" t="inlineStr"/>
       <c r="O805" t="inlineStr">
         <is>
           <t>2026-05-24 07:00:00 PM CDT</t>
@@ -58895,11 +58887,7 @@
           <t>Develops and manages hospitality and residential real estate properties.</t>
         </is>
       </c>
-      <c r="N806" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N806" t="inlineStr"/>
       <c r="O806" t="inlineStr">
         <is>
           <t>2026-05-24 07:00:00 PM CDT</t>
@@ -58980,6 +58968,2470 @@
       <c r="O807" t="inlineStr">
         <is>
           <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Commercial Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>https://gilliatte-general-contractors-inc.careerplug.com/jobs/2316209</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Indianapolis, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>Experience in commercial construction and estimating; strong organization, communication, and leadership; proficient with Microsoft Office and estimating software.</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Estimating Software</t>
+        </is>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:24:06 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>https://fivestarpaintingcareers.careerplug.com/jobs/2417027</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Amarillo, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>2+ years of project management; residential/light commercial painting experience preferred; budgeting and scheduling; subcontractor coordination; strong communication.</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:24 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>https://fivestarpaintingcareers.careerplug.com/jobs/766723</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Fulshear, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>$60k-$60k/yr, $28-$28/hr</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Project management experience in residential/ light commercial painting; scheduling, budgeting, subcontractor coordination; strong communication and leadership.</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:23 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Customer Service Project Manager</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-of-southeast-louisiana.careerplug.com/jobs/1984717</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Metairie, Louisiana, United States</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>$40k-$75k/yr, $19-$36/hr</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Manage painting projects, coordinate subcontractors, schedule and budget, and ensure clear communication with clients; 2+ years project management experience preferred.</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Google Drive, Gmail, Google Calendar</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-of-mishawaka.careerplug.com/jobs/2018942</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Mishawaka, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>$40k-$55k/yr, $19-$26/hr</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Project management experience required; residential/light commercial painting knowledge; strong communication; budgeting and scheduling skills; proficiency with MS Office and scheduling tools.</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>MS Excel, MS Word, Google Mail/Calendar/Drive</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-of-n-kansas-city-mo.careerplug.com/jobs/2919109</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Kansas City, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Coordinate schedules, manage subcontractors, budget, and client communication; 2+ years project management experience preferred.</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>MS Excel, MS Word, Google Mail, Google Calendar, Google Drive</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:16 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Residential Project Manager</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-of-douglasville.careerplug.com/jobs/1544232</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Douglasville, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>$45k-$55k/yr, $21-$26/hr</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Minimum 2 years residential project management; strong communication; computer literacy; professional appearance; team player.</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:16 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Residential Painting Project Manager</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-saint-johns-county.careerplug.com/jobs/2006835</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Coordinate painting projects, manage schedules and budgets, and communicate with homeowners, contractors, and crews. Minimum 2 years PM experience; strong communication and MS Office skills.</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>MS Excel, MS Word, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:16 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-of-loveland.careerplug.com/jobs/2064684</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Loveland, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>$45k-$65k/yr, $21-$31/hr</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Coordinate scheduling, budgeting, subcontractors, and client communication for residential and light commercial painting projects.</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Google Calendar, Gmail, Google Drive</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:15 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-fayettville.careerplug.com/jobs/1355874</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas, United States</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Coordinate painting projects, schedule, manage subcontractors, communicate with clients, and maintain documentation.</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>MS Excel, MS Word, Google Calendar, Google Drive</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:14 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Estimator Project Manager</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>https://five-star-paining-of-muskegon.careerplug.com/jobs/1265821</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Kalamazoo, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>$45k-$100k/yr, $21-$48/hr</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>Experience in home services sales, strong communication, detail-oriented, professional demeanor.</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:23:11 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Exhibit Pros</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Account Project Manager Trade Shows and Events</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>https://exhibit-pros.careerplug.com/jobs/2728540</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>$70k-$90k/yr, $33-$43/hr</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>3-5 years trade show project management; strong budgeting, ERP and client management skills; leadership and team coordination.</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>https://exhibit-pros.com</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>Rents and designs custom trade show exhibits and displays.</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>ERP systems, Project management software</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:21:48 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Exhibit Pros</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>https://exhibit-pros.careerplug.com/jobs/2851127</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>$52k-$58k/yr, $25-$28/hr</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>Associate’s degree; 1-2 years in proposal writing/event planning/trade shows; tech-savvy; strong organization and communication; proficient in Google Suite and MS Office; willingness to learn.</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>https://exhibit-pros.com</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>Rents and designs custom trade show exhibits and displays.</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>Google Workspace, Microsoft Office, Adobe Photoshop, Adobe Illustrator</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:21:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Exhibit Pros</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Trade Shows and Events</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>https://exhibit-pros.careerplug.com/jobs/3267265</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>$52k-$58k/yr, $25-$28/hr</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>Associate’s degree required; 1-2 years in proposal writing or event planning preferred; tech-savvy; strong organizational and writing skills; proficient in Google Suite and Microsoft Office; able to learn project management tools.</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>https://exhibit-pros.com</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>Rents and designs custom trade show exhibits and displays.</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>Monday.com, ExhibitForce, IntelliEvent, Google Suite, Microsoft Office, Photoshop, Adobe Illustrator</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:21:47 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Project Manager - Solar Construction</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>https://ees-energy-services-corporation.careerplug.com/jobs/2448411</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Rochester, New York, United States</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>$70k-$100k/yr, $33-$48/hr</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>Solar construction project management experience; travel ability; strong communication; knowledge of quality, health and safety standards; computer skills (Word, Excel, Project); read plans and contracts; solar construction background; project management experience; OSHA 10; electrical license; safety/QA environment focus.</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft Project</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:20:52 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Construction Foreman / Project Manager</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>https://djh-mechanical-corp.careerplug.com/jobs/2910542</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>$47k-$74k/yr, $23-$36/hr</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>Experience in construction/project management; leadership; strong communication; punctuality; knowledge of building codes.</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:20:32 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Water/Fire/Mold Mitigation Project Manager</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>https://drymedic-careers.careerplug.com/jobs/3113170</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Irondale, Alabama, United States</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>$52k-$58k/yr, $25-$28/hr</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>Experience in emergency restoration and sales; strong communication; Xactimate/DASH proficiency; high school or GED; valid driver’s license; able to lift 50 lbs; OSHA respirator use.</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>Xactimate, DASH</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:20:32 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Cooper Tacia</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Commercial Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>https://cooper-tacia-general-contracting-company.careerplug.com/jobs/2885805</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Raleigh, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Construction Management or Civil Engineering; 3+ years PM experience for PM1, 5+ years for PM2; proficient with MS Projects, Procore, Sage 100; strong communication and multitasking skills.</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>https://coopertacia.com</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>General contractor for commercial and industrial infrastructure projects.</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>Microsoft Projects, Procore, Sage Construction 100</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:18:54 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Cooper Tacia</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>https://cooper-tacia-general-contracting-company.careerplug.com/jobs/3031580</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>Bachelor’s in Construction Management or Civil Engineering; 3+ years PM experience preferred (PM1) or 5+ years preferred (PM2); proficient with MS Projects, Procore, Sage Construction 100; strong communication and multitasking.</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>https://coopertacia.com</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>General contractor for commercial and industrial infrastructure projects.</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Microsoft Project, Procore, Sage Construction 100</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:18:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-sarasota-south-tampa.careerplug.com/jobs/2408708</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Punta Gorda, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>$62k-$74k/yr, $30-$36/hr</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>Supervise remediation operations including packing, moving, cleaning; oversee inventory and client/insurer communications; lead safety and training; operate specialized equipment.</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>Forklift, Power tools, Hand tools</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:59 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Restoration Project Manager</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-long-island.careerplug.com/jobs/3316369</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Bay Shore, New York, United States</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>$70k-$110k/yr, $33-$52/hr</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>2+ years restoration project management; leadership; strong communication; Xactimate; valid driver’s license; able to manage multiple priorities.</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>Xactimate</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:58 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Field &amp; Warehouse Technician/Potential Project Manager</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-central-iowa.careerplug.com/jobs/2820496</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Grimes, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>$31k-$41k/yr, $15-$20/hr</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>Experience in restoration or construction is valuable; must be able to operate a motor vehicle; strong work ethic; ability to multitask; strong customer service mindset.</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:57 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>https://bay-area-dki.careerplug.com/jobs/2149085</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>$60k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>Entry level junior project manager with strong organization, communication, and willingness to learn; basic PM knowledge and software skills preferred.</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Full Time, Part Time</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:10 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Associate Controls Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>https://axiom-innovation-llc.careerplug.com/jobs/3222197</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Washington, United States</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>$60k-$80k/yr, $28-$38/hr</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>3+ years in mission critical industry with experience in process controls/adherence; field experience in large commercial construction; SCADA or software control credentials; strong client communication; willing to travel.</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>SCADA, Microsoft 365</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:14:45 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Project Manager - Printing</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>https://alphagraphics-us398.careerplug.com/jobs/2865057</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Cary, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>$36k-$47k/yr, $17-$23/hr</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Project management experience preferred; strong communication, organizational, and customer service skills; high school diploma or equivalent; some college coursework preferred.</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:13:26 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Project Manager TEST</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>https://acca-careers.careerplug.com/jobs/2176682</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Akron, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>$50k-$64k/yr, $24-$31/hr</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Project management for HVAC service installs; travel to sites; strong organization and communication; HVAC knowledge; willing to work full-time with benefits.</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:12:45 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Project Manager Mechanical Construction</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>https://acca-careers.careerplug.com/jobs/3186895</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Columbus, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>$60k-$95k/yr, $28-$45/hr</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Experience in mechanical or HVAC project management; strong understanding of construction drawings and mechanical systems; proficiency with AutoCAD, REVIT, or Autodesk tools; strong organizational and communication skills; ability to manage budgets, schedules, and subcontractors; problem-solving with a customer-focused approach.</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>AutoCAD, REVIT, Autodesk MEP, Navisworks</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:12:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Reconstruction Project Manager</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>https://aboveallcleaningandrestorationllc.careerplug.com/jobs/2243007</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Tucker, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Experience as a Project Manager or in a similar role; proficient in Xactimate; detail-oriented; highly organized; able to manage multiple projects; strong verbal and written communication.</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>Xactimate</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:12:12 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Project Manager/ Estimator</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>https://1-800-water-damage-of-cleveland-west.careerplug.com/jobs/3145412</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>North Olmsted, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>$60k-$80k/yr, $28-$38/hr</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Manage mitigation projects, supervise teams, budget and estimate jobs, strong customer service and communication; IICRC certifications; MS Office proficiency.</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:11:45 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Visual Solutions Project Manager</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>https://fastsigns-careers.careerplug.com/jobs/1336201</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>York, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>$43k-$52k/yr, $21-$25/hr</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Detail-oriented project manager with strong client communication, coordination of installations, vendor sourcing, and sales experience.</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>Point of Sale</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:07:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Inside Sales &amp; Project Manager – Signs &amp; Graphics</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>https://fastsigns-careers.careerplug.com/jobs/2805147</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Orlando, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>$31k-$41k/yr, $15-$20/hr</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Quoted sign projects, manage customer relations, coordinate with production and installation, handle multiple orders, grow sales.</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator, CorelDRAW</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:07:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Project Manager Assistant</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>https://crrcsifangamerica.apscareerportal.com/jobs/1210602</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>$58k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in business or engineering or 4 years related experience; strong project management, communication, and computer skills.</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:43:20 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O839"/>
+  <dimension ref="A1:O866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58972,11 +58972,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A808" t="inlineStr"/>
       <c r="B808" t="inlineStr">
         <is>
           <t>Commercial Construction Project Manager</t>
@@ -59027,16 +59023,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L808" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M808" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L808" t="inlineStr"/>
+      <c r="M808" t="inlineStr"/>
       <c r="N808" t="inlineStr">
         <is>
           <t>Microsoft Office, Estimating Software</t>
@@ -59049,11 +59037,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A809" t="inlineStr"/>
       <c r="B809" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -59104,16 +59088,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L809" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M809" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L809" t="inlineStr"/>
+      <c r="M809" t="inlineStr"/>
       <c r="N809" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Word, Google Workspace</t>
@@ -59126,11 +59102,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A810" t="inlineStr"/>
       <c r="B810" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -59181,16 +59153,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L810" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M810" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L810" t="inlineStr"/>
+      <c r="M810" t="inlineStr"/>
       <c r="N810" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Word, Google Workspace</t>
@@ -59203,11 +59167,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A811" t="inlineStr"/>
       <c r="B811" t="inlineStr">
         <is>
           <t>Customer Service Project Manager</t>
@@ -59258,16 +59218,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L811" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M811" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L811" t="inlineStr"/>
+      <c r="M811" t="inlineStr"/>
       <c r="N811" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Word, Google Drive, Gmail, Google Calendar</t>
@@ -59280,11 +59232,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A812" t="inlineStr"/>
       <c r="B812" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -59335,16 +59283,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L812" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M812" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L812" t="inlineStr"/>
+      <c r="M812" t="inlineStr"/>
       <c r="N812" t="inlineStr">
         <is>
           <t>MS Excel, MS Word, Google Mail/Calendar/Drive</t>
@@ -59357,11 +59297,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A813" t="inlineStr"/>
       <c r="B813" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -59412,16 +59348,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L813" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M813" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L813" t="inlineStr"/>
+      <c r="M813" t="inlineStr"/>
       <c r="N813" t="inlineStr">
         <is>
           <t>MS Excel, MS Word, Google Mail, Google Calendar, Google Drive</t>
@@ -59434,11 +59362,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A814" t="inlineStr"/>
       <c r="B814" t="inlineStr">
         <is>
           <t>Residential Project Manager</t>
@@ -59489,16 +59413,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L814" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M814" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L814" t="inlineStr"/>
+      <c r="M814" t="inlineStr"/>
       <c r="N814" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel</t>
@@ -59511,11 +59427,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A815" t="inlineStr"/>
       <c r="B815" t="inlineStr">
         <is>
           <t>Residential Painting Project Manager</t>
@@ -59566,16 +59478,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L815" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M815" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L815" t="inlineStr"/>
+      <c r="M815" t="inlineStr"/>
       <c r="N815" t="inlineStr">
         <is>
           <t>MS Excel, MS Word, Google Workspace</t>
@@ -59588,11 +59492,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A816" t="inlineStr"/>
       <c r="B816" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -59643,16 +59543,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L816" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M816" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L816" t="inlineStr"/>
+      <c r="M816" t="inlineStr"/>
       <c r="N816" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Word, Google Calendar, Gmail, Google Drive</t>
@@ -59665,11 +59557,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A817" t="inlineStr"/>
       <c r="B817" t="inlineStr">
         <is>
           <t>Project Coordinator</t>
@@ -59720,16 +59608,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L817" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M817" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L817" t="inlineStr"/>
+      <c r="M817" t="inlineStr"/>
       <c r="N817" t="inlineStr">
         <is>
           <t>MS Excel, MS Word, Google Calendar, Google Drive</t>
@@ -59742,11 +59622,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A818" t="inlineStr"/>
       <c r="B818" t="inlineStr">
         <is>
           <t>Estimator Project Manager</t>
@@ -59797,21 +59673,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L818" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M818" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N818" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L818" t="inlineStr"/>
+      <c r="M818" t="inlineStr"/>
+      <c r="N818" t="inlineStr"/>
       <c r="O818" t="inlineStr">
         <is>
           <t>2026-05-25 04:23:11 PM CDT</t>
@@ -60050,11 +59914,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A822" t="inlineStr"/>
       <c r="B822" t="inlineStr">
         <is>
           <t>Project Manager - Solar Construction</t>
@@ -60105,16 +59965,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L822" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M822" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L822" t="inlineStr"/>
+      <c r="M822" t="inlineStr"/>
       <c r="N822" t="inlineStr">
         <is>
           <t>Microsoft Word, Microsoft Excel, Microsoft Project</t>
@@ -60127,11 +59979,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A823" t="inlineStr"/>
       <c r="B823" t="inlineStr">
         <is>
           <t>Construction Foreman / Project Manager</t>
@@ -60182,21 +60030,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L823" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M823" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N823" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L823" t="inlineStr"/>
+      <c r="M823" t="inlineStr"/>
+      <c r="N823" t="inlineStr"/>
       <c r="O823" t="inlineStr">
         <is>
           <t>2026-05-25 04:20:32 PM CDT</t>
@@ -60204,11 +60040,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A824" t="inlineStr"/>
       <c r="B824" t="inlineStr">
         <is>
           <t>Water/Fire/Mold Mitigation Project Manager</t>
@@ -60259,16 +60091,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M824" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L824" t="inlineStr"/>
+      <c r="M824" t="inlineStr"/>
       <c r="N824" t="inlineStr">
         <is>
           <t>Xactimate, DASH</t>
@@ -60435,1003 +60259,2906 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="inlineStr">
+      <c r="A827" t="inlineStr"/>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-sarasota-south-tampa.careerplug.com/jobs/2408708</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Punta Gorda, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>$62k-$74k/yr, $30-$36/hr</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>Supervise remediation operations including packing, moving, cleaning; oversee inventory and client/insurer communications; lead safety and training; operate specialized equipment.</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr"/>
+      <c r="M827" t="inlineStr"/>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>Forklift, Power tools, Hand tools</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:59 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr"/>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Restoration Project Manager</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-long-island.careerplug.com/jobs/3316369</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Bay Shore, New York, United States</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>$70k-$110k/yr, $33-$52/hr</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>2+ years restoration project management; leadership; strong communication; Xactimate; valid driver’s license; able to manage multiple priorities.</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr"/>
+      <c r="M828" t="inlineStr"/>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>Xactimate</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:58 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr"/>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Field &amp; Warehouse Technician/Potential Project Manager</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-central-iowa.careerplug.com/jobs/2820496</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Grimes, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>$31k-$41k/yr, $15-$20/hr</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>Experience in restoration or construction is valuable; must be able to operate a motor vehicle; strong work ethic; ability to multitask; strong customer service mindset.</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr"/>
+      <c r="M829" t="inlineStr"/>
+      <c r="N829" t="inlineStr"/>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:57 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr"/>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>https://bay-area-dki.careerplug.com/jobs/2149085</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>$60k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>Entry level junior project manager with strong organization, communication, and willingness to learn; basic PM knowledge and software skills preferred.</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Full Time, Part Time</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr"/>
+      <c r="M830" t="inlineStr"/>
+      <c r="N830" t="inlineStr"/>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:15:10 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr"/>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Associate Controls Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>https://axiom-innovation-llc.careerplug.com/jobs/3222197</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Washington, United States</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>$60k-$80k/yr, $28-$38/hr</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>3+ years in mission critical industry with experience in process controls/adherence; field experience in large commercial construction; SCADA or software control credentials; strong client communication; willing to travel.</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr"/>
+      <c r="M831" t="inlineStr"/>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>SCADA, Microsoft 365</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:14:45 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr"/>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Project Manager - Printing</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>https://alphagraphics-us398.careerplug.com/jobs/2865057</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Cary, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>$36k-$47k/yr, $17-$23/hr</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Project management experience preferred; strong communication, organizational, and customer service skills; high school diploma or equivalent; some college coursework preferred.</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr"/>
+      <c r="M832" t="inlineStr"/>
+      <c r="N832" t="inlineStr"/>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:13:26 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr"/>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Project Manager TEST</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>https://acca-careers.careerplug.com/jobs/2176682</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Akron, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>$50k-$64k/yr, $24-$31/hr</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Project management for HVAC service installs; travel to sites; strong organization and communication; HVAC knowledge; willing to work full-time with benefits.</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr"/>
+      <c r="M833" t="inlineStr"/>
+      <c r="N833" t="inlineStr"/>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:12:45 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr"/>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Project Manager Mechanical Construction</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>https://acca-careers.careerplug.com/jobs/3186895</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Columbus, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>$60k-$95k/yr, $28-$45/hr</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Experience in mechanical or HVAC project management; strong understanding of construction drawings and mechanical systems; proficiency with AutoCAD, REVIT, or Autodesk tools; strong organizational and communication skills; ability to manage budgets, schedules, and subcontractors; problem-solving with a customer-focused approach.</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr"/>
+      <c r="M834" t="inlineStr"/>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>AutoCAD, REVIT, Autodesk MEP, Navisworks</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:12:29 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr"/>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Reconstruction Project Manager</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>https://aboveallcleaningandrestorationllc.careerplug.com/jobs/2243007</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Tucker, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Experience as a Project Manager or in a similar role; proficient in Xactimate; detail-oriented; highly organized; able to manage multiple projects; strong verbal and written communication.</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr"/>
+      <c r="M835" t="inlineStr"/>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>Xactimate</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:12:12 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr"/>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Project Manager/ Estimator</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>https://1-800-water-damage-of-cleveland-west.careerplug.com/jobs/3145412</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>North Olmsted, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>$60k-$80k/yr, $28-$38/hr</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Manage mitigation projects, supervise teams, budget and estimate jobs, strong customer service and communication; IICRC certifications; MS Office proficiency.</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr"/>
+      <c r="M836" t="inlineStr"/>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:11:45 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr"/>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Visual Solutions Project Manager</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>https://fastsigns-careers.careerplug.com/jobs/1336201</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>York, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>$43k-$52k/yr, $21-$25/hr</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Detail-oriented project manager with strong client communication, coordination of installations, vendor sourcing, and sales experience.</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr"/>
+      <c r="M837" t="inlineStr"/>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>Point of Sale</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:07:55 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr"/>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Inside Sales &amp; Project Manager – Signs &amp; Graphics</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>https://fastsigns-careers.careerplug.com/jobs/2805147</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Orlando, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>$31k-$41k/yr, $15-$20/hr</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Quoted sign projects, manage customer relations, coordinate with production and installation, handle multiple orders, grow sales.</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr"/>
+      <c r="M838" t="inlineStr"/>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator, CorelDRAW</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:07:51 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr"/>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Project Manager Assistant</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>https://crrcsifangamerica.apscareerportal.com/jobs/1210602</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>$58k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in business or engineering or 4 years related experience; strong project management, communication, and computer skills.</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr"/>
+      <c r="M839" t="inlineStr"/>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:43:20 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>MasTec</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Data Center</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>https://careers.wanzek.com/jobs/64147</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>1–4 years in project management for transmission/substation utilities; manages small to medium projects; PMP/CCM pursuing; bachelor in engineering/construction/project management.</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>https://mastec.com</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>Provides infrastructure engineering, construction, and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>Primavera, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>2026-05-25 05:39:52 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B827" t="inlineStr">
+      <c r="B841" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="C827" t="inlineStr">
-        <is>
-          <t>https://blue-kangaroo-packoutz-sarasota-south-tampa.careerplug.com/jobs/2408708</t>
-        </is>
-      </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E827" t="inlineStr">
-        <is>
-          <t>Punta Gorda, Florida, United States</t>
-        </is>
-      </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G827" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H827" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I827" t="inlineStr">
-        <is>
-          <t>$62k-$74k/yr, $30-$36/hr</t>
-        </is>
-      </c>
-      <c r="J827" t="inlineStr">
-        <is>
-          <t>Supervise remediation operations including packing, moving, cleaning; oversee inventory and client/insurer communications; lead safety and training; operate specialized equipment.</t>
-        </is>
-      </c>
-      <c r="K827" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L827" t="inlineStr">
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>https://stand-strong-fencing-careers.careerplug.com/jobs/2964385</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Sarasota, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>$54k-$60k/yr, $25-$28/hr</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Project Manager with construction/trade experience; coordinate projects, teams, and communications; driver’s license required.</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M827" t="inlineStr">
+      <c r="M841" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N827" t="inlineStr">
-        <is>
-          <t>Forklift, Power tools, Hand tools</t>
-        </is>
-      </c>
-      <c r="O827" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:15:59 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" t="inlineStr">
+      <c r="N841" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B828" t="inlineStr">
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:45:36 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>https://sipley-the-best-llc-1.careerplug.com/jobs/3131801</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Lake City, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>$70k-$85k/yr, $33-$40/hr</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>2+ years in technical/manufacturing project management; strong technical aptitude; planning, budgeting, and cross-functional coordination; excellent communication.</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>Microsoft Office, CRM/ERP systems, CAD software</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:44:26 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Estimator - Project Manager – ADA and Fire Safety Signage</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>https://signarama-careers.careerplug.com/jobs/3371423</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Redmond, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>$48k-$96k/yr, $23-$46/hr</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Estimating, project management, or sales experience in signage/construction; bid platforms familiarity; ADA/life-safety signage knowledge; strong communication; estimating tools, CRM, MS Office; proactive BD mindset.</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>Estimating software, CRM, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:44:24 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Sales &amp; Project Manager</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>https://protectpainterscareers.careerplug.com/jobs/1641183</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Richmond, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>$70k-$100k/yr, $33-$48/hr</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Manage, estimate, coordinate painting projects; supervise subcontractors; communicate with owners, clients, and crews; ensure on-time, on-budget delivery.</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Word, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:40:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>https://powers-built-structures.careerplug.com/jobs/1663918</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Hudson, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>$70k-$85k/yr, $33-$40/hr</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Three years steel erection PM experience; five years commercial steel industry experience; AISC compliance; high school diploma; bachelor's in construction management preferred.</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>Trimble Connect, Procore</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:39:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Panhandle Cleaning &amp; Restoration</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>https://panhandle-cleaning-restoration.careerplug.com/jobs/640274</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>4+ years project management in construction; lead multiple projects; strong leadership; safety and budget management; ability to train staff.</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>https://panhandlecr.com</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>Provides disaster restoration and property reconstruction services for properties.</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>MS Project, Excel</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:37:48 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>ServiceMaster Contract Services</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>https://iicrc-careers.careerplug.com/jobs/2214043</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Los Angeles, California, United States</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>$54k-$75k/yr, $26-$36/hr</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Experience managing production crews, coordinating job sites, budgeting and ensuring safety; IICRC certification and familiarity with Xactimate.</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>https://servicemasterclean.com</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>Professional janitorial and commercial cleaning services provider.</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>Xactimate, MICA, Claims Connect</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:32:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>ServiceMaster Contract Services</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
         <is>
           <t>Restoration Project Manager</t>
         </is>
       </c>
-      <c r="C828" t="inlineStr">
-        <is>
-          <t>https://blue-kangaroo-packoutz-long-island.careerplug.com/jobs/3316369</t>
-        </is>
-      </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E828" t="inlineStr">
-        <is>
-          <t>Bay Shore, New York, United States</t>
-        </is>
-      </c>
-      <c r="F828" t="inlineStr">
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>https://iicrc-careers.careerplug.com/jobs/1735580</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Lanham, Maryland, United States</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Experience in restoration production focusing on mold; strong leadership; IICRC certifications preferred; travel locally and out of state; background check; able to lift 50-100 lbs.</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>https://servicemasterclean.com</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>Professional janitorial and commercial cleaning services provider.</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:32:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>ServiceMaster Contract Services</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Restoration Project Manager</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>https://iicrc-careers.careerplug.com/jobs/934469</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Worthington, Kentucky, United States</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>Leads restoration projects, manages budgets, coordinates teams, communicates with clients; construction project management experience preferred.</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>https://servicemasterclean.com</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>Professional janitorial and commercial cleaning services provider.</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:32:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>ServiceMaster Contract Services</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Reconstruction Project Manager/ Estimator</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>https://iicrc-careers.careerplug.com/jobs/750540</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Lancaster, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
         <is>
           <t>2+ YOE</t>
         </is>
       </c>
-      <c r="G828" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H828" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I828" t="inlineStr">
-        <is>
-          <t>$70k-$110k/yr, $33-$52/hr</t>
-        </is>
-      </c>
-      <c r="J828" t="inlineStr">
-        <is>
-          <t>2+ years restoration project management; leadership; strong communication; Xactimate; valid driver’s license; able to manage multiple priorities.</t>
-        </is>
-      </c>
-      <c r="K828" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L828" t="inlineStr">
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>$35k-$55k/yr, $16-$26/hr</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>2+ years PM experience in restoration or construction; proficient with computers; Xactimate experience; IICRC and Lead certs preferred; valid driver’s license; background check; on-call availability</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>https://servicemasterclean.com</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Professional janitorial and commercial cleaning services provider.</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Xactimate, computers/tablets</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:32:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M828" t="inlineStr">
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Project Manager/Operations Kitchen Design and Remodeling Company</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>https://kitchen-solvers-careers.careerplug.com/jobs/3202590</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>South Bend, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>$2k-$2k/yr, $1-$1/hr</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>Experience in office management and/or project management; QuickBooks proficiency; strong organizational and communication skills; knowledge of kitchen design/remodeling preferred.</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N828" t="inlineStr">
-        <is>
-          <t>Xactimate</t>
-        </is>
-      </c>
-      <c r="O828" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:15:58 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" t="inlineStr">
+      <c r="M851" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B829" t="inlineStr">
-        <is>
-          <t>Field &amp; Warehouse Technician/Potential Project Manager</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr">
-        <is>
-          <t>https://blue-kangaroo-packoutz-central-iowa.careerplug.com/jobs/2820496</t>
-        </is>
-      </c>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E829" t="inlineStr">
-        <is>
-          <t>Grimes, Iowa, United States</t>
-        </is>
-      </c>
-      <c r="F829" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G829" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H829" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I829" t="inlineStr">
-        <is>
-          <t>$31k-$41k/yr, $15-$20/hr</t>
-        </is>
-      </c>
-      <c r="J829" t="inlineStr">
-        <is>
-          <t>Experience in restoration or construction is valuable; must be able to operate a motor vehicle; strong work ethic; ability to multitask; strong customer service mindset.</t>
-        </is>
-      </c>
-      <c r="K829" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L829" t="inlineStr">
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>QuickBooks, Microsoft Office Suite, Project management tools</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:30:37 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Insulate SB</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>https://insulate-sb-inc.careerplug.com/jobs/3113416</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Santa Barbara, California, United States</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>$65k-$80k/yr, $31-$38/hr</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>3+ years in construction/insulation with at least 2 years in supervision; strong leadership, organizational and communication skills; bilingual; knowledge of OSHA standards.</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>https://insulatesb.com</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>Provider of residential and commercial insulation and thermal protection services.</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M829" t="inlineStr">
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:28:20 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N829" t="inlineStr">
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Landscape Project Manager</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>https://jlm-strategic-talent-partners.careerplug.com/jobs/1967665</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Glendale, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>$83k-$108k/yr, $40-$52/hr</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>Experience in project engineering and civil construction; strong team leadership and communication; able to work on project sites and manage landscape teams.</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O829" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:15:57 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr">
+      <c r="M853" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B830" t="inlineStr">
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:10:17 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Heavy Civil Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>https://jlm-strategic-talent-partners.careerplug.com/jobs/2074347</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Concord, California, United States</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>$104k-$208k/yr, $50-$100/hr</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>Experience in project engineering and civil construction; strong communicator; able to manage project controls and scheduling; relocation to Concord, CA.</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:10:16 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Heavy Civil Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>https://jlm-strategic-talent-partners.careerplug.com/jobs/2074329</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Fremont or Concord</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>$104k-$208k/yr, $50-$100/hr</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>Experience managing heavy civil construction projects; strong planning, scheduling, QA/QC, cost tracking; team leadership; able to work on site.</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Project Scheduling Software, Budgeting Tools, Document Control Systems, Quality Management System</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:10:15 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>https://bay-area-dki.careerplug.com/jobs/2149085</t>
-        </is>
-      </c>
-      <c r="D830" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E830" t="inlineStr">
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>https://jlm-strategic-talent-partners.careerplug.com/jobs/1917132</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Fort Worth, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>$72k-$114k/yr, $35-$55/hr</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>Experience managing project scope, schedule, and budget; strong communication; organized; team oriented; willing to work on Fort Worth project site.</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:10:14 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>https://servicemaster-restore-usa-careers.careerplug.com/jobs/1092326</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Johnson City, Tennessee, United States</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>High school diploma; experience in insurance restoration or construction; valid driver’s license; leadership experience; strong communication and customer service; on-call flexibility.</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>Xactimate, Mobile devices</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:09:23 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>https://servicemaster-restore-usa-careers.careerplug.com/jobs/1079246</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>West Palm Beach, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Lead field restoration projects, manage crews, estimate with Xactimate, ensure quality and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>Xactimate, Mobile Tablet, Insurance software</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:09:21 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>https://servicemaster-restore-usa-careers.careerplug.com/jobs/1388407</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Staten Island, New York, United States</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Lead field restoration projects, supervise crews, estimate with Xactimate, strong customer service, driver license, on-call.</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>Xactimate, tablet, mobile phone</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:09:19 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>https://servicemaster-restore-usa-careers.careerplug.com/jobs/2718234</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Miami, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Lead field operations for healthcare construction, maintenance, and roofing; ensure compliance with Joint Commission, ICRA, ILMS; bilingual English/Spanish.</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:09:14 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>AV Installation Technician/Project Manager</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>https://prosource-careers.careerplug.com/jobs/2986427</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Sonoma, California, United States</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>$80k-$120k/yr, $38-$57/hr</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>2+ years AV installation experience; install/calibrate AV systems; Control4/Savant; CTS-I/NSCA/CEDIA a plus; valid driver's license.</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>Control4, Savant, CAT5e/6, HDMI, DVI, RGB, Networking, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:08:41 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>https://prosource-careers.careerplug.com/jobs/2529566</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Venice, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>$40k-$40k/yr, $19-$19/hr</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>Full-time project management role in Venice, FL; compensation $40,000 per year.</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:08:38 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Residential A/V Project Manager</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>https://prosource-careers.careerplug.com/jobs/1990169</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="F830" t="inlineStr">
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>$60k-$90k/yr, $28-$43/hr</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Strong communication, self-motivated, problem-solving, client management, leadership, time management, travel willingness.</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>2026-05-25 04:08:35 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Exelon</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Project Manager-Transmission</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>https://careers.delmarva.com/jobs/28958</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
         <is>
           <t>2+ YOE</t>
         </is>
       </c>
-      <c r="G830" t="inlineStr">
+      <c r="G864" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="H830" t="inlineStr">
-        <is>
-          <t>Entry Level</t>
-        </is>
-      </c>
-      <c r="I830" t="inlineStr">
-        <is>
-          <t>$60k-$70k/yr, $28-$33/hr</t>
-        </is>
-      </c>
-      <c r="J830" t="inlineStr">
-        <is>
-          <t>Entry level junior project manager with strong organization, communication, and willingness to learn; basic PM knowledge and software skills preferred.</t>
-        </is>
-      </c>
-      <c r="K830" t="inlineStr">
-        <is>
-          <t>Full Time, Part Time</t>
-        </is>
-      </c>
-      <c r="L830" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M830" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N830" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O830" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:15:10 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B831" t="inlineStr">
-        <is>
-          <t>Associate Controls Technical Project Manager</t>
-        </is>
-      </c>
-      <c r="C831" t="inlineStr">
-        <is>
-          <t>https://axiom-innovation-llc.careerplug.com/jobs/3222197</t>
-        </is>
-      </c>
-      <c r="D831" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E831" t="inlineStr">
-        <is>
-          <t>Washington, United States</t>
-        </is>
-      </c>
-      <c r="F831" t="inlineStr">
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>$83k-$114k/yr, $40-$55/hr</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Bachelor's in engineering or related field with 2-4 years PM experience; or HS diploma with 3-6 years experience; for non-construction also with business/engineering degree; strong leadership, communication, and project management skills; valid driver's license.</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>https://exeloncorp.com</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>Electric utility holding company delivering energy to customers.</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>Word, Excel, Access, PowerPoint, Microsoft Project, Passport</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:40:53 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>The Whiting-Turner Contracting Company</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>https://jobs.silkroad.com/whitingturner/careers/jobs/3122?embedded=true</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Millbrae or Pleasanton</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
         <is>
           <t>3+ YOE</t>
         </is>
       </c>
-      <c r="G831" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="H831" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I831" t="inlineStr">
-        <is>
-          <t>$60k-$80k/yr, $28-$38/hr</t>
-        </is>
-      </c>
-      <c r="J831" t="inlineStr">
-        <is>
-          <t>3+ years in mission critical industry with experience in process controls/adherence; field experience in large commercial construction; SCADA or software control credentials; strong client communication; willing to travel.</t>
-        </is>
-      </c>
-      <c r="K831" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L831" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M831" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N831" t="inlineStr">
-        <is>
-          <t>SCADA, Microsoft 365</t>
-        </is>
-      </c>
-      <c r="O831" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:14:45 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B832" t="inlineStr">
-        <is>
-          <t>Project Manager - Printing</t>
-        </is>
-      </c>
-      <c r="C832" t="inlineStr">
-        <is>
-          <t>https://alphagraphics-us398.careerplug.com/jobs/2865057</t>
-        </is>
-      </c>
-      <c r="D832" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E832" t="inlineStr">
-        <is>
-          <t>Cary, North Carolina, United States</t>
-        </is>
-      </c>
-      <c r="F832" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G832" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H832" t="inlineStr">
-        <is>
-          <t>Entry Level</t>
-        </is>
-      </c>
-      <c r="I832" t="inlineStr">
-        <is>
-          <t>$36k-$47k/yr, $17-$23/hr</t>
-        </is>
-      </c>
-      <c r="J832" t="inlineStr">
-        <is>
-          <t>Project management experience preferred; strong communication, organizational, and customer service skills; high school diploma or equivalent; some college coursework preferred.</t>
-        </is>
-      </c>
-      <c r="K832" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L832" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M832" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N832" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O832" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:13:26 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B833" t="inlineStr">
-        <is>
-          <t>Project Manager TEST</t>
-        </is>
-      </c>
-      <c r="C833" t="inlineStr">
-        <is>
-          <t>https://acca-careers.careerplug.com/jobs/2176682</t>
-        </is>
-      </c>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E833" t="inlineStr">
-        <is>
-          <t>Akron, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>2+ YOE</t>
-        </is>
-      </c>
-      <c r="G833" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H833" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I833" t="inlineStr">
-        <is>
-          <t>$50k-$64k/yr, $24-$31/hr</t>
-        </is>
-      </c>
-      <c r="J833" t="inlineStr">
-        <is>
-          <t>Project management for HVAC service installs; travel to sites; strong organization and communication; HVAC knowledge; willing to work full-time with benefits.</t>
-        </is>
-      </c>
-      <c r="K833" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N833" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O833" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:12:45 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B834" t="inlineStr">
-        <is>
-          <t>Project Manager Mechanical Construction</t>
-        </is>
-      </c>
-      <c r="C834" t="inlineStr">
-        <is>
-          <t>https://acca-careers.careerplug.com/jobs/3186895</t>
-        </is>
-      </c>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E834" t="inlineStr">
-        <is>
-          <t>Columbus, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="F834" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G834" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H834" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I834" t="inlineStr">
-        <is>
-          <t>$60k-$95k/yr, $28-$45/hr</t>
-        </is>
-      </c>
-      <c r="J834" t="inlineStr">
-        <is>
-          <t>Experience in mechanical or HVAC project management; strong understanding of construction drawings and mechanical systems; proficiency with AutoCAD, REVIT, or Autodesk tools; strong organizational and communication skills; ability to manage budgets, schedules, and subcontractors; problem-solving with a customer-focused approach.</t>
-        </is>
-      </c>
-      <c r="K834" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L834" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M834" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N834" t="inlineStr">
-        <is>
-          <t>AutoCAD, REVIT, Autodesk MEP, Navisworks</t>
-        </is>
-      </c>
-      <c r="O834" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:12:29 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>Reconstruction Project Manager</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>https://aboveallcleaningandrestorationllc.careerplug.com/jobs/2243007</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E835" t="inlineStr">
-        <is>
-          <t>Tucker, Georgia, United States</t>
-        </is>
-      </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G835" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H835" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I835" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J835" t="inlineStr">
-        <is>
-          <t>Experience as a Project Manager or in a similar role; proficient in Xactimate; detail-oriented; highly organized; able to manage multiple projects; strong verbal and written communication.</t>
-        </is>
-      </c>
-      <c r="K835" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L835" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M835" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N835" t="inlineStr">
-        <is>
-          <t>Xactimate</t>
-        </is>
-      </c>
-      <c r="O835" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:12:12 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B836" t="inlineStr">
-        <is>
-          <t>Project Manager/ Estimator</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr">
-        <is>
-          <t>https://1-800-water-damage-of-cleveland-west.careerplug.com/jobs/3145412</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E836" t="inlineStr">
-        <is>
-          <t>North Olmsted, Ohio, United States</t>
-        </is>
-      </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H836" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I836" t="inlineStr">
-        <is>
-          <t>$60k-$80k/yr, $28-$38/hr</t>
-        </is>
-      </c>
-      <c r="J836" t="inlineStr">
-        <is>
-          <t>Manage mitigation projects, supervise teams, budget and estimate jobs, strong customer service and communication; IICRC certifications; MS Office proficiency.</t>
-        </is>
-      </c>
-      <c r="K836" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L836" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M836" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N836" t="inlineStr">
-        <is>
-          <t>Microsoft Office</t>
-        </is>
-      </c>
-      <c r="O836" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:11:45 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B837" t="inlineStr">
-        <is>
-          <t>Visual Solutions Project Manager</t>
-        </is>
-      </c>
-      <c r="C837" t="inlineStr">
-        <is>
-          <t>https://fastsigns-careers.careerplug.com/jobs/1336201</t>
-        </is>
-      </c>
-      <c r="D837" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E837" t="inlineStr">
-        <is>
-          <t>York, Pennsylvania, United States</t>
-        </is>
-      </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G837" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H837" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I837" t="inlineStr">
-        <is>
-          <t>$43k-$52k/yr, $21-$25/hr</t>
-        </is>
-      </c>
-      <c r="J837" t="inlineStr">
-        <is>
-          <t>Detail-oriented project manager with strong client communication, coordination of installations, vendor sourcing, and sales experience.</t>
-        </is>
-      </c>
-      <c r="K837" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L837" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M837" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N837" t="inlineStr">
-        <is>
-          <t>Point of Sale</t>
-        </is>
-      </c>
-      <c r="O837" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:07:55 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B838" t="inlineStr">
-        <is>
-          <t>Inside Sales &amp; Project Manager – Signs &amp; Graphics</t>
-        </is>
-      </c>
-      <c r="C838" t="inlineStr">
-        <is>
-          <t>https://fastsigns-careers.careerplug.com/jobs/2805147</t>
-        </is>
-      </c>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>Orlando, Florida, United States</t>
-        </is>
-      </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G838" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H838" t="inlineStr">
-        <is>
-          <t>Mid Level</t>
-        </is>
-      </c>
-      <c r="I838" t="inlineStr">
-        <is>
-          <t>$31k-$41k/yr, $15-$20/hr</t>
-        </is>
-      </c>
-      <c r="J838" t="inlineStr">
-        <is>
-          <t>Quoted sign projects, manage customer relations, coordinate with production and installation, handle multiple orders, grow sales.</t>
-        </is>
-      </c>
-      <c r="K838" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L838" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M838" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N838" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator, CorelDRAW</t>
-        </is>
-      </c>
-      <c r="O838" t="inlineStr">
-        <is>
-          <t>2026-05-25 04:07:51 PM CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B839" t="inlineStr">
-        <is>
-          <t>Project Manager Assistant</t>
-        </is>
-      </c>
-      <c r="C839" t="inlineStr">
-        <is>
-          <t>https://crrcsifangamerica.apscareerportal.com/jobs/1210602</t>
-        </is>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>Direct Apply URL</t>
-        </is>
-      </c>
-      <c r="E839" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>4+ YOE</t>
-        </is>
-      </c>
-      <c r="G839" t="inlineStr">
-        <is>
-          <t>Onsite</t>
-        </is>
-      </c>
-      <c r="H839" t="inlineStr">
-        <is>
-          <t>Entry Level</t>
-        </is>
-      </c>
-      <c r="I839" t="inlineStr">
-        <is>
-          <t>$58k-$70k/yr, $28-$33/hr</t>
-        </is>
-      </c>
-      <c r="J839" t="inlineStr">
-        <is>
-          <t>Bachelor’s degree in business or engineering or 4 years related experience; strong project management, communication, and computer skills.</t>
-        </is>
-      </c>
-      <c r="K839" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="L839" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M839" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N839" t="inlineStr">
-        <is>
-          <t>Microsoft Office</t>
-        </is>
-      </c>
-      <c r="O839" t="inlineStr">
-        <is>
-          <t>2026-05-25 03:43:20 PM CDT</t>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>$80k-$235k/yr, $38-$112/hr</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>3-20+ years in construction/project management; leadership; schedule and cost control; strong communication; on-site interface with owners, architects, engineers.</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>https://whiting-turner.com</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr"/>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>Scheduling software, Project management software, Microsoft Excel</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:59:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>NRT Technology</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Marketing Tech Solutions Partner (Project Manager/Customer Success)</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/nrt/candidateportal/jobs/5709</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Las Vegas, Nevada, United States</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Account/relationship management, project delivery, client-facing, travel required, software/systems experience.</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>https://nrttech.com</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>Provides payment and kiosk solutions for the casino industry.</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>Microsoft Word, Microsoft Excel, Microsoft PowerPoint</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>2026-05-24 11:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O866"/>
+  <dimension ref="A1:O876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61165,11 +61165,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A841" t="inlineStr"/>
       <c r="B841" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -61220,21 +61216,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N841" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L841" t="inlineStr"/>
+      <c r="M841" t="inlineStr"/>
+      <c r="N841" t="inlineStr"/>
       <c r="O841" t="inlineStr">
         <is>
           <t>2026-05-25 04:45:36 PM CDT</t>
@@ -61242,11 +61226,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A842" t="inlineStr"/>
       <c r="B842" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -61297,16 +61277,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L842" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M842" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L842" t="inlineStr"/>
+      <c r="M842" t="inlineStr"/>
       <c r="N842" t="inlineStr">
         <is>
           <t>Microsoft Office, CRM/ERP systems, CAD software</t>
@@ -61319,11 +61291,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A843" t="inlineStr"/>
       <c r="B843" t="inlineStr">
         <is>
           <t>Estimator - Project Manager – ADA and Fire Safety Signage</t>
@@ -61374,16 +61342,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L843" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M843" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L843" t="inlineStr"/>
+      <c r="M843" t="inlineStr"/>
       <c r="N843" t="inlineStr">
         <is>
           <t>Estimating software, CRM, Microsoft Office</t>
@@ -61396,11 +61356,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A844" t="inlineStr"/>
       <c r="B844" t="inlineStr">
         <is>
           <t>Sales &amp; Project Manager</t>
@@ -61451,16 +61407,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L844" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M844" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L844" t="inlineStr"/>
+      <c r="M844" t="inlineStr"/>
       <c r="N844" t="inlineStr">
         <is>
           <t>Microsoft Excel, Microsoft Word, Google Workspace</t>
@@ -61473,11 +61421,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A845" t="inlineStr"/>
       <c r="B845" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -61528,16 +61472,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L845" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M845" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L845" t="inlineStr"/>
+      <c r="M845" t="inlineStr"/>
       <c r="N845" t="inlineStr">
         <is>
           <t>Trimble Connect, Procore</t>
@@ -61769,11 +61705,7 @@
           <t>Professional janitorial and commercial cleaning services provider.</t>
         </is>
       </c>
-      <c r="N848" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N848" t="inlineStr"/>
       <c r="O848" t="inlineStr">
         <is>
           <t>2026-05-25 04:32:53 PM CDT</t>
@@ -61846,11 +61778,7 @@
           <t>Professional janitorial and commercial cleaning services provider.</t>
         </is>
       </c>
-      <c r="N849" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N849" t="inlineStr"/>
       <c r="O849" t="inlineStr">
         <is>
           <t>2026-05-25 04:32:53 PM CDT</t>
@@ -61935,11 +61863,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A851" t="inlineStr"/>
       <c r="B851" t="inlineStr">
         <is>
           <t>Project Manager/Operations Kitchen Design and Remodeling Company</t>
@@ -61990,16 +61914,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L851" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M851" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L851" t="inlineStr"/>
+      <c r="M851" t="inlineStr"/>
       <c r="N851" t="inlineStr">
         <is>
           <t>QuickBooks, Microsoft Office Suite, Project management tools</t>
@@ -62077,11 +61993,7 @@
           <t>Provider of residential and commercial insulation and thermal protection services.</t>
         </is>
       </c>
-      <c r="N852" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N852" t="inlineStr"/>
       <c r="O852" t="inlineStr">
         <is>
           <t>2026-05-25 04:28:20 PM CDT</t>
@@ -62089,11 +62001,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A853" t="inlineStr"/>
       <c r="B853" t="inlineStr">
         <is>
           <t>Landscape Project Manager</t>
@@ -62144,21 +62052,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L853" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M853" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N853" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L853" t="inlineStr"/>
+      <c r="M853" t="inlineStr"/>
+      <c r="N853" t="inlineStr"/>
       <c r="O853" t="inlineStr">
         <is>
           <t>2026-05-25 04:10:17 PM CDT</t>
@@ -62166,11 +62062,7 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A854" t="inlineStr"/>
       <c r="B854" t="inlineStr">
         <is>
           <t>Heavy Civil Construction Project Manager</t>
@@ -62221,21 +62113,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L854" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M854" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N854" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L854" t="inlineStr"/>
+      <c r="M854" t="inlineStr"/>
+      <c r="N854" t="inlineStr"/>
       <c r="O854" t="inlineStr">
         <is>
           <t>2026-05-25 04:10:16 PM CDT</t>
@@ -62243,11 +62123,7 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A855" t="inlineStr"/>
       <c r="B855" t="inlineStr">
         <is>
           <t>Heavy Civil Construction Project Manager</t>
@@ -62298,16 +62174,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L855" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M855" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L855" t="inlineStr"/>
+      <c r="M855" t="inlineStr"/>
       <c r="N855" t="inlineStr">
         <is>
           <t>Project Scheduling Software, Budgeting Tools, Document Control Systems, Quality Management System</t>
@@ -62320,11 +62188,7 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A856" t="inlineStr"/>
       <c r="B856" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -62375,21 +62239,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L856" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M856" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N856" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L856" t="inlineStr"/>
+      <c r="M856" t="inlineStr"/>
+      <c r="N856" t="inlineStr"/>
       <c r="O856" t="inlineStr">
         <is>
           <t>2026-05-25 04:10:14 PM CDT</t>
@@ -62397,11 +62249,7 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A857" t="inlineStr"/>
       <c r="B857" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -62452,16 +62300,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L857" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M857" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L857" t="inlineStr"/>
+      <c r="M857" t="inlineStr"/>
       <c r="N857" t="inlineStr">
         <is>
           <t>Xactimate, Mobile devices</t>
@@ -62474,11 +62314,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A858" t="inlineStr"/>
       <c r="B858" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -62529,16 +62365,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L858" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M858" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L858" t="inlineStr"/>
+      <c r="M858" t="inlineStr"/>
       <c r="N858" t="inlineStr">
         <is>
           <t>Xactimate, Mobile Tablet, Insurance software</t>
@@ -62551,11 +62379,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A859" t="inlineStr"/>
       <c r="B859" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -62606,16 +62430,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L859" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M859" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L859" t="inlineStr"/>
+      <c r="M859" t="inlineStr"/>
       <c r="N859" t="inlineStr">
         <is>
           <t>Xactimate, tablet, mobile phone</t>
@@ -62628,11 +62444,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A860" t="inlineStr"/>
       <c r="B860" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -62683,21 +62495,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L860" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M860" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N860" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L860" t="inlineStr"/>
+      <c r="M860" t="inlineStr"/>
+      <c r="N860" t="inlineStr"/>
       <c r="O860" t="inlineStr">
         <is>
           <t>2026-05-25 04:09:14 PM CDT</t>
@@ -62705,11 +62505,7 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A861" t="inlineStr"/>
       <c r="B861" t="inlineStr">
         <is>
           <t>AV Installation Technician/Project Manager</t>
@@ -62760,16 +62556,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L861" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M861" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L861" t="inlineStr"/>
+      <c r="M861" t="inlineStr"/>
       <c r="N861" t="inlineStr">
         <is>
           <t>Control4, Savant, CAT5e/6, HDMI, DVI, RGB, Networking, Microsoft Office</t>
@@ -62782,11 +62570,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A862" t="inlineStr"/>
       <c r="B862" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -62837,21 +62621,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L862" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M862" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N862" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L862" t="inlineStr"/>
+      <c r="M862" t="inlineStr"/>
+      <c r="N862" t="inlineStr"/>
       <c r="O862" t="inlineStr">
         <is>
           <t>2026-05-25 04:08:38 PM CDT</t>
@@ -62859,11 +62631,7 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A863" t="inlineStr"/>
       <c r="B863" t="inlineStr">
         <is>
           <t>Residential A/V Project Manager</t>
@@ -62914,21 +62682,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L863" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M863" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N863" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L863" t="inlineStr"/>
+      <c r="M863" t="inlineStr"/>
+      <c r="N863" t="inlineStr"/>
       <c r="O863" t="inlineStr">
         <is>
           <t>2026-05-25 04:08:35 PM CDT</t>
@@ -63159,6 +62915,772 @@
       <c r="O866" t="inlineStr">
         <is>
           <t>2026-05-24 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Estimator - Project Manager – ADA and Fire Safety Signage</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>https://signarama-redmond-wa.careerplug.com/jobs/3371423</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Redmond, Washington, United States</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>$48k-$96k/yr, $23-$46/hr</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Experience in estimating, project management, or sales within signage or construction; knowledge of ADA and life-safety signage; strong communication; proficiency with estimating tools, CRM, and Microsoft Office; self-starter with business development mindset.</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>Estimating tools, CRM, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:24:08 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Sales &amp; Project Manager</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>https://protect-painters-of-west-richmond.careerplug.com/jobs/1641183</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Richmond, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>$70k-$100k/yr, $33-$48/hr</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Oversee sales, estimates, scheduling; manage subcontractors; 2+ years project management; bilingual a plus.</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>MS Excel, MS Word, Google Workspace</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:21:03 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Project Manager/Operations Kitchen Design and Remodeling Company</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>https://kitchen-solvers-south-bend.careerplug.com/jobs/3202590</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>South Bend, Indiana, United States</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Experience in office and/or project management; QuickBooks proficiency; familiarity with kitchen design; strong organizational and communication skills.</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>QuickBooks, Microsoft Office, Project management tools</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:11:27 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>https://five-star-painting-of-lamesa-tx.careerplug.com/jobs/2417027</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Amarillo, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Manage residential and light commercial painting projects; schedule, coordinate subcontractors, manage budgets and communicate with owners, estimators, and crews.</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>MS Excel, MS Word, Google Calendar, Google Drive, CORE</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:04:42 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Blue Kangaroo Packoutz</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-careers.careerplug.com/jobs/2408708</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Punta Gorda, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>$62k-$74k/yr, $30-$36/hr</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Oversee remediation projects; coordinate contents packing, cleaning, and logistics; lead safety and client communications.</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>https://bluekangaroopackoutz.com</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>Specialized contents cleaning and property restoration services.</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:58:08 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Blue Kangaroo Packoutz</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Field &amp; Warehouse Technician/Potential Project Manager</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>https://blue-kangaroo-packoutz-careers.careerplug.com/jobs/2820496</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Grimes, Iowa, United States</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>$31k-$41k/yr, $15-$20/hr</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>Experience in restoration/construction preferred; valid driver's license; able to multitask; strong work ethic and customer service.</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>https://bluekangaroopackoutz.com</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>Specialized contents cleaning and property restoration services.</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:58:08 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>AlphaGraphics</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Project Manager - Printing</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>https://alphagraphics-careers.careerplug.com/jobs/2865057</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Cary, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>$36k-$47k/yr, $17-$23/hr</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>High school diploma or equivalent; some college preferred; experience in project management in printing or signage; strong communication; organizational skills; detail-oriented.</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>https://alphagraphics.com</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr"/>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:55:36 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>1-800 WATER DAMAGE</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Project Manager/ Estimator</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>https://1-800-water-damage-careers.careerplug.com/jobs/3145412</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>North Olmsted, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>$60k-$80k/yr, $28-$38/hr</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Experience managing mitigation projects, supervising technicians, budgeting, estimating; strong MS Office; IICRC certifications; customer service; insurance and claims knowledge.</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>https://1800waterdamage.com</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>Provides emergency property restoration and disaster cleanup services.</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:53:56 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>GHD</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Graduate Planner / Associate Project Manager</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>https://ejov.fa.ca2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/26460</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Sacramento, California, United States</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>$60k-$70k/yr, $28-$33/hr</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Political Science; 0-2 years experience; data analysis, stakeholder engagement, communications.</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>https://ghd.com</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>Global professional services firm specializing in engineering and architecture.</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>2026-05-25 05:22:07 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Day Translations</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Japanese Project Manager</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>https://daytranslations.bamboohr.com/careers/100</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Experienced project manager with localization, customer service, and business administration; familiar with CAT tools (Smartcat, MemoQ) and TMS (Trados); degree preferred; strong English and foreign language skills; excellent organization.</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>https://daytranslations.com</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>Provides global language translation, interpretation, and localization services.</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>CAT tools, Smartcat, MemoQ, Trados, Translation Management System</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>2026-05-24 07:00:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O876"/>
+  <dimension ref="A1:O885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62919,11 +62919,7 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A867" t="inlineStr"/>
       <c r="B867" t="inlineStr">
         <is>
           <t>Estimator - Project Manager – ADA and Fire Safety Signage</t>
@@ -62974,16 +62970,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L867" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M867" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L867" t="inlineStr"/>
+      <c r="M867" t="inlineStr"/>
       <c r="N867" t="inlineStr">
         <is>
           <t>Estimating tools, CRM, Microsoft Office</t>
@@ -62996,11 +62984,7 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A868" t="inlineStr"/>
       <c r="B868" t="inlineStr">
         <is>
           <t>Sales &amp; Project Manager</t>
@@ -63051,16 +63035,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L868" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M868" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L868" t="inlineStr"/>
+      <c r="M868" t="inlineStr"/>
       <c r="N868" t="inlineStr">
         <is>
           <t>MS Excel, MS Word, Google Workspace</t>
@@ -63073,11 +63049,7 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A869" t="inlineStr"/>
       <c r="B869" t="inlineStr">
         <is>
           <t>Project Manager/Operations Kitchen Design and Remodeling Company</t>
@@ -63128,16 +63100,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L869" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M869" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L869" t="inlineStr"/>
+      <c r="M869" t="inlineStr"/>
       <c r="N869" t="inlineStr">
         <is>
           <t>QuickBooks, Microsoft Office, Project management tools</t>
@@ -63150,11 +63114,7 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A870" t="inlineStr"/>
       <c r="B870" t="inlineStr">
         <is>
           <t>Project Manager</t>
@@ -63205,16 +63165,8 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="L870" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M870" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="L870" t="inlineStr"/>
+      <c r="M870" t="inlineStr"/>
       <c r="N870" t="inlineStr">
         <is>
           <t>MS Excel, MS Word, Google Calendar, Google Drive, CORE</t>
@@ -63292,11 +63244,7 @@
           <t>Specialized contents cleaning and property restoration services.</t>
         </is>
       </c>
-      <c r="N871" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N871" t="inlineStr"/>
       <c r="O871" t="inlineStr">
         <is>
           <t>2026-05-25 08:58:08 PM CDT</t>
@@ -63369,11 +63317,7 @@
           <t>Specialized contents cleaning and property restoration services.</t>
         </is>
       </c>
-      <c r="N872" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N872" t="inlineStr"/>
       <c r="O872" t="inlineStr">
         <is>
           <t>2026-05-25 08:58:08 PM CDT</t>
@@ -63442,11 +63386,7 @@
         </is>
       </c>
       <c r="M873" t="inlineStr"/>
-      <c r="N873" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N873" t="inlineStr"/>
       <c r="O873" t="inlineStr">
         <is>
           <t>2026-05-25 08:55:36 PM CDT</t>
@@ -63681,6 +63621,699 @@
       <c r="O876" t="inlineStr">
         <is>
           <t>2026-05-24 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Emory Healthcare</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>https://emory.jibeapply.com/jobs/156785</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>Manages financial information systems; Bachelor's in accounting, computer science, or business; four years project planning experience or a Master's with two years planning experience.</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>https://emoryhealthcare.org</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>Academic healthcare system providing patient care and medical services.</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>2026-05-26 07:31:16 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Hillsborough County</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Project Manager (Real Estate Services)</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>https://fa-eqsg-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/4243</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Miami, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>4+ YOE</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>$68k-$93k/yr, $32-$45/hr</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>Real estate, title analysis, and project management experience; Florida Real Estate license or driver license preferred; bachelor’s degree in Real Estate/Business/Public Administration or related field.</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>https://hcfl.gov</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>Providing essential public services and infrastructure to Florida residents.</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>Project Management, Title Analysis, Contract/Legal Documentation, Real Estate Transactions</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>2026-05-26 06:21:43 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>PLZ Corp</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Project Manager I</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>https://recruiting2.ultipro.com/plz1000plz/JobBoard/a12f577a-8447-4e92-82b4-7475368b7d64/OpportunityDetail?opportunityId=3e2f14bf-0ee3-41d2-9a6e-a1ac5c1f343a</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Coal City or Indianapolis</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>$65k-$80k/yr, $31-$38/hr</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; 3+ years in consumer products/customer service roles; SAP experience preferred; strong communication and presentation skills.</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>https://plzcorp.com</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>Manufactures specialty aerosol and liquid products for diverse markets.</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>2026-05-26 06:02:45 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Cyber Security Project Manager  - Water Utilities, Consulting</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>https://cognizant.taleo.net/careersection/lateral/jobdetail.ftl?job=47352&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Teaneck, New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>Experienced cyber security project manager managing enterprise programs within utilities or critical infrastructure.</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>https://cognizant.com</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>Provides IT consulting and technology services to global enterprises.</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>MS Project, Jira, Azure DevOps, Cisco ISE, Microsoft Entra ID, Azure, SIEM (Splunk, QRadar)</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>2026-05-26 05:45:24 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Archadeck of Northeast Cleveland</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>https://archadeck-northeast-cleveland.careerplug.com/jobs/2907013</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Macedonia, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>$52k-$72k/yr, $25-$35/hr</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>Manage daily construction, quality control, site visits, coordinate crews and vendors, ensure on-time, on-budget projects; strong customer service, organization, communication, problem-solving; requires driver’s license.</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>https://archadeck.com</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>Designs and builds custom outdoor living structures and spaces.</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>Project Management Software, Mobile Tools</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>2026-05-26 01:38:55 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Reli</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Technical Project Manager, E-commerce Operations</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/shopreli/85b5c22f-55bc-451d-95e4-719f77f91729/apply</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Cerritos, California, United States</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>3-6+ years in project or program management; Bachelor's degree or equivalent; strong written and verbal communication; comfortable with technical teams; basic ecommerce knowledge.</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>https://shopreli.com</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>Sells household and business supplies through multiple online marketplaces.</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>Asana, JIRA, Confluence, Slack, Google Workspace, Otter</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:26:32 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Project Manager – Project Management Officer</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>https://worldbankgroup.csod.com/ux/ats/careersite/6/home/requisition/36475?c=worldbankgroup</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Washington, District of Columbia, United States</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>Master’s degree with five years of experience; PMO leadership 3+ years; strong finance, procurement, and PM skills.</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>https://worldbank.org</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>Provide financial and technical assistance to developing countries globally.</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>MS Project</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>MasTec</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Data Center</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>https://jobs.mastec.com/jobs/64147/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Abernathy, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>1–4 years PM experience in transmission, substations, data center utilities, or EPC; Bachelor in engineering/construction/project mgmt; PMP/ CCM pursuing; Primavera and MS Office proficiency; safety/regulatory knowledge.</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>https://mastec.com</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>Provides engineering and construction for energy and communications infrastructure.</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>Primavera, Microsoft Excel, Microsoft Word, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>2026-05-25 05:39:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>MasTec</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Data Center</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>https://careers.mastec.com/jobs/64147/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Abernathy, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>1–4 years in project management for transmission, substation, distribution, data center utilities, or EPC projects; pursuing PMP or CCM; engineering/related degree; proficient in Primavera and MS Office; strong leadership and communication.</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>https://mastec.com</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>Builds and maintains energy, communications, and utility infrastructure.</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>Primavera, Microsoft Office Suite</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>2026-05-25 05:39:00 PM CDT</t>
         </is>
       </c>
     </row>

--- a/hiring_cafe_jobs.xlsx
+++ b/hiring_cafe_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O885"/>
+  <dimension ref="A1:O915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63690,11 +63690,7 @@
           <t>Academic healthcare system providing patient care and medical services.</t>
         </is>
       </c>
-      <c r="N877" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N877" t="inlineStr"/>
       <c r="O877" t="inlineStr">
         <is>
           <t>2026-05-26 07:31:16 AM CDT</t>
@@ -64314,6 +64310,2312 @@
       <c r="O885" t="inlineStr">
         <is>
           <t>2026-05-25 05:39:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Atlas Copco</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager (Voorheesville, New York, United States)</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>https://www.careers.homeofindustrialideas.com/job/Voorheesville-Assistant-Project-Manager-New/1397294633/</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Voorheesville, New York, United States</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>$67k-$81k/yr, $32-$38/hr</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>Bachelor's degree or equivalent work experience; strong project coordination, budgeting, scheduling, and customer service; cross-functional collaboration.</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>https://atlascopco.com</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>Manufactures industrial compressors, vacuum systems, and power tools.</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:24:59 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Marsden Services</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager (APM) - FEI</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>https://web.fountain.com/marsden/apply/assistant-project-manager-apm-fei</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Cincinnati, Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>1-3 years of experience in commercial mechanical construction; field experience with HVAC/plumbing/piping; proficient with MS Office; strong communication; Procore/ComputerEase a plus.</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr"/>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>Provides commercial janitorial, security, and facility maintenance services.</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Project, Procore, ComputerEase</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:06:55 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Texas Woman's University</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Project Manager - Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>https://ewal.fa.us8.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/12613</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Denton, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>Bachelor's degree; minimum three years in marketing/communications project management; budgeting and analysis preferred.</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>https://twu.edu</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>Provides undergraduate and graduate degree programs and academic research.</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>Google Suite, Creative Cloud Storage Management, Microsoft Office, Constant Contact, Asana, Adobe InDesign, Adobe Photoshop, Adobe Illustrator, Adobe Acrobat, Lucid Press</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:57:30 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>CLX Engineering</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Project Manager - Software</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4197213</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Sanford, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>$80k-$110k/yr, $38-$52/hr</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>2–5+ years PM experience coordinating enterprise software deployments and OT environments; strong customer-facing skills; travel to customer sites.</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>https://clxengineering.com</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>Provides industrial automation and control system integration services.</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>Microsoft Office 365, Teams, SharePoint, Project management platforms</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:54:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Toyota Automated Logistics</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>https://myjobs.adp.com/talcareers/cx/job-details?reqId=5001200015000</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Maryland Heights, Missouri, United States</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>Coordinate PLM data, manage part lifecycle, track engineering deliverables and documentation; identify duplicates and obsolescence; support cross-functional communication and continuous improvement.</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>https://toyota-automated-logistics.com</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>Integrated warehouse automation systems, software, and lifecycle services.</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Microsoft Outlook, Microsoft Teams, SharePoint, Power BI</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:34:33 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Himmel's Architectural Door and Hardware</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Project Manager (Dallas)</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>https://himmels-architechtural-door-hardware.prismhr-hire.com/job/1026924/project-manager-dallas</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Dallas, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>Excellent organizational, communication, and multitasking skills; proficient with Excel, Word, Outlook, and Bluebeam; experience reading plans; Familiar with industry software (Comsense); able to work in a fast-paced environment; strong customer service.</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>https://himmels.com</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>Supplier of commercial doors, frames, and architectural hardware products.</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>Excel, Word, Outlook, Bluebeam, Comsense</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:31:34 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Himmel's Architectural Door and Hardware</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager (New Orleans)</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>https://himmels-architechtural-door-hardware.prismhr-hire.com/job/1026921/assistant-project-manager-new-orleans</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>New Orleans, Louisiana, United States</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>Assist the project manager; communicate with customers, vendors, and architects; read plans; 1 year PM and commercial construction experience; proficient in Excel, Word, Outlook, Bluebeam.</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>https://himmels.com</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>Supplier of commercial doors, frames, and architectural hardware products.</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>Comsense, Bluebeam, Excel, Word, Outlook</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:30:24 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Himmel's Architectural Door and Hardware</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager (Prairieville)</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>https://himmels-architechtural-door-hardware.prismhr-hire.com/job/1026920/assistant-project-manager-prairieville</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Prairieville, Louisiana, United States</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>Assist project manager; communicate with customers, vendors, architects; read plans; use Comsense; Excel/Word/Outlook/Bluebeam; multi-task; fast-paced environment; background check required.</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>https://himmels.com</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>Supplier of commercial doors, frames, and architectural hardware products.</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>Comsense, Bluebeam, Excel, Word, Outlook</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:29:20 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Himmel's Architectural Door and Hardware</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager (Dallas)</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>https://himmels-architechtural-door-hardware.prismhr-hire.com/job/1026918/assistant-project-manager-dallas</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Dallas, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>Assist the project manager across project phases; strong organization, communication, and computer skills; ability to multitask in a fast-paced environment; background check and drug screening.</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>https://himmels.com</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>Supplier of commercial doors, frames, and architectural hardware products.</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>Excel, Word, Outlook, Bluebeam, Comsense</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:27:48 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>MJ Nester</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Assistant Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4191426</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Pottstown, Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>Administrative or construction experience; strong organization, communication, multitasking; detail-oriented; computer skills.</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Part Time, Full Time</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>https://mjnester.com</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>Provides industrial maintenance, rigging, and equipment installation services.</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>Microsoft Outlook, Microsoft Excel, Microsoft Word, Project management software</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:22:12 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>NVR</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Construction Project Manager Trainee</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>https://phg.tbe.taleo.net/phg01/ats/careers/requisition.jsp?org=NVRINC&amp;cws=58&amp;rid=37030</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Polk County, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree preferred; strong time management, organizational, and interpersonal skills; valid driver’s license; leadership ability; construction or customer relations experience a plus.</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>https://nvrinc.com</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>Constructs residential homes and provides mortgage and title services.</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>2026-05-26 10:13:56 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>NVR</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Construction Project Manager Trainee</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>https://phg.tbe.taleo.net/phg01/ats/careers/requisition.jsp?org=NVRINC&amp;cws=58&amp;rid=37029</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>No Prior Experience Required</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree preferred; strong time management, organizational and interpersonal skills; leadership; valid driver’s license; construction or customer-relations experience a plus.</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>https://nvrinc.com</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>Constructs residential homes and provides mortgage and title services.</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:15:56 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>NVR</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Construction Project Manager Trainee</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>https://phg.tbe.taleo.net/phg01/ats/careers/requisition.jsp?org=NVRINC&amp;cws=58&amp;rid=37028</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Huntersville, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree preferred; strong time management, organizational skills, attention to detail; excellent interpersonal skills; leadership abilities; current driver’s license; construction and/or customer relations experience a plus.</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>https://nvrinc.com</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>Constructs residential homes and provides mortgage and title services.</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:56:53 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Sault Tribe Incorporated</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Project Manager, Level 3</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=f4b11e01-e1da-41a8-a389-8fc2829c0503&amp;jobId=566992</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Charleston, South Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>$160k-$165k/yr, $76-$79/hr</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>Lead IT projects; manage BA and QA teams; Agile/hybrid SDLC; DoD secret clearance eligibility.</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>https://saulttribeinc.com</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>Provides technical and professional services to federal government agencies.</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>JIRA, Azure DevOps, MS Project</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:49:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>MPSW</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Project Manager/Estimator </t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mpsw/jobs/5230662008</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Phoenix, Arizona, United States</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Entry Level (0+ YOE)</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Entry-level role to learn estimating, submittals, pricing and project coordination; strong organizational and communication skills; MS Office proficiency.</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>https://mpsw.com</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>Provides engineered commercial HVAC solutions and building automation controls.</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel, PowerPoint, Word</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:33:29 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Project Manager - Asset Assurance</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>https://ebcs.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/41173</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Tampa or Atlanta or Nashville or Los Angeles or Richmond or Austin or Dallas or Cleveland or Lexington or Philadelphia</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>$80k-$95k/yr, $38-$45/hr</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Experience leading regional or national teams; facility/technical inspections; team leadership; knowledge of safety standards; valid driver's license.</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>https://arcadis.com</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>Designing and engineering sustainable solutions for natural and built environments</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:21:39 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>https://egay.fa.us6.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX/requisitions/job/41555</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Andrews, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Engineering, Project Management or related field; minimum 3 years project management in manufacturing/engineering; PMP preferred; located in Andrews/Odessa/Midland; strong ERP/PM tools; travel up to 10%.</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>https://nov.com</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>Manufactures and provides equipment for the energy industry.</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>MS Project, Oracle, Microsoft Office Suite (Excel, Word, PowerPoint, Outlook)</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>2026-05-26 07:42:47 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Valley Cabinet</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=c47dcd78-fc35-4d00-b238-2c594eafc2b5&amp;jobId=619661</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>De Pere, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>2-3 years of project management in residential construction, cabinetry, or related field; strong cabinet construction, layout, and communication skills; proficient with project management software; valid driver’s license.</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>https://valleycabinetinc.com</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>Designs and manufactures custom wood cabinetry for homes.</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>Cabinet Vision, CAD drafting, BuilderTrend, ProCore</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr">
+        <is>
+          <t>2026-05-26 07:15:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Ruppert Landscape</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>https://jobs.jobvite.com/ruppertlandscape/job/olobAfwe?nl=1&amp;fr=true</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Gainesville, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Multi-task in a fast-paced environment; landscape construction experience; read blueprints; negotiate with vendors/customers; build relationships; strong organizational skills; proficient in Word, Excel, Outlook; basic business math and financial reporting.</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>https://ruppertlandscape.com</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>Commercial landscape construction and maintenance services provider.</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>Word, Excel, Outlook</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>2026-05-26 07:00:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Springs Window Fashions</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>https://careers-springswindowfashions.icims.com/jobs/12257/job?utm_source=hiringcafe_integration&amp;iis=Job%20Board&amp;iisn=HiringCafe</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Middletown, Wisconsin, United States</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Bachelor's degree in Business or Information Technology; 2+ years in project management; PMP a plus; ERP project experience helpful; strong PM skills and tools; excellent communication.</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>https://springswindowfashions.com</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>Manufacturer of custom window coverings for residential and commercial buildings.</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>Excel, Power BI, Smartsheet, Microsoft Project, PowerPoint</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>2026-05-26 06:57:00 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>U.S. Army Corps of Engineers</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>https://www.usajobs.gov/job/870534400</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Winchester, Virginia, United States</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>$57k-$133k/yr, $27-$64/hr</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Project management experience, life-cycle project oversight, coordination with design/construction teams, and adherence to policies and funding limits.</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Full Time, Contract, Temporary</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>https://army.mil</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>Provides public engineering, design, and construction management services.</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>2026-05-26 05:38:22 AM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Thayer Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>https://jobs.dayforcehcm.com/en-US/tisg/candidateportal/jobs/3648</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Warren, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Coordinate between field and office, manage data, billing, and schedules; ensure timely payroll and project records.</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>https://thetisgroup.com</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>Infrastructure construction and maintenance for utility and telecommunications sectors.</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Excel</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>2026-05-25 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Fire Alarm Installation Assistant Project Manager-Miller Electric Company</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>https://careers-emcorgroup.icims.com/jobs/50151/fire-alarm-installation-assistant-project-manager-miller-electric-company/job?in_iframe=1</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Jacksonville, Florida, United States</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Fire alarm experience; assistant PM/coordination exp; reading electrical/mechanical drawings; proficient in Microsoft 365; COINS experience; preferred college degree and NICET certification.</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>https://mecojax.com</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>Provides electrical and technology infrastructure construction and maintenance services.</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>Microsoft 365, COINS, Electrical Drawings</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>2026-05-25 11:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Advocate Health</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Project Coordinator AHEC</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>https://aah.wd5.myworkdayjobs.com/external/job/Charlotte-NC---5039-Airport-Center-Pkwy/Project-Coordinator-AHEC_R213241</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Charlotte, North Carolina, United States</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>$45k-$68k/yr, $21-$32/hr</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Bachelor's degree required; administrative experience preferred; strong communication and organizational skills.</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>https://advocatehealth.org</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>Provides integrated clinical care through a network of hospitals.</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>Microsoft Office</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>UCHealth</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>https://css-uchealth-prd.inforcloudsuite.com/hcm/Jobs/navigation/JobPosting%5BJobPostingSet%5D(1000,385993,1).JobPostingDisplayNav?csk.HROrganization=1000&amp;csk.JobBoard=EXTERNAL</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Aurora, Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>$70k-$105k/yr, $33-$50/hr</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Bachelor's degree and 3 years of relevant project management experience.</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>https://uchealth.org</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>Operates acute-care hospitals and clinics providing comprehensive medical services.</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Colas Construction</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>http://colasconstruction.applytojob.com/apply/aMVxEmizub/Project-Manager</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Portland, Oregon, United States</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Bachelor's in Construction Management, Engineering, Architecture or related field; 3-8 years construction experience with 3-5+ years in management; experience with structural concrete and wood framing; on-site Monday–Friday.</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>https://colasconstruction.com</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>Provides general contracting services for commercial and community-focused projects.</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Construction Project Manager</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>https://linde.csod.com/ux/ats/careersite/23/home/requisition/29158?c=linde</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>The Woodlands, Texas, United States</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>3+ YOE</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>BS/BA or equivalent; 3+ years leading large-scale construction projects ($25M+); strong leadership, communication, and software skills.</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>https://linde.com</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>Supplies industrial gases and develops gas processing technologies.</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Lotus Notes</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>https://careers.umich.edu/job_detail/apply/278013</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Ann Arbor, Michigan, United States</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>$56k-$70k/yr, $26-$33/hr</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Bachelor's degree and 2 years of progressive experience in program/operations management or project coordination; strong organizational, communication, and problem-solving skills; ability to manage multiple stakeholders and workflows; proficient with project management tools.</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>https://umich.edu</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>Public research university offering undergraduate and graduate education.</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>Project management software</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Center for Justice Innovation</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Project Manager, Eviction Diversion Initiative (Syracuse)</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>http://innovatingjustice.applytojob.com/apply/3gYP5MngNm/Project-Manager-Eviction-Diversion-Initiative-Syracuse</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Syracuse, New York, United States</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>2+ YOE</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>Mid Level</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>$64k-$79k/yr, $30-$38/hr</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Bachelor's degree with 2-3 years relevant experience, or Master's with 1-2 years; 1-2 years supervisory experience; strong communication and leadership; landlord/tenant court knowledge preferred; English plus other languages desirable.</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>https://innovatingjustice.org</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>Creating innovative solutions to improve the criminal justice system.</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 PM CDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Project Manager I -Data Analytics</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>https://kp.taleo.net/careersection/external/jobdetail.ftl?job=1424537&amp;lang=en</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Direct Apply URL</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Los Angeles, California, United States</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>1+ YOE</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>Entry Level</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Project coordination and planning experience; support project plans, scheduling, and budgets; strong communication.</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>https://kaiserpermanente.org</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>Provides integrated medical care and health insurance plans.</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>Microsoft Excel</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:00:00 AM CDT</t>
         </is>
       </c>
     </row>
